--- a/docs/CDOP Enumerated Values Lists.xlsx
+++ b/docs/CDOP Enumerated Values Lists.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Fast Track Pods/R2FT Enumerated Values/Enum List with R2 Fast Track Pods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="8_{5B2DF6FD-60F9-42F7-9793-6864D7C82CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56D5A4D8-B432-4ABD-9874-5108CB21A4A0}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{5B2DF6FD-60F9-42F7-9793-6864D7C82CD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA822B43-4A17-4CC3-B33A-41402F4AFA51}"/>
   <bookViews>
-    <workbookView xWindow="-28080" yWindow="1035" windowWidth="27285" windowHeight="14370" xr2:uid="{6157C829-B9E8-47C5-B94D-577BB9DC27B4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6157C829-B9E8-47C5-B94D-577BB9DC27B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Enumerated Values Lists" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="1905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2237" uniqueCount="1909">
   <si>
     <t>Enumerated Values List</t>
   </si>
@@ -4328,12 +4328,6 @@
     <t xml:space="preserve">Any combination of the above </t>
   </si>
   <si>
-    <t>origin_registry &amp; current_registry &amp; current_project_issuance_registry</t>
-  </si>
-  <si>
-    <t>crediting_program_name &amp; previous_project_crediting_program_name</t>
-  </si>
-  <si>
     <t>financing_options</t>
   </si>
   <si>
@@ -5609,12 +5603,6 @@
     <t>Waste Reduction</t>
   </si>
   <si>
-    <t>current_validation_stage</t>
-  </si>
-  <si>
-    <t>current_validation_stage_status</t>
-  </si>
-  <si>
     <t>validation_body_sectoral_scopes</t>
   </si>
   <si>
@@ -5636,9 +5624,6 @@
     <t>On-site audits and interviews</t>
   </si>
   <si>
-    <t>In progress</t>
-  </si>
-  <si>
     <t>Program validation</t>
   </si>
   <si>
@@ -5751,6 +5736,33 @@
   </si>
   <si>
     <t>Pending review (Audit currently in progress)</t>
+  </si>
+  <si>
+    <t>validation_status</t>
+  </si>
+  <si>
+    <t>vvb_type</t>
+  </si>
+  <si>
+    <t>Validation body</t>
+  </si>
+  <si>
+    <t>Verification body</t>
+  </si>
+  <si>
+    <t>sectoral_scopes</t>
+  </si>
+  <si>
+    <t>registration_status</t>
+  </si>
+  <si>
+    <t>Transferred out</t>
+  </si>
+  <si>
+    <t>origin_registry &amp; current_registry &amp; current_project_issuance_registry &amp; registry_name</t>
+  </si>
+  <si>
+    <t>crediting_program_name &amp; previous_project_crediting_program_name &amp; program_name</t>
   </si>
 </sst>
 </file>
@@ -5897,7 +5909,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5961,21 +5973,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6312,7 +6320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B85F238-80B8-43F8-AABF-7B9427088CCA}">
-  <dimension ref="A1:DU500"/>
+  <dimension ref="A1:DW500"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="26.08984375" bestFit="1" customWidth="1"/>
@@ -6355,16 +6363,16 @@
     <col min="109" max="109" width="33.7265625" customWidth="1"/>
     <col min="110" max="110" width="24" customWidth="1"/>
     <col min="111" max="111" width="22.36328125" bestFit="1" customWidth="1"/>
-    <col min="113" max="113" width="28.7265625" bestFit="1" customWidth="1"/>
-    <col min="115" max="115" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="113" max="113" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="29.81640625" bestFit="1" customWidth="1"/>
     <col min="119" max="119" width="15.90625" bestFit="1" customWidth="1"/>
     <col min="121" max="121" width="21.26953125" bestFit="1" customWidth="1"/>
     <col min="123" max="123" width="23.7265625" bestFit="1" customWidth="1"/>
     <col min="125" max="125" width="33.26953125" bestFit="1" customWidth="1"/>
+    <col min="127" max="127" width="17.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:127" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6387,7 +6395,7 @@
       <c r="R1" s="12"/>
       <c r="S1" s="12"/>
     </row>
-    <row r="2" spans="1:125" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:127" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -6408,7 +6416,7 @@
       <c r="R2" s="12"/>
       <c r="S2" s="12"/>
     </row>
-    <row r="3" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>1332</v>
       </c>
@@ -6474,10 +6482,10 @@
         <v>1349</v>
       </c>
       <c r="AK3" t="s">
-        <v>1430</v>
+        <v>1907</v>
       </c>
       <c r="AM3" t="s">
-        <v>1431</v>
+        <v>1908</v>
       </c>
       <c r="AO3" t="s">
         <v>1350</v>
@@ -6513,125 +6521,122 @@
         <v>1358</v>
       </c>
       <c r="BK3" s="9" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="BL3" s="9"/>
       <c r="BM3" s="9" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="BN3" s="9"/>
       <c r="BO3" s="9" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="BP3" s="9"/>
       <c r="BQ3" s="9" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="BR3" s="9"/>
       <c r="BS3" s="9" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="BT3" s="9"/>
       <c r="BU3" s="23" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="BV3" s="23"/>
       <c r="BW3" s="9" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="BX3" s="9"/>
       <c r="BY3" s="9" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="BZ3" s="9"/>
       <c r="CA3" s="9" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="CB3" s="9"/>
       <c r="CC3" s="9" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="CD3" s="9"/>
       <c r="CE3" s="9" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="CG3" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="CI3" t="s">
+        <v>1682</v>
+      </c>
+      <c r="CK3" s="22" t="s">
+        <v>1681</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>1683</v>
+      </c>
+      <c r="CO3" t="s">
         <v>1684</v>
       </c>
-      <c r="CK3" s="22" t="s">
-        <v>1683</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>1685</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>1686</v>
-      </c>
       <c r="CQ3" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="CS3" s="27" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="CT3" s="27"/>
       <c r="CU3" s="27" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="CV3" s="27"/>
       <c r="CW3" s="27" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="CX3" s="27"/>
       <c r="CY3" s="27" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="CZ3" s="27"/>
       <c r="DA3" s="27" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="DB3" s="27"/>
       <c r="DC3" s="27" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="DD3" s="27"/>
       <c r="DE3" s="27" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="DG3" s="9" t="s">
-        <v>1857</v>
-      </c>
-      <c r="DH3" s="34"/>
-      <c r="DI3" s="35" t="s">
-        <v>1858</v>
-      </c>
-      <c r="DJ3" s="34"/>
-      <c r="DK3" s="19" t="s">
+        <v>1856</v>
+      </c>
+      <c r="DI3" s="19" t="s">
         <v>1353</v>
       </c>
-      <c r="DL3" s="34"/>
-      <c r="DM3" s="9" t="s">
-        <v>1859</v>
-      </c>
-      <c r="DN3" s="34"/>
+      <c r="DK3" s="9" t="s">
+        <v>1904</v>
+      </c>
+      <c r="DM3" s="33" t="s">
+        <v>1901</v>
+      </c>
       <c r="DO3" s="9" t="s">
-        <v>1860</v>
-      </c>
-      <c r="DQ3" s="34" t="s">
-        <v>1885</v>
-      </c>
-      <c r="DR3" s="34"/>
-      <c r="DS3" s="34" t="s">
-        <v>1886</v>
-      </c>
-      <c r="DT3" s="34"/>
-      <c r="DU3" s="34" t="s">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="4" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+        <v>1900</v>
+      </c>
+      <c r="DQ3" t="s">
+        <v>1880</v>
+      </c>
+      <c r="DS3" t="s">
+        <v>1881</v>
+      </c>
+      <c r="DU3" t="s">
+        <v>1882</v>
+      </c>
+      <c r="DW3" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="4" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -6748,54 +6753,54 @@
         <v>1364</v>
       </c>
       <c r="BK4" s="24" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="BL4" s="9"/>
       <c r="BM4" s="24" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="BN4" s="24"/>
       <c r="BO4" s="24" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="BP4" s="24"/>
       <c r="BQ4" s="24" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="BR4" s="24"/>
       <c r="BS4" s="24" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="BT4" s="24"/>
       <c r="BU4" s="25" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="BV4" s="25"/>
       <c r="BW4" s="24" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="BX4" s="24"/>
       <c r="BY4" s="24" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="BZ4" s="24"/>
       <c r="CA4" s="24" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="CB4" s="24"/>
       <c r="CC4" s="24" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="CD4" s="24"/>
       <c r="CE4" s="24" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="CG4" s="1" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="CH4" s="1"/>
       <c r="CI4" s="1" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="CJ4" s="1"/>
       <c r="CK4" s="1" t="s">
@@ -6803,78 +6808,81 @@
       </c>
       <c r="CL4" s="1"/>
       <c r="CM4" s="1" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="CN4" s="1"/>
       <c r="CO4" s="1" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="CP4" s="1"/>
       <c r="CQ4" s="1" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="CR4" s="1"/>
       <c r="CS4" s="26" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="CT4" s="26"/>
       <c r="CU4" s="26" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="CV4" s="26"/>
       <c r="CW4" s="26" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="CX4" s="26"/>
       <c r="CY4" s="26" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="CZ4" s="26"/>
       <c r="DA4" s="26" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="DB4" s="26"/>
       <c r="DC4" s="26" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="DD4" s="26"/>
       <c r="DE4" s="26" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="DF4" s="26"/>
       <c r="DG4" s="24" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="DH4" s="1"/>
       <c r="DI4" s="31" t="s">
-        <v>1858</v>
+        <v>1353</v>
       </c>
       <c r="DJ4" s="1"/>
-      <c r="DK4" s="32" t="s">
-        <v>1353</v>
+      <c r="DK4" s="24" t="s">
+        <v>1855</v>
       </c>
       <c r="DL4" s="1"/>
-      <c r="DM4" s="24" t="s">
-        <v>1859</v>
+      <c r="DM4" s="34" t="s">
+        <v>1901</v>
       </c>
       <c r="DN4" s="1"/>
       <c r="DO4" s="24" t="s">
-        <v>1860</v>
+        <v>1900</v>
       </c>
       <c r="DP4" s="1"/>
       <c r="DQ4" s="1" t="s">
-        <v>1885</v>
+        <v>1880</v>
       </c>
       <c r="DR4" s="1"/>
       <c r="DS4" s="1" t="s">
-        <v>1886</v>
+        <v>1881</v>
       </c>
       <c r="DT4" s="1"/>
       <c r="DU4" s="1" t="s">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="5" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+        <v>1882</v>
+      </c>
+      <c r="DW4" s="1" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="5" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>11</v>
       </c>
@@ -6985,15 +6993,15 @@
         <v>1371</v>
       </c>
       <c r="BK5" s="9" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="BL5" s="9"/>
       <c r="BM5" s="9" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="BN5" s="9"/>
       <c r="BO5" s="9" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="BP5" s="9"/>
       <c r="BQ5" s="9" t="s">
@@ -7001,104 +7009,107 @@
       </c>
       <c r="BR5" s="9"/>
       <c r="BS5" s="9" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="BT5" s="9"/>
       <c r="BU5" s="9" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="BV5" s="9"/>
       <c r="BW5" s="9" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="BX5" s="9"/>
       <c r="BY5" s="9" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="BZ5" s="9"/>
       <c r="CA5" s="9" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="CB5" s="9"/>
       <c r="CC5" s="9" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="CD5" s="9"/>
       <c r="CE5" s="9" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="CG5" s="19" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="CI5" s="19" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="CK5" s="19" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="CM5" s="19" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="CO5" s="19" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="CQ5" s="19" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="CS5" s="27" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="CT5" s="27"/>
       <c r="CU5" s="27" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="CV5" s="27"/>
       <c r="CW5" s="27" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="CX5" s="27"/>
       <c r="CY5" s="28" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="CZ5" s="28"/>
       <c r="DA5" s="28" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="DB5" s="28"/>
       <c r="DC5" s="28" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="DD5" s="28"/>
       <c r="DE5" s="28" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="DF5" s="28"/>
       <c r="DG5" s="9" t="s">
-        <v>1861</v>
-      </c>
-      <c r="DI5" s="33" t="s">
-        <v>1862</v>
+        <v>1857</v>
+      </c>
+      <c r="DI5" s="9" t="s">
+        <v>1859</v>
       </c>
       <c r="DK5" s="9" t="s">
-        <v>1863</v>
-      </c>
-      <c r="DM5" s="9" t="s">
-        <v>1864</v>
+        <v>1860</v>
+      </c>
+      <c r="DM5" t="s">
+        <v>1902</v>
       </c>
       <c r="DO5" s="9" t="s">
-        <v>1861</v>
+        <v>1857</v>
       </c>
       <c r="DQ5" t="s">
-        <v>1888</v>
-      </c>
-      <c r="DS5" s="36" t="s">
-        <v>1894</v>
-      </c>
-      <c r="DU5" s="36" t="s">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="6" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+        <v>1883</v>
+      </c>
+      <c r="DS5" s="32" t="s">
+        <v>1889</v>
+      </c>
+      <c r="DU5" s="32" t="s">
+        <v>1895</v>
+      </c>
+      <c r="DW5" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="6" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="20" t="s">
         <v>21</v>
       </c>
@@ -7203,15 +7214,15 @@
         <v>1377</v>
       </c>
       <c r="BK6" s="9" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="BL6" s="9"/>
       <c r="BM6" s="9" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="BN6" s="9"/>
       <c r="BO6" s="9" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="BP6" s="9"/>
       <c r="BQ6" s="9" t="s">
@@ -7219,102 +7230,105 @@
       </c>
       <c r="BR6" s="9"/>
       <c r="BS6" s="9" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="BT6" s="9"/>
       <c r="BU6" s="9" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="BV6" s="9"/>
       <c r="BW6" s="9" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="BX6" s="9"/>
       <c r="BY6" s="9" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="BZ6" s="9"/>
       <c r="CA6" s="9" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="CB6" s="9"/>
       <c r="CC6" s="9" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="CD6" s="9"/>
       <c r="CE6" s="9" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="CG6" s="19" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="CI6" s="19" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="CK6" s="19" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="CM6" s="19" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="CO6" s="19" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="CQ6" s="19" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="CS6" s="28" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="CT6" s="28"/>
       <c r="CU6" s="27" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="CV6" s="27"/>
       <c r="CW6" s="27"/>
       <c r="CX6" s="27"/>
       <c r="CY6" s="28" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="CZ6" s="28"/>
       <c r="DA6" s="28" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="DB6" s="28"/>
       <c r="DC6" s="28" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="DD6" s="28"/>
       <c r="DE6" s="28" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="DF6" s="28"/>
       <c r="DG6" s="9" t="s">
-        <v>1865</v>
-      </c>
-      <c r="DI6" s="33" t="s">
-        <v>1866</v>
+        <v>1861</v>
+      </c>
+      <c r="DI6" s="9" t="s">
+        <v>1862</v>
       </c>
       <c r="DK6" s="9" t="s">
-        <v>1867</v>
-      </c>
-      <c r="DM6" s="9" t="s">
-        <v>1868</v>
+        <v>1863</v>
+      </c>
+      <c r="DM6" t="s">
+        <v>1903</v>
       </c>
       <c r="DO6" s="9" t="s">
-        <v>1865</v>
+        <v>1861</v>
       </c>
       <c r="DQ6" t="s">
-        <v>1889</v>
-      </c>
-      <c r="DS6" s="36" t="s">
-        <v>1895</v>
-      </c>
-      <c r="DU6" s="36" t="s">
-        <v>1901</v>
-      </c>
-    </row>
-    <row r="7" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+        <v>1884</v>
+      </c>
+      <c r="DS6" s="32" t="s">
+        <v>1890</v>
+      </c>
+      <c r="DU6" s="32" t="s">
+        <v>1896</v>
+      </c>
+      <c r="DW6" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="7" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>29</v>
       </c>
@@ -7413,15 +7427,15 @@
         <v>1383</v>
       </c>
       <c r="BK7" s="9" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="BL7" s="9"/>
       <c r="BM7" s="9" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="BN7" s="9"/>
       <c r="BO7" s="9" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="BP7" s="9"/>
       <c r="BQ7" s="9" t="s">
@@ -7429,99 +7443,99 @@
       </c>
       <c r="BR7" s="9"/>
       <c r="BS7" s="9" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="BT7" s="9"/>
       <c r="BU7" s="9" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="BV7" s="9"/>
       <c r="BW7" s="9" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="BX7" s="9"/>
       <c r="BY7" s="9" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="BZ7" s="9"/>
       <c r="CA7" s="9" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="CB7" s="9"/>
       <c r="CC7" s="9" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="CD7" s="9"/>
       <c r="CE7" s="9" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="CG7" s="19" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="CI7" s="19" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="CK7" s="19" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="CM7" s="19" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="CO7" s="19" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="CQ7" s="19" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="CS7" s="28" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="CT7" s="28"/>
       <c r="CU7" s="27" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="CV7" s="27"/>
       <c r="CW7" s="27"/>
       <c r="CX7" s="27"/>
       <c r="CY7" s="28" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="CZ7" s="28"/>
       <c r="DA7" s="28" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="DB7" s="28"/>
       <c r="DC7" s="28" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="DD7" s="28"/>
       <c r="DE7" s="28" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="DF7" s="28"/>
       <c r="DG7" s="9" t="s">
-        <v>1869</v>
-      </c>
-      <c r="DI7" s="33" t="s">
-        <v>665</v>
-      </c>
-      <c r="DM7" s="9" t="s">
-        <v>1870</v>
+        <v>1864</v>
+      </c>
+      <c r="DK7" s="9" t="s">
+        <v>1865</v>
       </c>
       <c r="DO7" s="9" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="DQ7" t="s">
-        <v>1890</v>
-      </c>
-      <c r="DS7" s="36" t="s">
-        <v>1896</v>
-      </c>
-      <c r="DU7" s="36" t="s">
-        <v>1902</v>
-      </c>
-    </row>
-    <row r="8" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+        <v>1885</v>
+      </c>
+      <c r="DS7" s="32" t="s">
+        <v>1891</v>
+      </c>
+      <c r="DU7" s="32" t="s">
+        <v>1897</v>
+      </c>
+      <c r="DW7" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="8" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="20" t="s">
         <v>36</v>
       </c>
@@ -7610,15 +7624,15 @@
         <v>1387</v>
       </c>
       <c r="BK8" s="9" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="BL8" s="9"/>
       <c r="BM8" s="9" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="BN8" s="9"/>
       <c r="BO8" s="9" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="BP8" s="9"/>
       <c r="BQ8" s="9" t="s">
@@ -7626,19 +7640,19 @@
       </c>
       <c r="BR8" s="9"/>
       <c r="BS8" s="9" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="BT8" s="9"/>
       <c r="BU8" s="9" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="BV8" s="9"/>
       <c r="BW8" s="9" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="BX8" s="9"/>
       <c r="BY8" s="9" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="BZ8" s="9"/>
       <c r="CA8" s="9" t="s">
@@ -7646,76 +7660,79 @@
       </c>
       <c r="CB8" s="9"/>
       <c r="CC8" s="9" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="CD8" s="9"/>
       <c r="CE8" s="9" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="CG8" s="19" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="CI8" s="19" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="CK8" s="19" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="CM8" s="19" t="s">
         <v>1371</v>
       </c>
       <c r="CO8" s="19" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="CQ8" s="19" t="s">
         <v>737</v>
       </c>
       <c r="CS8" s="28" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="CT8" s="28"/>
       <c r="CU8" s="27" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="CV8" s="27"/>
       <c r="CW8" s="27"/>
       <c r="CX8" s="27"/>
       <c r="CY8" s="28" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="CZ8" s="28"/>
       <c r="DA8" s="28" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="DB8" s="28"/>
       <c r="DC8" s="28" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="DD8" s="28"/>
       <c r="DE8" s="28" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="DF8" s="27"/>
       <c r="DG8" s="9" t="s">
-        <v>1871</v>
-      </c>
-      <c r="DM8" s="9" t="s">
-        <v>1872</v>
+        <v>1866</v>
+      </c>
+      <c r="DK8" s="9" t="s">
+        <v>1867</v>
       </c>
       <c r="DO8" s="9" t="s">
-        <v>1871</v>
+        <v>1866</v>
       </c>
       <c r="DQ8" t="s">
-        <v>1891</v>
-      </c>
-      <c r="DS8" s="36" t="s">
-        <v>1897</v>
-      </c>
-      <c r="DU8" s="36" t="s">
-        <v>1903</v>
-      </c>
-    </row>
-    <row r="9" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+        <v>1886</v>
+      </c>
+      <c r="DS8" s="32" t="s">
+        <v>1892</v>
+      </c>
+      <c r="DU8" s="32" t="s">
+        <v>1898</v>
+      </c>
+      <c r="DW8" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="9" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>42</v>
       </c>
@@ -7797,15 +7814,15 @@
         <v>1391</v>
       </c>
       <c r="BK9" s="9" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="BL9" s="9"/>
       <c r="BM9" s="9" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="BN9" s="9"/>
       <c r="BO9" s="9" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="BP9" s="9"/>
       <c r="BQ9" s="9" t="s">
@@ -7813,15 +7830,15 @@
       </c>
       <c r="BR9" s="9"/>
       <c r="BS9" s="9" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="BT9" s="9"/>
       <c r="BU9" s="9" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="BV9" s="9"/>
       <c r="BW9" s="9" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="BX9" s="9"/>
       <c r="BY9" s="9"/>
@@ -7831,73 +7848,76 @@
       </c>
       <c r="CB9" s="9"/>
       <c r="CC9" s="9" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="CD9" s="9"/>
       <c r="CE9" s="9" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="CG9" s="19" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="CI9" s="19" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="CK9" s="19" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="CM9" s="19" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="CO9" s="19" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="CS9" s="28" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="CT9" s="28"/>
       <c r="CU9" s="27" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="CV9" s="27"/>
       <c r="CW9" s="27"/>
       <c r="CX9" s="27"/>
       <c r="CY9" s="28" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="CZ9" s="28"/>
       <c r="DA9" s="28" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="DB9" s="28"/>
       <c r="DC9" s="28" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="DD9" s="28"/>
       <c r="DE9" s="28" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="DF9" s="27"/>
       <c r="DG9" s="9" t="s">
-        <v>1873</v>
-      </c>
-      <c r="DM9" s="9" t="s">
-        <v>1874</v>
+        <v>1868</v>
+      </c>
+      <c r="DK9" s="9" t="s">
+        <v>1869</v>
       </c>
       <c r="DO9" s="9" t="s">
-        <v>1873</v>
+        <v>1868</v>
       </c>
       <c r="DQ9" t="s">
-        <v>1892</v>
-      </c>
-      <c r="DS9" s="36" t="s">
-        <v>1898</v>
-      </c>
-      <c r="DU9" s="36" t="s">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="10" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+        <v>1887</v>
+      </c>
+      <c r="DS9" s="32" t="s">
+        <v>1893</v>
+      </c>
+      <c r="DU9" s="32" t="s">
+        <v>1899</v>
+      </c>
+      <c r="DW9" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="10" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A10" s="20" t="s">
         <v>48</v>
       </c>
@@ -7982,15 +8002,15 @@
         <v>1394</v>
       </c>
       <c r="BK10" s="9" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="BL10" s="9"/>
       <c r="BM10" s="9" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="BN10" s="9"/>
       <c r="BO10" s="9" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="BP10" s="9"/>
       <c r="BQ10" s="9" t="s">
@@ -8002,7 +8022,7 @@
       <c r="BU10" s="9"/>
       <c r="BV10" s="9"/>
       <c r="BW10" s="9" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="BX10" s="9"/>
       <c r="BY10" s="9"/>
@@ -8019,19 +8039,19 @@
         <v>693</v>
       </c>
       <c r="CG10" s="19" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="CI10" s="19" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="CK10" s="19" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="CM10" s="19" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="CO10" s="19" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="CS10" s="27"/>
       <c r="CT10" s="27"/>
@@ -8040,32 +8060,35 @@
       <c r="CW10" s="27"/>
       <c r="CX10" s="27"/>
       <c r="CY10" s="28" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="CZ10" s="28"/>
       <c r="DA10" s="28" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="DB10" s="28"/>
       <c r="DC10" s="28" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="DD10" s="28"/>
       <c r="DE10" s="28" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="DF10" s="27"/>
-      <c r="DM10" s="9" t="s">
-        <v>1875</v>
+      <c r="DK10" s="9" t="s">
+        <v>1870</v>
+      </c>
+      <c r="DO10" s="9" t="s">
+        <v>665</v>
       </c>
       <c r="DQ10" t="s">
-        <v>1893</v>
-      </c>
-      <c r="DS10" s="36" t="s">
-        <v>1899</v>
-      </c>
-    </row>
-    <row r="11" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+        <v>1888</v>
+      </c>
+      <c r="DS10" s="32" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="11" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>54</v>
       </c>
@@ -8136,11 +8159,11 @@
         <v>1398</v>
       </c>
       <c r="BK11" s="9" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="BL11" s="9"/>
       <c r="BM11" s="9" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="BN11" s="9"/>
       <c r="BO11" s="9"/>
@@ -8154,7 +8177,7 @@
       <c r="BU11" s="9"/>
       <c r="BV11" s="9"/>
       <c r="BW11" s="9" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="BX11" s="9"/>
       <c r="BY11" s="9"/>
@@ -8166,19 +8189,19 @@
       <c r="CC11" s="9"/>
       <c r="CD11" s="9"/>
       <c r="CE11" s="9" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="CG11" s="19" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="CI11" s="19" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="CM11" s="19" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="CO11" s="19" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="CS11" s="27"/>
       <c r="CT11" s="27"/>
@@ -8187,26 +8210,29 @@
       <c r="CW11" s="27"/>
       <c r="CX11" s="27"/>
       <c r="CY11" s="28" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="CZ11" s="28"/>
       <c r="DA11" s="28" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="DB11" s="28"/>
       <c r="DC11" s="28" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="DD11" s="28"/>
       <c r="DE11" s="28" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="DF11" s="27"/>
-      <c r="DM11" s="9" t="s">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="12" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+      <c r="DK11" s="9" t="s">
+        <v>1871</v>
+      </c>
+      <c r="DO11" s="9" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="12" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="20" t="s">
         <v>60</v>
       </c>
@@ -8289,7 +8315,7 @@
       <c r="BU12" s="9"/>
       <c r="BV12" s="9"/>
       <c r="BW12" s="9" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="BX12" s="9"/>
       <c r="BY12" s="9"/>
@@ -8302,13 +8328,13 @@
       <c r="CD12" s="9"/>
       <c r="CE12" s="9"/>
       <c r="CG12" s="19" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="CI12" s="19" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="CO12" s="19" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="CS12" s="27"/>
       <c r="CT12" s="27"/>
@@ -8317,26 +8343,26 @@
       <c r="CW12" s="27"/>
       <c r="CX12" s="27"/>
       <c r="CY12" s="28" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="CZ12" s="28"/>
       <c r="DA12" s="28" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="DB12" s="28"/>
       <c r="DC12" s="28" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="DD12" s="28"/>
       <c r="DE12" s="28" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="DF12" s="27"/>
-      <c r="DM12" s="9" t="s">
-        <v>1877</v>
-      </c>
-    </row>
-    <row r="13" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+      <c r="DK12" s="9" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="13" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>66</v>
       </c>
@@ -8415,7 +8441,7 @@
       <c r="BU13" s="9"/>
       <c r="BV13" s="9"/>
       <c r="BW13" s="9" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="BX13" s="9"/>
       <c r="BY13" s="9"/>
@@ -8428,13 +8454,13 @@
       <c r="CD13" s="9"/>
       <c r="CE13" s="9"/>
       <c r="CG13" s="19" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="CI13" s="19" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="CO13" s="19" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="CS13" s="27"/>
       <c r="CT13" s="27"/>
@@ -8443,26 +8469,26 @@
       <c r="CW13" s="27"/>
       <c r="CX13" s="27"/>
       <c r="CY13" s="28" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="CZ13" s="28"/>
       <c r="DA13" s="28" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="DB13" s="28"/>
       <c r="DC13" s="28" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="DD13" s="28"/>
       <c r="DE13" s="28" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="DF13" s="27"/>
-      <c r="DM13" s="9" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="14" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+      <c r="DK13" s="9" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="14" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="20" t="s">
         <v>71</v>
       </c>
@@ -8543,7 +8569,7 @@
       <c r="BU14" s="9"/>
       <c r="BV14" s="9"/>
       <c r="BW14" s="9" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="BX14" s="9"/>
       <c r="BY14" s="9"/>
@@ -8556,10 +8582,10 @@
       <c r="CD14" s="9"/>
       <c r="CE14" s="9"/>
       <c r="CG14" s="19" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="CI14" s="19" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="CO14" s="19" t="s">
         <v>737</v>
@@ -8571,26 +8597,26 @@
       <c r="CW14" s="27"/>
       <c r="CX14" s="27"/>
       <c r="CY14" s="28" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="CZ14" s="28"/>
       <c r="DA14" s="28" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="DB14" s="28"/>
       <c r="DC14" s="28" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="DD14" s="28"/>
       <c r="DE14" s="28" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="DF14" s="27"/>
-      <c r="DM14" s="9" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="15" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+      <c r="DK14" s="9" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="15" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>76</v>
       </c>
@@ -8672,7 +8698,7 @@
       <c r="BU15" s="9"/>
       <c r="BV15" s="9"/>
       <c r="BW15" s="9" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="BX15" s="9"/>
       <c r="BY15" s="9"/>
@@ -8685,10 +8711,10 @@
       <c r="CD15" s="9"/>
       <c r="CE15" s="9"/>
       <c r="CG15" s="19" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="CI15" s="19" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="CS15" s="27"/>
       <c r="CT15" s="27"/>
@@ -8697,26 +8723,26 @@
       <c r="CW15" s="27"/>
       <c r="CX15" s="27"/>
       <c r="CY15" s="28" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="CZ15" s="28"/>
       <c r="DA15" s="28" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="DB15" s="28"/>
       <c r="DC15" s="28" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="DD15" s="28"/>
       <c r="DE15" s="28" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="DF15" s="27"/>
-      <c r="DM15" s="9" t="s">
-        <v>1880</v>
-      </c>
-    </row>
-    <row r="16" spans="1:125" ht="16" x14ac:dyDescent="0.4">
+      <c r="DK15" s="9" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:127" ht="16" x14ac:dyDescent="0.4">
       <c r="A16" s="20" t="s">
         <v>81</v>
       </c>
@@ -8795,7 +8821,7 @@
       <c r="BU16" s="9"/>
       <c r="BV16" s="9"/>
       <c r="BW16" s="9" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="BX16" s="9"/>
       <c r="BY16" s="9"/>
@@ -8808,7 +8834,7 @@
       <c r="CD16" s="9"/>
       <c r="CE16" s="9"/>
       <c r="CG16" s="19" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="CS16" s="27"/>
       <c r="CT16" s="27"/>
@@ -8817,26 +8843,26 @@
       <c r="CW16" s="27"/>
       <c r="CX16" s="27"/>
       <c r="CY16" s="28" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="CZ16" s="28"/>
       <c r="DA16" s="28" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="DB16" s="28"/>
       <c r="DC16" s="28" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="DD16" s="28"/>
       <c r="DE16" s="28" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="DF16" s="27"/>
-      <c r="DM16" s="9" t="s">
-        <v>1881</v>
-      </c>
-    </row>
-    <row r="17" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+      <c r="DK16" s="9" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="17" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>86</v>
       </c>
@@ -8917,7 +8943,7 @@
       <c r="BU17" s="9"/>
       <c r="BV17" s="9"/>
       <c r="BW17" s="9" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="BX17" s="9"/>
       <c r="BY17" s="9"/>
@@ -8928,7 +8954,7 @@
       <c r="CD17" s="9"/>
       <c r="CE17" s="9"/>
       <c r="CG17" s="19" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="CS17" s="27"/>
       <c r="CT17" s="27"/>
@@ -8937,26 +8963,26 @@
       <c r="CW17" s="27"/>
       <c r="CX17" s="27"/>
       <c r="CY17" s="28" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="CZ17" s="28"/>
       <c r="DA17" s="28" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="DB17" s="28"/>
       <c r="DC17" s="28" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="DD17" s="28"/>
       <c r="DE17" s="28" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="DF17" s="27"/>
-      <c r="DM17" s="9" t="s">
-        <v>1882</v>
-      </c>
-    </row>
-    <row r="18" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+      <c r="DK17" s="9" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="18" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A18" s="20" t="s">
         <v>91</v>
       </c>
@@ -9036,7 +9062,7 @@
       <c r="BU18" s="9"/>
       <c r="BV18" s="9"/>
       <c r="BW18" s="9" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="BX18" s="9"/>
       <c r="BY18" s="9"/>
@@ -9047,7 +9073,7 @@
       <c r="CD18" s="9"/>
       <c r="CE18" s="9"/>
       <c r="CG18" s="19" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="CS18" s="27"/>
       <c r="CT18" s="27"/>
@@ -9056,26 +9082,26 @@
       <c r="CW18" s="27"/>
       <c r="CX18" s="27"/>
       <c r="CY18" s="28" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="CZ18" s="28"/>
       <c r="DA18" s="28" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="DB18" s="28"/>
       <c r="DC18" s="28" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="DD18" s="28"/>
       <c r="DE18" s="28" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="DF18" s="27"/>
-      <c r="DM18" s="9" t="s">
-        <v>1883</v>
-      </c>
-    </row>
-    <row r="19" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+      <c r="DK18" s="9" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="19" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>96</v>
       </c>
@@ -9155,7 +9181,7 @@
       <c r="BU19" s="9"/>
       <c r="BV19" s="9"/>
       <c r="BW19" s="9" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="BX19" s="9"/>
       <c r="BY19" s="9"/>
@@ -9166,7 +9192,7 @@
       <c r="CD19" s="9"/>
       <c r="CE19" s="9"/>
       <c r="CG19" s="19" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="CS19" s="27"/>
       <c r="CT19" s="27"/>
@@ -9175,26 +9201,26 @@
       <c r="CW19" s="27"/>
       <c r="CX19" s="27"/>
       <c r="CY19" s="28" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="CZ19" s="28"/>
       <c r="DA19" s="28" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="DB19" s="28"/>
       <c r="DC19" s="28" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="DD19" s="28"/>
       <c r="DE19" s="28" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="DF19" s="27"/>
-      <c r="DM19" s="9" t="s">
-        <v>1884</v>
-      </c>
-    </row>
-    <row r="20" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+      <c r="DK19" s="9" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="20" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A20" s="20" t="s">
         <v>100</v>
       </c>
@@ -9270,7 +9296,7 @@
       <c r="BU20" s="9"/>
       <c r="BV20" s="9"/>
       <c r="BW20" s="9" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="BX20" s="9"/>
       <c r="BY20" s="9"/>
@@ -9281,7 +9307,7 @@
       <c r="CD20" s="9"/>
       <c r="CE20" s="9"/>
       <c r="CG20" s="19" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="CS20" s="27"/>
       <c r="CT20" s="27"/>
@@ -9290,23 +9316,23 @@
       <c r="CW20" s="27"/>
       <c r="CX20" s="27"/>
       <c r="CY20" s="28" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="CZ20" s="28"/>
       <c r="DA20" s="28" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="DB20" s="28"/>
       <c r="DC20" s="28" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="DD20" s="28"/>
       <c r="DE20" s="28" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="DF20" s="27"/>
     </row>
-    <row r="21" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>105</v>
       </c>
@@ -9382,7 +9408,7 @@
       <c r="BU21" s="9"/>
       <c r="BV21" s="9"/>
       <c r="BW21" s="9" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="BX21" s="9"/>
       <c r="BY21" s="9"/>
@@ -9393,7 +9419,7 @@
       <c r="CD21" s="9"/>
       <c r="CE21" s="9"/>
       <c r="CG21" s="19" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="CS21" s="27"/>
       <c r="CT21" s="27"/>
@@ -9402,23 +9428,23 @@
       <c r="CW21" s="27"/>
       <c r="CX21" s="27"/>
       <c r="CY21" s="28" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="CZ21" s="28"/>
       <c r="DA21" s="28" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="DB21" s="28"/>
       <c r="DC21" s="28" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="DD21" s="28"/>
       <c r="DE21" s="28" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="DF21" s="27"/>
     </row>
-    <row r="22" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="20" t="s">
         <v>109</v>
       </c>
@@ -9490,7 +9516,7 @@
       <c r="BU22" s="9"/>
       <c r="BV22" s="9"/>
       <c r="BW22" s="9" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="BX22" s="9"/>
       <c r="BY22" s="9"/>
@@ -9507,23 +9533,23 @@
       <c r="CW22" s="27"/>
       <c r="CX22" s="27"/>
       <c r="CY22" s="28" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="CZ22" s="28"/>
       <c r="DA22" s="28" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="DB22" s="28"/>
       <c r="DC22" s="28" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="DD22" s="28"/>
       <c r="DE22" s="28" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="DF22" s="27"/>
     </row>
-    <row r="23" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>113</v>
       </c>
@@ -9587,7 +9613,7 @@
       <c r="BU23" s="9"/>
       <c r="BV23" s="9"/>
       <c r="BW23" s="9" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="BX23" s="9"/>
       <c r="BY23" s="9"/>
@@ -9604,23 +9630,23 @@
       <c r="CW23" s="27"/>
       <c r="CX23" s="27"/>
       <c r="CY23" s="28" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="CZ23" s="28"/>
       <c r="DA23" s="28" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="DB23" s="28"/>
       <c r="DC23" s="28" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="DD23" s="28"/>
       <c r="DE23" s="28" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="DF23" s="27"/>
     </row>
-    <row r="24" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A24" s="20" t="s">
         <v>117</v>
       </c>
@@ -9680,7 +9706,7 @@
       <c r="BU24" s="9"/>
       <c r="BV24" s="9"/>
       <c r="BW24" s="9" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="BX24" s="9"/>
       <c r="BY24" s="9"/>
@@ -9697,23 +9723,23 @@
       <c r="CW24" s="27"/>
       <c r="CX24" s="27"/>
       <c r="CY24" s="28" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="CZ24" s="28"/>
       <c r="DA24" s="28" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="DB24" s="28"/>
       <c r="DC24" s="28" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="DD24" s="28"/>
       <c r="DE24" s="28" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="DF24" s="27"/>
     </row>
-    <row r="25" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A25" s="14" t="s">
         <v>121</v>
       </c>
@@ -9791,23 +9817,23 @@
       <c r="CW25" s="27"/>
       <c r="CX25" s="27"/>
       <c r="CY25" s="28" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="CZ25" s="28"/>
       <c r="DA25" s="28" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="DB25" s="28"/>
       <c r="DC25" s="28" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="DD25" s="28"/>
       <c r="DE25" s="28" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="DF25" s="27"/>
     </row>
-    <row r="26" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
         <v>125</v>
       </c>
@@ -9869,7 +9895,7 @@
       <c r="BU26" s="9"/>
       <c r="BV26" s="9"/>
       <c r="BW26" s="9" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="BX26" s="9"/>
       <c r="BY26" s="9"/>
@@ -9886,23 +9912,23 @@
       <c r="CW26" s="27"/>
       <c r="CX26" s="27"/>
       <c r="CY26" s="28" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="CZ26" s="28"/>
       <c r="DA26" s="28" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="DB26" s="28"/>
       <c r="DC26" s="28" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="DD26" s="28"/>
       <c r="DE26" s="28" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="DF26" s="27"/>
     </row>
-    <row r="27" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A27" s="14" t="s">
         <v>129</v>
       </c>
@@ -9962,7 +9988,7 @@
       <c r="BU27" s="9"/>
       <c r="BV27" s="9"/>
       <c r="BW27" s="9" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="BX27" s="9"/>
       <c r="BY27" s="9"/>
@@ -9979,23 +10005,23 @@
       <c r="CW27" s="27"/>
       <c r="CX27" s="27"/>
       <c r="CY27" s="28" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="CZ27" s="28"/>
       <c r="DA27" s="28" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="DB27" s="28"/>
       <c r="DC27" s="28" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="DD27" s="28"/>
       <c r="DE27" s="28" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="DF27" s="27"/>
     </row>
-    <row r="28" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A28" s="20" t="s">
         <v>133</v>
       </c>
@@ -10055,7 +10081,7 @@
       <c r="BU28" s="9"/>
       <c r="BV28" s="9"/>
       <c r="BW28" s="9" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="BX28" s="9"/>
       <c r="BY28" s="9"/>
@@ -10072,23 +10098,23 @@
       <c r="CW28" s="27"/>
       <c r="CX28" s="27"/>
       <c r="CY28" s="28" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="CZ28" s="28"/>
       <c r="DA28" s="28" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="DB28" s="28"/>
       <c r="DC28" s="28" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="DD28" s="28"/>
       <c r="DE28" s="28" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="DF28" s="27"/>
     </row>
-    <row r="29" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A29" s="14" t="s">
         <v>137</v>
       </c>
@@ -10147,7 +10173,7 @@
       <c r="BU29" s="9"/>
       <c r="BV29" s="9"/>
       <c r="BW29" s="9" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="BX29" s="9"/>
       <c r="BY29" s="9"/>
@@ -10164,23 +10190,23 @@
       <c r="CW29" s="27"/>
       <c r="CX29" s="27"/>
       <c r="CY29" s="28" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="CZ29" s="28"/>
       <c r="DA29" s="28" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="DB29" s="28"/>
       <c r="DC29" s="28" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="DD29" s="28"/>
       <c r="DE29" s="28" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="DF29" s="27"/>
     </row>
-    <row r="30" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A30" s="20" t="s">
         <v>141</v>
       </c>
@@ -10240,7 +10266,7 @@
       <c r="BU30" s="9"/>
       <c r="BV30" s="9"/>
       <c r="BW30" s="9" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="BX30" s="9"/>
       <c r="BY30" s="9"/>
@@ -10257,23 +10283,23 @@
       <c r="CW30" s="27"/>
       <c r="CX30" s="27"/>
       <c r="CY30" s="28" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="CZ30" s="28"/>
       <c r="DA30" s="28" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="DB30" s="28"/>
       <c r="DC30" s="28" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="DD30" s="28"/>
       <c r="DE30" s="28" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="DF30" s="27"/>
     </row>
-    <row r="31" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A31" s="14" t="s">
         <v>145</v>
       </c>
@@ -10334,7 +10360,7 @@
       <c r="BU31" s="9"/>
       <c r="BV31" s="9"/>
       <c r="BW31" s="9" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="BX31" s="9"/>
       <c r="BY31" s="9"/>
@@ -10351,23 +10377,23 @@
       <c r="CW31" s="27"/>
       <c r="CX31" s="27"/>
       <c r="CY31" s="28" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="CZ31" s="28"/>
       <c r="DA31" s="28" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="DB31" s="28"/>
       <c r="DC31" s="28" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="DD31" s="28"/>
       <c r="DE31" s="28" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="DF31" s="27"/>
     </row>
-    <row r="32" spans="1:117" ht="16" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:115" ht="16" x14ac:dyDescent="0.4">
       <c r="A32" s="20" t="s">
         <v>149</v>
       </c>
@@ -10400,7 +10426,7 @@
       </c>
       <c r="AH32" s="9"/>
       <c r="AI32" s="9" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="AK32" t="s">
         <v>778</v>
@@ -10427,7 +10453,7 @@
       <c r="BU32" s="9"/>
       <c r="BV32" s="9"/>
       <c r="BW32" s="9" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="BX32" s="9"/>
       <c r="BY32" s="9"/>
@@ -10444,19 +10470,19 @@
       <c r="CW32" s="27"/>
       <c r="CX32" s="27"/>
       <c r="CY32" s="28" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="CZ32" s="28"/>
       <c r="DA32" s="28" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="DB32" s="28"/>
       <c r="DC32" s="28" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="DD32" s="28"/>
       <c r="DE32" s="28" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="DF32" s="27"/>
     </row>
@@ -10493,7 +10519,7 @@
       </c>
       <c r="AH33" s="9"/>
       <c r="AI33" s="9" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="AK33" s="9" t="s">
         <v>781</v>
@@ -10520,7 +10546,7 @@
       <c r="BU33" s="9"/>
       <c r="BV33" s="9"/>
       <c r="BW33" s="9" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="BX33" s="9"/>
       <c r="BY33" s="9"/>
@@ -10537,19 +10563,19 @@
       <c r="CW33" s="27"/>
       <c r="CX33" s="27"/>
       <c r="CY33" s="28" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="CZ33" s="28"/>
       <c r="DA33" s="28" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="DB33" s="28"/>
       <c r="DC33" s="28" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="DD33" s="28"/>
       <c r="DE33" s="28" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="DF33" s="27"/>
     </row>
@@ -10586,7 +10612,7 @@
       </c>
       <c r="AH34" s="9"/>
       <c r="AI34" s="9" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="AK34" s="9" t="s">
         <v>784</v>
@@ -10614,7 +10640,7 @@
       <c r="BU34" s="9"/>
       <c r="BV34" s="9"/>
       <c r="BW34" s="9" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="BX34" s="9"/>
       <c r="BY34" s="9"/>
@@ -10631,19 +10657,19 @@
       <c r="CW34" s="27"/>
       <c r="CX34" s="27"/>
       <c r="CY34" s="28" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="CZ34" s="28"/>
       <c r="DA34" s="28" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="DB34" s="28"/>
       <c r="DC34" s="28" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="DD34" s="28"/>
       <c r="DE34" s="28" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="DF34" s="27"/>
     </row>
@@ -10680,7 +10706,7 @@
       </c>
       <c r="AH35" s="9"/>
       <c r="AI35" s="30" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="AK35" s="9" t="s">
         <v>787</v>
@@ -10708,7 +10734,7 @@
       <c r="BU35" s="9"/>
       <c r="BV35" s="9"/>
       <c r="BW35" s="9" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="BX35" s="9"/>
       <c r="BY35" s="9"/>
@@ -10725,19 +10751,19 @@
       <c r="CW35" s="27"/>
       <c r="CX35" s="27"/>
       <c r="CY35" s="28" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="CZ35" s="28"/>
       <c r="DA35" s="28" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="DB35" s="28"/>
       <c r="DC35" s="28" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="DD35" s="28"/>
       <c r="DE35" s="28" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="DF35" s="27"/>
     </row>
@@ -10770,7 +10796,7 @@
       </c>
       <c r="AH36" s="9"/>
       <c r="AI36" s="9" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="AK36" s="9" t="s">
         <v>791</v>
@@ -10798,7 +10824,7 @@
       <c r="BU36" s="9"/>
       <c r="BV36" s="9"/>
       <c r="BW36" s="9" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="BX36" s="9"/>
       <c r="BY36" s="9"/>
@@ -10815,19 +10841,19 @@
       <c r="CW36" s="27"/>
       <c r="CX36" s="27"/>
       <c r="CY36" s="28" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="CZ36" s="28"/>
       <c r="DA36" s="28" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="DB36" s="28"/>
       <c r="DC36" s="28" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="DD36" s="28"/>
       <c r="DE36" s="28" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="DF36" s="27"/>
     </row>
@@ -10860,7 +10886,7 @@
       </c>
       <c r="AH37" s="9"/>
       <c r="AI37" s="9" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="AK37" t="s">
         <v>794</v>
@@ -10886,7 +10912,7 @@
       <c r="BU37" s="9"/>
       <c r="BV37" s="9"/>
       <c r="BW37" s="9" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="BX37" s="9"/>
       <c r="BY37" s="9"/>
@@ -10903,19 +10929,19 @@
       <c r="CW37" s="27"/>
       <c r="CX37" s="27"/>
       <c r="CY37" s="28" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="CZ37" s="28"/>
       <c r="DA37" s="28" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="DB37" s="28"/>
       <c r="DC37" s="28" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="DD37" s="28"/>
       <c r="DE37" s="28" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="DF37" s="27"/>
     </row>
@@ -10948,7 +10974,7 @@
       </c>
       <c r="AH38" s="9"/>
       <c r="AI38" s="9" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="AK38" s="9" t="s">
         <v>797</v>
@@ -10976,7 +11002,7 @@
       <c r="BU38" s="9"/>
       <c r="BV38" s="9"/>
       <c r="BW38" s="9" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="BX38" s="9"/>
       <c r="BY38" s="9"/>
@@ -10993,19 +11019,19 @@
       <c r="CW38" s="27"/>
       <c r="CX38" s="27"/>
       <c r="CY38" s="28" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="CZ38" s="28"/>
       <c r="DA38" s="28" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="DB38" s="28"/>
       <c r="DC38" s="28" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="DD38" s="28"/>
       <c r="DE38" s="28" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="DF38" s="27"/>
     </row>
@@ -11038,7 +11064,7 @@
       </c>
       <c r="AH39" s="9"/>
       <c r="AI39" s="9" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="AK39" s="9" t="s">
         <v>801</v>
@@ -11065,7 +11091,7 @@
       <c r="BU39" s="9"/>
       <c r="BV39" s="9"/>
       <c r="BW39" s="9" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="BX39" s="9"/>
       <c r="BY39" s="9"/>
@@ -11082,19 +11108,19 @@
       <c r="CW39" s="27"/>
       <c r="CX39" s="27"/>
       <c r="CY39" s="28" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="CZ39" s="28"/>
       <c r="DA39" s="28" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="DB39" s="28"/>
       <c r="DC39" s="28" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="DD39" s="28"/>
       <c r="DE39" s="28" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="DF39" s="27"/>
     </row>
@@ -11127,7 +11153,7 @@
       </c>
       <c r="AH40" s="9"/>
       <c r="AI40" s="9" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="AM40" s="9" t="s">
         <v>781</v>
@@ -11151,7 +11177,7 @@
       <c r="BU40" s="9"/>
       <c r="BV40" s="9"/>
       <c r="BW40" s="9" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="BX40" s="9"/>
       <c r="BY40" s="9"/>
@@ -11168,19 +11194,19 @@
       <c r="CW40" s="27"/>
       <c r="CX40" s="27"/>
       <c r="CY40" s="28" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="CZ40" s="28"/>
       <c r="DA40" s="28" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="DB40" s="28"/>
       <c r="DC40" s="28" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="DD40" s="28"/>
       <c r="DE40" s="28" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="DF40" s="27"/>
     </row>
@@ -11213,7 +11239,7 @@
       </c>
       <c r="AH41" s="9"/>
       <c r="AI41" s="9" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="AM41" s="9" t="s">
         <v>806</v>
@@ -11237,7 +11263,7 @@
       <c r="BU41" s="9"/>
       <c r="BV41" s="9"/>
       <c r="BW41" s="9" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="BX41" s="9"/>
       <c r="BY41" s="9"/>
@@ -11254,19 +11280,19 @@
       <c r="CW41" s="27"/>
       <c r="CX41" s="27"/>
       <c r="CY41" s="28" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="CZ41" s="28"/>
       <c r="DA41" s="28" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="DB41" s="28"/>
       <c r="DC41" s="28" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="DD41" s="28"/>
       <c r="DE41" s="28" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="DF41" s="27"/>
     </row>
@@ -11299,7 +11325,7 @@
       </c>
       <c r="AH42" s="9"/>
       <c r="AI42" s="9" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="AM42" s="9" t="s">
         <v>784</v>
@@ -11323,7 +11349,7 @@
       <c r="BU42" s="9"/>
       <c r="BV42" s="9"/>
       <c r="BW42" s="9" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="BX42" s="9"/>
       <c r="BY42" s="9"/>
@@ -11340,19 +11366,19 @@
       <c r="CW42" s="27"/>
       <c r="CX42" s="27"/>
       <c r="CY42" s="28" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="CZ42" s="28"/>
       <c r="DA42" s="28" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="DB42" s="28"/>
       <c r="DC42" s="28" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="DD42" s="28"/>
       <c r="DE42" s="28" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="DF42" s="27"/>
     </row>
@@ -11385,7 +11411,7 @@
       </c>
       <c r="AH43" s="9"/>
       <c r="AI43" s="9" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="AM43" t="s">
         <v>811</v>
@@ -11408,7 +11434,7 @@
       <c r="BU43" s="9"/>
       <c r="BV43" s="9"/>
       <c r="BW43" s="9" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="BX43" s="9"/>
       <c r="BY43" s="9"/>
@@ -11425,19 +11451,19 @@
       <c r="CW43" s="27"/>
       <c r="CX43" s="27"/>
       <c r="CY43" s="28" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="CZ43" s="28"/>
       <c r="DA43" s="28" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="DB43" s="28"/>
       <c r="DC43" s="28" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="DD43" s="28"/>
       <c r="DE43" s="28" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="DF43" s="27"/>
     </row>
@@ -11470,7 +11496,7 @@
       </c>
       <c r="AH44" s="9"/>
       <c r="AI44" s="9" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="AM44" s="9" t="s">
         <v>787</v>
@@ -11494,7 +11520,7 @@
       <c r="BU44" s="9"/>
       <c r="BV44" s="9"/>
       <c r="BW44" s="9" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="BX44" s="9"/>
       <c r="BY44" s="9"/>
@@ -11511,19 +11537,19 @@
       <c r="CW44" s="27"/>
       <c r="CX44" s="27"/>
       <c r="CY44" s="28" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="CZ44" s="28"/>
       <c r="DA44" s="28" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="DB44" s="28"/>
       <c r="DC44" s="28" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="DD44" s="28"/>
       <c r="DE44" s="28" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="DF44" s="27"/>
     </row>
@@ -11556,7 +11582,7 @@
       </c>
       <c r="AH45" s="9"/>
       <c r="AI45" s="9" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="AM45" s="9" t="s">
         <v>791</v>
@@ -11580,7 +11606,7 @@
       <c r="BU45" s="9"/>
       <c r="BV45" s="9"/>
       <c r="BW45" s="9" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="BX45" s="9"/>
       <c r="BY45" s="9"/>
@@ -11597,19 +11623,19 @@
       <c r="CW45" s="27"/>
       <c r="CX45" s="27"/>
       <c r="CY45" s="28" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="CZ45" s="28"/>
       <c r="DA45" s="28" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="DB45" s="28"/>
       <c r="DC45" s="28" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="DD45" s="28"/>
       <c r="DE45" s="28" t="s">
-        <v>1767</v>
+        <v>1765</v>
       </c>
       <c r="DF45" s="27"/>
     </row>
@@ -11642,7 +11668,7 @@
       </c>
       <c r="AH46" s="9"/>
       <c r="AI46" s="9" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="AM46" t="s">
         <v>818</v>
@@ -11665,7 +11691,7 @@
       <c r="BU46" s="9"/>
       <c r="BV46" s="9"/>
       <c r="BW46" s="9" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="BX46" s="9"/>
       <c r="BY46" s="9"/>
@@ -11682,19 +11708,19 @@
       <c r="CW46" s="27"/>
       <c r="CX46" s="27"/>
       <c r="CY46" s="28" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="CZ46" s="28"/>
       <c r="DA46" s="28" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="DB46" s="28"/>
       <c r="DC46" s="28" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="DD46" s="28"/>
       <c r="DE46" s="28" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="DF46" s="27"/>
     </row>
@@ -11727,7 +11753,7 @@
       </c>
       <c r="AH47" s="9"/>
       <c r="AI47" s="9" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="AM47" s="9" t="s">
         <v>801</v>
@@ -11751,7 +11777,7 @@
       <c r="BU47" s="9"/>
       <c r="BV47" s="9"/>
       <c r="BW47" s="9" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="BX47" s="9"/>
       <c r="BY47" s="9"/>
@@ -11768,19 +11794,19 @@
       <c r="CW47" s="27"/>
       <c r="CX47" s="27"/>
       <c r="CY47" s="28" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="CZ47" s="28"/>
       <c r="DA47" s="28" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="DB47" s="28"/>
       <c r="DC47" s="28" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="DD47" s="28"/>
       <c r="DE47" s="28" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="DF47" s="27"/>
     </row>
@@ -11813,7 +11839,7 @@
       </c>
       <c r="AH48" s="9"/>
       <c r="AI48" s="9" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="AQ48" s="9" t="s">
         <v>823</v>
@@ -11833,7 +11859,7 @@
       <c r="BU48" s="9"/>
       <c r="BV48" s="9"/>
       <c r="BW48" s="9" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="BX48" s="9"/>
       <c r="BY48" s="9"/>
@@ -11850,19 +11876,19 @@
       <c r="CW48" s="27"/>
       <c r="CX48" s="27"/>
       <c r="CY48" s="28" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="CZ48" s="28"/>
       <c r="DA48" s="28" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="DB48" s="28"/>
       <c r="DC48" s="28" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="DD48" s="28"/>
       <c r="DE48" s="28" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="DF48" s="27"/>
     </row>
@@ -11895,7 +11921,7 @@
       </c>
       <c r="AH49" s="9"/>
       <c r="AI49" s="9" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="AQ49" s="9" t="s">
         <v>825</v>
@@ -11915,7 +11941,7 @@
       <c r="BU49" s="9"/>
       <c r="BV49" s="9"/>
       <c r="BW49" s="9" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="BX49" s="9"/>
       <c r="BY49" s="9"/>
@@ -11955,7 +11981,7 @@
       </c>
       <c r="AH50" s="9"/>
       <c r="AI50" s="9" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="AQ50" s="9" t="s">
         <v>827</v>
@@ -11975,7 +12001,7 @@
       <c r="BU50" s="9"/>
       <c r="BV50" s="9"/>
       <c r="BW50" s="9" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="BX50" s="9"/>
       <c r="BY50" s="9"/>
@@ -12015,7 +12041,7 @@
       </c>
       <c r="AH51" s="9"/>
       <c r="AI51" s="9" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="AQ51" s="9" t="s">
         <v>829</v>
@@ -12035,7 +12061,7 @@
       <c r="BU51" s="9"/>
       <c r="BV51" s="9"/>
       <c r="BW51" s="9" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="BX51" s="9"/>
       <c r="BY51" s="9"/>
@@ -12075,7 +12101,7 @@
       </c>
       <c r="AH52" s="9"/>
       <c r="AI52" s="9" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="AQ52" s="9" t="s">
         <v>831</v>
@@ -12095,7 +12121,7 @@
       <c r="BU52" s="9"/>
       <c r="BV52" s="9"/>
       <c r="BW52" s="9" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="BX52" s="9"/>
       <c r="BY52" s="9"/>
@@ -12135,7 +12161,7 @@
       </c>
       <c r="AH53" s="9"/>
       <c r="AI53" s="9" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="AQ53" s="9" t="s">
         <v>833</v>
@@ -12155,7 +12181,7 @@
       <c r="BU53" s="9"/>
       <c r="BV53" s="9"/>
       <c r="BW53" s="9" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="BX53" s="9"/>
       <c r="BY53" s="9"/>
@@ -12195,7 +12221,7 @@
       </c>
       <c r="AH54" s="9"/>
       <c r="AI54" s="9" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="AQ54" s="9" t="s">
         <v>835</v>
@@ -12215,7 +12241,7 @@
       <c r="BU54" s="9"/>
       <c r="BV54" s="9"/>
       <c r="BW54" s="9" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="BX54" s="9"/>
       <c r="BY54" s="9"/>
@@ -12255,7 +12281,7 @@
       </c>
       <c r="AH55" s="9"/>
       <c r="AI55" s="9" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="AQ55" s="9" t="s">
         <v>837</v>
@@ -12275,7 +12301,7 @@
       <c r="BU55" s="9"/>
       <c r="BV55" s="9"/>
       <c r="BW55" s="9" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="BX55" s="9"/>
       <c r="BY55" s="9"/>
@@ -12315,7 +12341,7 @@
       </c>
       <c r="AH56" s="9"/>
       <c r="AI56" s="9" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="AQ56" s="9" t="s">
         <v>839</v>
@@ -12335,7 +12361,7 @@
       <c r="BU56" s="9"/>
       <c r="BV56" s="9"/>
       <c r="BW56" s="9" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="BX56" s="9"/>
       <c r="BY56" s="9"/>
@@ -12375,7 +12401,7 @@
       </c>
       <c r="AH57" s="9"/>
       <c r="AI57" s="9" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="AQ57" s="9" t="s">
         <v>841</v>
@@ -12395,7 +12421,7 @@
       <c r="BU57" s="9"/>
       <c r="BV57" s="9"/>
       <c r="BW57" s="9" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="BX57" s="9"/>
       <c r="BY57" s="9"/>
@@ -12435,7 +12461,7 @@
       </c>
       <c r="AH58" s="9"/>
       <c r="AI58" s="9" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="AQ58" s="9" t="s">
         <v>843</v>
@@ -12455,7 +12481,7 @@
       <c r="BU58" s="9"/>
       <c r="BV58" s="9"/>
       <c r="BW58" s="9" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="BX58" s="9"/>
       <c r="BY58" s="9"/>
@@ -12495,7 +12521,7 @@
       </c>
       <c r="AH59" s="9"/>
       <c r="AI59" s="9" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="AQ59" s="9" t="s">
         <v>845</v>
@@ -12515,7 +12541,7 @@
       <c r="BU59" s="9"/>
       <c r="BV59" s="9"/>
       <c r="BW59" s="9" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="BX59" s="9"/>
       <c r="BY59" s="9"/>
@@ -12555,7 +12581,7 @@
       </c>
       <c r="AH60" s="9"/>
       <c r="AI60" s="9" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="AQ60" s="9" t="s">
         <v>847</v>
@@ -12575,7 +12601,7 @@
       <c r="BU60" s="9"/>
       <c r="BV60" s="9"/>
       <c r="BW60" s="9" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="BX60" s="9"/>
       <c r="BY60" s="9"/>
@@ -12615,7 +12641,7 @@
       </c>
       <c r="AH61" s="9"/>
       <c r="AI61" s="9" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="AQ61" s="9" t="s">
         <v>849</v>
@@ -12635,7 +12661,7 @@
       <c r="BU61" s="9"/>
       <c r="BV61" s="9"/>
       <c r="BW61" s="9" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="BX61" s="9"/>
       <c r="BY61" s="9"/>
@@ -12675,7 +12701,7 @@
       </c>
       <c r="AH62" s="9"/>
       <c r="AI62" s="9" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="AQ62" s="9" t="s">
         <v>851</v>
@@ -12695,7 +12721,7 @@
       <c r="BU62" s="9"/>
       <c r="BV62" s="9"/>
       <c r="BW62" s="9" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="BX62" s="9"/>
       <c r="BY62" s="9"/>
@@ -12735,7 +12761,7 @@
       </c>
       <c r="AH63" s="9"/>
       <c r="AI63" s="9" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="AQ63" s="9" t="s">
         <v>853</v>
@@ -12755,7 +12781,7 @@
       <c r="BU63" s="9"/>
       <c r="BV63" s="9"/>
       <c r="BW63" s="9" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="BX63" s="9"/>
       <c r="BY63" s="9"/>
@@ -12795,7 +12821,7 @@
       </c>
       <c r="AH64" s="9"/>
       <c r="AI64" s="9" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="AQ64" s="9" t="s">
         <v>855</v>
@@ -12815,7 +12841,7 @@
       <c r="BU64" s="9"/>
       <c r="BV64" s="9"/>
       <c r="BW64" s="9" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="BX64" s="9"/>
       <c r="BY64" s="9"/>
@@ -12855,7 +12881,7 @@
       </c>
       <c r="AH65" s="9"/>
       <c r="AI65" s="9" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="AQ65" s="9" t="s">
         <v>857</v>
@@ -12875,7 +12901,7 @@
       <c r="BU65" s="9"/>
       <c r="BV65" s="9"/>
       <c r="BW65" s="9" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="BX65" s="9"/>
       <c r="BY65" s="9"/>
@@ -12915,7 +12941,7 @@
       </c>
       <c r="AH66" s="9"/>
       <c r="AI66" s="9" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="AQ66" s="9" t="s">
         <v>859</v>
@@ -12935,7 +12961,7 @@
       <c r="BU66" s="9"/>
       <c r="BV66" s="9"/>
       <c r="BW66" s="9" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="BX66" s="9"/>
       <c r="BY66" s="9"/>
@@ -12975,7 +13001,7 @@
       </c>
       <c r="AH67" s="9"/>
       <c r="AI67" s="9" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="AQ67" s="9" t="s">
         <v>861</v>
@@ -12995,7 +13021,7 @@
       <c r="BU67" s="9"/>
       <c r="BV67" s="9"/>
       <c r="BW67" s="9" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="BX67" s="9"/>
       <c r="BY67" s="9"/>
@@ -13035,7 +13061,7 @@
       </c>
       <c r="AH68" s="9"/>
       <c r="AI68" s="9" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="AQ68" s="9" t="s">
         <v>863</v>
@@ -13055,7 +13081,7 @@
       <c r="BU68" s="9"/>
       <c r="BV68" s="9"/>
       <c r="BW68" s="9" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="BX68" s="9"/>
       <c r="BY68" s="9"/>
@@ -13095,7 +13121,7 @@
       </c>
       <c r="AH69" s="9"/>
       <c r="AI69" s="9" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="AQ69" s="9" t="s">
         <v>865</v>
@@ -13115,7 +13141,7 @@
       <c r="BU69" s="9"/>
       <c r="BV69" s="9"/>
       <c r="BW69" s="9" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="BX69" s="9"/>
       <c r="BY69" s="9"/>
@@ -13155,7 +13181,7 @@
       </c>
       <c r="AH70" s="9"/>
       <c r="AI70" s="9" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="AQ70" s="9" t="s">
         <v>867</v>
@@ -13175,7 +13201,7 @@
       <c r="BU70" s="9"/>
       <c r="BV70" s="9"/>
       <c r="BW70" s="9" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="BX70" s="9"/>
       <c r="BY70" s="9"/>
@@ -13215,7 +13241,7 @@
       </c>
       <c r="AH71" s="9"/>
       <c r="AI71" s="9" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="AQ71" s="9" t="s">
         <v>869</v>
@@ -13235,7 +13261,7 @@
       <c r="BU71" s="9"/>
       <c r="BV71" s="9"/>
       <c r="BW71" s="9" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="BX71" s="9"/>
       <c r="BY71" s="9"/>
@@ -13275,7 +13301,7 @@
       </c>
       <c r="AH72" s="9"/>
       <c r="AI72" s="9" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="AQ72" s="9" t="s">
         <v>871</v>
@@ -13295,7 +13321,7 @@
       <c r="BU72" s="9"/>
       <c r="BV72" s="9"/>
       <c r="BW72" s="9" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="BX72" s="9"/>
       <c r="BY72" s="9"/>
@@ -13335,7 +13361,7 @@
       </c>
       <c r="AH73" s="9"/>
       <c r="AI73" s="9" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="AQ73" s="9" t="s">
         <v>873</v>
@@ -13355,7 +13381,7 @@
       <c r="BU73" s="9"/>
       <c r="BV73" s="9"/>
       <c r="BW73" s="9" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="BX73" s="9"/>
       <c r="BY73" s="9"/>
@@ -13395,7 +13421,7 @@
       </c>
       <c r="AH74" s="9"/>
       <c r="AI74" s="9" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="AQ74" s="9" t="s">
         <v>875</v>
@@ -13415,7 +13441,7 @@
       <c r="BU74" s="9"/>
       <c r="BV74" s="9"/>
       <c r="BW74" s="9" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="BX74" s="9"/>
       <c r="BY74" s="9"/>
@@ -13455,7 +13481,7 @@
       </c>
       <c r="AH75" s="9"/>
       <c r="AI75" s="9" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="AQ75" s="9" t="s">
         <v>877</v>
@@ -13475,7 +13501,7 @@
       <c r="BU75" s="9"/>
       <c r="BV75" s="9"/>
       <c r="BW75" s="9" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="BX75" s="9"/>
       <c r="BY75" s="9"/>
@@ -13515,7 +13541,7 @@
       </c>
       <c r="AH76" s="9"/>
       <c r="AI76" s="9" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="AQ76" s="9" t="s">
         <v>879</v>
@@ -13535,7 +13561,7 @@
       <c r="BU76" s="9"/>
       <c r="BV76" s="9"/>
       <c r="BW76" s="9" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="BX76" s="9"/>
       <c r="BY76" s="9"/>
@@ -13575,7 +13601,7 @@
       </c>
       <c r="AH77" s="9"/>
       <c r="AI77" s="9" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="AQ77" s="9" t="s">
         <v>881</v>
@@ -13595,7 +13621,7 @@
       <c r="BU77" s="9"/>
       <c r="BV77" s="9"/>
       <c r="BW77" s="9" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="BX77" s="9"/>
       <c r="BY77" s="9"/>
@@ -13635,7 +13661,7 @@
       </c>
       <c r="AH78" s="9"/>
       <c r="AI78" s="9" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="AQ78" s="9" t="s">
         <v>883</v>
@@ -13655,7 +13681,7 @@
       <c r="BU78" s="9"/>
       <c r="BV78" s="9"/>
       <c r="BW78" s="9" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="BX78" s="9"/>
       <c r="BY78" s="9"/>
@@ -13695,7 +13721,7 @@
       </c>
       <c r="AH79" s="9"/>
       <c r="AI79" s="9" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="AQ79" s="9" t="s">
         <v>885</v>
@@ -13715,7 +13741,7 @@
       <c r="BU79" s="9"/>
       <c r="BV79" s="9"/>
       <c r="BW79" s="9" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="BX79" s="9"/>
       <c r="BY79" s="9"/>
@@ -13755,7 +13781,7 @@
       </c>
       <c r="AH80" s="9"/>
       <c r="AI80" s="9" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AQ80" s="9" t="s">
         <v>887</v>
@@ -13775,7 +13801,7 @@
       <c r="BU80" s="9"/>
       <c r="BV80" s="9"/>
       <c r="BW80" s="9" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="BX80" s="9"/>
       <c r="BY80" s="9"/>
@@ -13815,7 +13841,7 @@
       </c>
       <c r="AH81" s="9"/>
       <c r="AI81" s="9" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="AQ81" s="9" t="s">
         <v>889</v>
@@ -13835,7 +13861,7 @@
       <c r="BU81" s="9"/>
       <c r="BV81" s="9"/>
       <c r="BW81" s="9" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="BX81" s="9"/>
       <c r="BY81" s="9"/>
@@ -13875,7 +13901,7 @@
       </c>
       <c r="AH82" s="9"/>
       <c r="AI82" s="9" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="AQ82" s="9" t="s">
         <v>891</v>
@@ -13895,7 +13921,7 @@
       <c r="BU82" s="9"/>
       <c r="BV82" s="9"/>
       <c r="BW82" s="9" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="BX82" s="9"/>
       <c r="BY82" s="9"/>
@@ -13935,7 +13961,7 @@
       </c>
       <c r="AH83" s="9"/>
       <c r="AI83" s="9" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="AQ83" s="9" t="s">
         <v>893</v>
@@ -13955,7 +13981,7 @@
       <c r="BU83" s="9"/>
       <c r="BV83" s="9"/>
       <c r="BW83" s="9" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="BX83" s="9"/>
       <c r="BY83" s="9"/>
@@ -13995,7 +14021,7 @@
       </c>
       <c r="AH84" s="9"/>
       <c r="AI84" s="9" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="AQ84" s="9" t="s">
         <v>895</v>
@@ -14015,7 +14041,7 @@
       <c r="BU84" s="9"/>
       <c r="BV84" s="9"/>
       <c r="BW84" s="9" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="BX84" s="9"/>
       <c r="BY84" s="9"/>
@@ -14055,7 +14081,7 @@
       </c>
       <c r="AH85" s="9"/>
       <c r="AI85" s="9" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="AQ85" s="9" t="s">
         <v>897</v>
@@ -14075,7 +14101,7 @@
       <c r="BU85" s="9"/>
       <c r="BV85" s="9"/>
       <c r="BW85" s="9" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="BX85" s="9"/>
       <c r="BY85" s="9"/>
@@ -14115,7 +14141,7 @@
       </c>
       <c r="AH86" s="9"/>
       <c r="AI86" s="9" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="AQ86" s="9" t="s">
         <v>899</v>
@@ -14135,7 +14161,7 @@
       <c r="BU86" s="9"/>
       <c r="BV86" s="9"/>
       <c r="BW86" s="9" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="BX86" s="9"/>
       <c r="BY86" s="9"/>
@@ -14175,7 +14201,7 @@
       </c>
       <c r="AH87" s="9"/>
       <c r="AI87" s="9" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="AQ87" s="9" t="s">
         <v>901</v>
@@ -14195,7 +14221,7 @@
       <c r="BU87" s="9"/>
       <c r="BV87" s="9"/>
       <c r="BW87" s="9" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="BX87" s="9"/>
       <c r="BY87" s="9"/>
@@ -14235,7 +14261,7 @@
       </c>
       <c r="AH88" s="9"/>
       <c r="AI88" s="9" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="AQ88" s="9" t="s">
         <v>903</v>
@@ -14255,7 +14281,7 @@
       <c r="BU88" s="9"/>
       <c r="BV88" s="9"/>
       <c r="BW88" s="9" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="BX88" s="9"/>
       <c r="BY88" s="9"/>
@@ -14295,7 +14321,7 @@
       </c>
       <c r="AH89" s="9"/>
       <c r="AI89" s="9" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="AQ89" s="9" t="s">
         <v>905</v>
@@ -14315,7 +14341,7 @@
       <c r="BU89" s="9"/>
       <c r="BV89" s="9"/>
       <c r="BW89" s="9" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="BX89" s="9"/>
       <c r="BY89" s="9"/>
@@ -14355,7 +14381,7 @@
       </c>
       <c r="AH90" s="9"/>
       <c r="AI90" s="9" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="AQ90" s="9" t="s">
         <v>907</v>
@@ -14375,7 +14401,7 @@
       <c r="BU90" s="9"/>
       <c r="BV90" s="9"/>
       <c r="BW90" s="9" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="BX90" s="9"/>
       <c r="BY90" s="9"/>
@@ -14415,7 +14441,7 @@
       </c>
       <c r="AH91" s="9"/>
       <c r="AI91" s="9" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="AQ91" s="9" t="s">
         <v>909</v>
@@ -14435,7 +14461,7 @@
       <c r="BU91" s="9"/>
       <c r="BV91" s="9"/>
       <c r="BW91" s="9" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="BX91" s="9"/>
       <c r="BY91" s="9"/>
@@ -14471,7 +14497,7 @@
       <c r="R92" s="12"/>
       <c r="S92" s="12"/>
       <c r="AI92" s="9" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="AQ92" s="9" t="s">
         <v>910</v>
@@ -14489,7 +14515,7 @@
       <c r="BU92" s="9"/>
       <c r="BV92" s="9"/>
       <c r="BW92" s="9" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="BX92" s="9"/>
       <c r="BY92" s="9"/>
@@ -14543,7 +14569,7 @@
       <c r="BU93" s="9"/>
       <c r="BV93" s="9"/>
       <c r="BW93" s="9" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="BX93" s="9"/>
       <c r="BY93" s="9"/>
@@ -14579,7 +14605,7 @@
       <c r="R94" s="12"/>
       <c r="S94" s="12"/>
       <c r="AI94" s="9" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="AQ94" s="9" t="s">
         <v>912</v>
@@ -14597,7 +14623,7 @@
       <c r="BU94" s="9"/>
       <c r="BV94" s="9"/>
       <c r="BW94" s="9" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="BX94" s="9"/>
       <c r="BY94" s="9"/>
@@ -14651,7 +14677,7 @@
       <c r="BU95" s="9"/>
       <c r="BV95" s="9"/>
       <c r="BW95" s="9" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="BX95" s="9"/>
       <c r="BY95" s="9"/>
@@ -14687,7 +14713,7 @@
       <c r="R96" s="12"/>
       <c r="S96" s="12"/>
       <c r="AI96" s="9" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="AQ96" s="9" t="s">
         <v>914</v>
@@ -14705,7 +14731,7 @@
       <c r="BU96" s="9"/>
       <c r="BV96" s="9"/>
       <c r="BW96" s="9" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="BX96" s="9"/>
       <c r="BY96" s="9"/>
@@ -14741,7 +14767,7 @@
       <c r="R97" s="12"/>
       <c r="S97" s="12"/>
       <c r="AI97" s="9" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="AQ97" s="9" t="s">
         <v>915</v>
@@ -14759,7 +14785,7 @@
       <c r="BU97" s="9"/>
       <c r="BV97" s="9"/>
       <c r="BW97" s="9" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="BX97" s="9"/>
       <c r="BY97" s="9"/>
@@ -14795,7 +14821,7 @@
       <c r="R98" s="12"/>
       <c r="S98" s="12"/>
       <c r="AI98" s="9" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="AQ98" s="9" t="s">
         <v>916</v>
@@ -14813,7 +14839,7 @@
       <c r="BU98" s="9"/>
       <c r="BV98" s="9"/>
       <c r="BW98" s="9" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="BX98" s="9"/>
       <c r="BY98" s="9"/>
@@ -14849,7 +14875,7 @@
       <c r="R99" s="12"/>
       <c r="S99" s="12"/>
       <c r="AI99" s="9" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="AQ99" s="9" t="s">
         <v>917</v>
@@ -14867,7 +14893,7 @@
       <c r="BU99" s="9"/>
       <c r="BV99" s="9"/>
       <c r="BW99" s="9" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="BX99" s="9"/>
       <c r="BY99" s="9"/>
@@ -14903,7 +14929,7 @@
       <c r="R100" s="12"/>
       <c r="S100" s="12"/>
       <c r="AI100" s="9" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="AQ100" s="9" t="s">
         <v>918</v>
@@ -14921,7 +14947,7 @@
       <c r="BU100" s="9"/>
       <c r="BV100" s="9"/>
       <c r="BW100" s="9" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="BX100" s="9"/>
       <c r="BY100" s="9"/>
@@ -14957,7 +14983,7 @@
       <c r="R101" s="12"/>
       <c r="S101" s="12"/>
       <c r="AI101" s="9" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="AQ101" s="9" t="s">
         <v>919</v>
@@ -14975,7 +15001,7 @@
       <c r="BU101" s="9"/>
       <c r="BV101" s="9"/>
       <c r="BW101" s="9" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="BX101" s="9"/>
       <c r="BY101" s="9"/>
@@ -15029,7 +15055,7 @@
       <c r="BU102" s="9"/>
       <c r="BV102" s="9"/>
       <c r="BW102" s="9" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="BX102" s="9"/>
       <c r="BY102" s="9"/>
@@ -15065,7 +15091,7 @@
       <c r="R103" s="12"/>
       <c r="S103" s="12"/>
       <c r="AI103" s="9" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="AQ103" s="9" t="s">
         <v>921</v>
@@ -15083,7 +15109,7 @@
       <c r="BU103" s="9"/>
       <c r="BV103" s="9"/>
       <c r="BW103" s="9" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="BX103" s="9"/>
       <c r="BY103" s="9"/>
@@ -15119,7 +15145,7 @@
       <c r="R104" s="12"/>
       <c r="S104" s="12"/>
       <c r="AI104" s="9" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="AQ104" s="9" t="s">
         <v>922</v>
@@ -15137,7 +15163,7 @@
       <c r="BU104" s="9"/>
       <c r="BV104" s="9"/>
       <c r="BW104" s="9" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="BX104" s="9"/>
       <c r="BY104" s="9"/>
@@ -15173,7 +15199,7 @@
       <c r="R105" s="12"/>
       <c r="S105" s="12"/>
       <c r="AI105" s="9" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AQ105" s="9" t="s">
         <v>923</v>
@@ -15191,7 +15217,7 @@
       <c r="BU105" s="9"/>
       <c r="BV105" s="9"/>
       <c r="BW105" s="9" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="BX105" s="9"/>
       <c r="BY105" s="9"/>
@@ -15227,7 +15253,7 @@
       <c r="R106" s="12"/>
       <c r="S106" s="12"/>
       <c r="AI106" s="9" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="AQ106" s="9" t="s">
         <v>924</v>
@@ -15245,7 +15271,7 @@
       <c r="BU106" s="9"/>
       <c r="BV106" s="9"/>
       <c r="BW106" s="9" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="BX106" s="9"/>
       <c r="BY106" s="9"/>
@@ -15281,7 +15307,7 @@
       <c r="R107" s="12"/>
       <c r="S107" s="12"/>
       <c r="AI107" s="9" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AQ107" s="9" t="s">
         <v>925</v>
@@ -15299,7 +15325,7 @@
       <c r="BU107" s="9"/>
       <c r="BV107" s="9"/>
       <c r="BW107" s="9" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="BX107" s="9"/>
       <c r="BY107" s="9"/>
@@ -15335,7 +15361,7 @@
       <c r="R108" s="12"/>
       <c r="S108" s="12"/>
       <c r="AI108" s="9" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AQ108" s="9" t="s">
         <v>926</v>
@@ -15353,7 +15379,7 @@
       <c r="BU108" s="9"/>
       <c r="BV108" s="9"/>
       <c r="BW108" s="9" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="BX108" s="9"/>
       <c r="BY108" s="9"/>
@@ -15389,7 +15415,7 @@
       <c r="R109" s="12"/>
       <c r="S109" s="12"/>
       <c r="AI109" s="9" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="AQ109" s="9" t="s">
         <v>927</v>
@@ -15407,7 +15433,7 @@
       <c r="BU109" s="9"/>
       <c r="BV109" s="9"/>
       <c r="BW109" s="9" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="BX109" s="9"/>
       <c r="BY109" s="9"/>
@@ -15443,7 +15469,7 @@
       <c r="R110" s="12"/>
       <c r="S110" s="12"/>
       <c r="AI110" s="9" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="AQ110" s="9" t="s">
         <v>928</v>
@@ -15461,7 +15487,7 @@
       <c r="BU110" s="9"/>
       <c r="BV110" s="9"/>
       <c r="BW110" s="9" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="BX110" s="9"/>
       <c r="BY110" s="9"/>
@@ -15497,7 +15523,7 @@
       <c r="R111" s="12"/>
       <c r="S111" s="12"/>
       <c r="AI111" s="9" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AQ111" s="9" t="s">
         <v>929</v>
@@ -15515,7 +15541,7 @@
       <c r="BU111" s="9"/>
       <c r="BV111" s="9"/>
       <c r="BW111" s="9" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="BX111" s="9"/>
       <c r="BY111" s="9"/>
@@ -15551,7 +15577,7 @@
       <c r="R112" s="12"/>
       <c r="S112" s="12"/>
       <c r="AI112" s="9" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="AQ112" s="9" t="s">
         <v>930</v>
@@ -15569,7 +15595,7 @@
       <c r="BU112" s="9"/>
       <c r="BV112" s="9"/>
       <c r="BW112" s="9" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="BX112" s="9"/>
       <c r="BY112" s="9"/>
@@ -15605,7 +15631,7 @@
       <c r="R113" s="12"/>
       <c r="S113" s="12"/>
       <c r="AI113" s="9" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="AQ113" s="9" t="s">
         <v>931</v>
@@ -15623,7 +15649,7 @@
       <c r="BU113" s="9"/>
       <c r="BV113" s="9"/>
       <c r="BW113" s="9" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="BX113" s="9"/>
       <c r="BY113" s="9"/>
@@ -15659,7 +15685,7 @@
       <c r="R114" s="12"/>
       <c r="S114" s="12"/>
       <c r="AI114" s="9" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="AQ114" s="9" t="s">
         <v>932</v>
@@ -15677,7 +15703,7 @@
       <c r="BU114" s="9"/>
       <c r="BV114" s="9"/>
       <c r="BW114" s="9" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="BX114" s="9"/>
       <c r="BY114" s="9"/>
@@ -15713,7 +15739,7 @@
       <c r="R115" s="12"/>
       <c r="S115" s="12"/>
       <c r="AI115" s="9" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="AQ115" s="9" t="s">
         <v>933</v>
@@ -15731,7 +15757,7 @@
       <c r="BU115" s="9"/>
       <c r="BV115" s="9"/>
       <c r="BW115" s="9" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="BX115" s="9"/>
       <c r="BY115" s="9"/>
@@ -15767,7 +15793,7 @@
       <c r="R116" s="12"/>
       <c r="S116" s="12"/>
       <c r="AI116" s="9" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="AQ116" s="9" t="s">
         <v>934</v>
@@ -15785,7 +15811,7 @@
       <c r="BU116" s="9"/>
       <c r="BV116" s="9"/>
       <c r="BW116" s="9" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="BX116" s="9"/>
       <c r="BY116" s="9"/>
@@ -15821,7 +15847,7 @@
       <c r="R117" s="12"/>
       <c r="S117" s="12"/>
       <c r="AI117" s="9" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="AQ117" s="9" t="s">
         <v>935</v>
@@ -15839,7 +15865,7 @@
       <c r="BU117" s="9"/>
       <c r="BV117" s="9"/>
       <c r="BW117" s="9" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="BX117" s="9"/>
       <c r="BY117" s="9"/>
@@ -15893,7 +15919,7 @@
       <c r="BU118" s="9"/>
       <c r="BV118" s="9"/>
       <c r="BW118" s="9" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="BX118" s="9"/>
       <c r="BY118" s="9"/>
@@ -15944,7 +15970,7 @@
       <c r="BU119" s="9"/>
       <c r="BV119" s="9"/>
       <c r="BW119" s="9" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="BX119" s="9"/>
       <c r="BY119" s="9"/>
@@ -15995,7 +16021,7 @@
       <c r="BU120" s="9"/>
       <c r="BV120" s="9"/>
       <c r="BW120" s="9" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="BX120" s="9"/>
       <c r="BY120" s="9"/>
@@ -16046,7 +16072,7 @@
       <c r="BU121" s="9"/>
       <c r="BV121" s="9"/>
       <c r="BW121" s="9" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="BX121" s="9"/>
       <c r="BY121" s="9"/>
@@ -16097,7 +16123,7 @@
       <c r="BU122" s="9"/>
       <c r="BV122" s="9"/>
       <c r="BW122" s="9" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="BX122" s="9"/>
       <c r="BY122" s="9"/>
@@ -16148,7 +16174,7 @@
       <c r="BU123" s="9"/>
       <c r="BV123" s="9"/>
       <c r="BW123" s="9" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="BX123" s="9"/>
       <c r="BY123" s="9"/>
@@ -16199,7 +16225,7 @@
       <c r="BU124" s="9"/>
       <c r="BV124" s="9"/>
       <c r="BW124" s="9" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="BX124" s="9"/>
       <c r="BY124" s="9"/>
@@ -16301,7 +16327,7 @@
       <c r="BU126" s="9"/>
       <c r="BV126" s="9"/>
       <c r="BW126" s="9" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="BX126" s="9"/>
       <c r="BY126" s="9"/>
@@ -16352,7 +16378,7 @@
       <c r="BU127" s="9"/>
       <c r="BV127" s="9"/>
       <c r="BW127" s="9" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="BX127" s="9"/>
       <c r="BY127" s="9"/>
@@ -16403,7 +16429,7 @@
       <c r="BU128" s="9"/>
       <c r="BV128" s="9"/>
       <c r="BW128" s="9" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="BX128" s="9"/>
       <c r="BY128" s="9"/>
@@ -16454,7 +16480,7 @@
       <c r="BU129" s="9"/>
       <c r="BV129" s="9"/>
       <c r="BW129" s="9" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="BX129" s="9"/>
       <c r="BY129" s="9"/>
@@ -16505,7 +16531,7 @@
       <c r="BU130" s="9"/>
       <c r="BV130" s="9"/>
       <c r="BW130" s="9" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="BX130" s="9"/>
       <c r="BY130" s="9"/>
@@ -16556,7 +16582,7 @@
       <c r="BU131" s="9"/>
       <c r="BV131" s="9"/>
       <c r="BW131" s="9" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="BX131" s="9"/>
       <c r="BY131" s="9"/>
@@ -16607,7 +16633,7 @@
       <c r="BU132" s="9"/>
       <c r="BV132" s="9"/>
       <c r="BW132" s="9" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="BX132" s="9"/>
       <c r="BY132" s="9"/>
@@ -16658,7 +16684,7 @@
       <c r="BU133" s="9"/>
       <c r="BV133" s="9"/>
       <c r="BW133" s="9" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="BX133" s="9"/>
       <c r="BY133" s="9"/>
@@ -16709,7 +16735,7 @@
       <c r="BU134" s="9"/>
       <c r="BV134" s="9"/>
       <c r="BW134" s="9" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="BX134" s="9"/>
       <c r="BY134" s="9"/>
@@ -16811,7 +16837,7 @@
       <c r="BU136" s="9"/>
       <c r="BV136" s="9"/>
       <c r="BW136" s="9" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="BX136" s="9"/>
       <c r="BY136" s="9"/>
@@ -16862,7 +16888,7 @@
       <c r="BU137" s="9"/>
       <c r="BV137" s="9"/>
       <c r="BW137" s="9" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="BX137" s="9"/>
       <c r="BY137" s="9"/>
@@ -16913,7 +16939,7 @@
       <c r="BU138" s="9"/>
       <c r="BV138" s="9"/>
       <c r="BW138" s="9" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="BX138" s="9"/>
       <c r="BY138" s="9"/>
@@ -16964,7 +16990,7 @@
       <c r="BU139" s="9"/>
       <c r="BV139" s="9"/>
       <c r="BW139" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="BX139" s="9"/>
       <c r="BY139" s="9"/>
@@ -17015,7 +17041,7 @@
       <c r="BU140" s="9"/>
       <c r="BV140" s="9"/>
       <c r="BW140" s="9" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="BX140" s="9"/>
       <c r="BY140" s="9"/>
@@ -17066,7 +17092,7 @@
       <c r="BU141" s="9"/>
       <c r="BV141" s="9"/>
       <c r="BW141" s="9" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="BX141" s="9"/>
       <c r="BY141" s="9"/>
@@ -17117,7 +17143,7 @@
       <c r="BU142" s="9"/>
       <c r="BV142" s="9"/>
       <c r="BW142" s="9" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="BX142" s="9"/>
       <c r="BY142" s="9"/>
@@ -17168,7 +17194,7 @@
       <c r="BU143" s="9"/>
       <c r="BV143" s="9"/>
       <c r="BW143" s="9" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="BX143" s="9"/>
       <c r="BY143" s="9"/>
@@ -17219,7 +17245,7 @@
       <c r="BU144" s="9"/>
       <c r="BV144" s="9"/>
       <c r="BW144" s="9" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="BX144" s="9"/>
       <c r="BY144" s="9"/>
@@ -17270,7 +17296,7 @@
       <c r="BU145" s="9"/>
       <c r="BV145" s="9"/>
       <c r="BW145" s="9" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="BX145" s="9"/>
       <c r="BY145" s="9"/>
@@ -17372,7 +17398,7 @@
       <c r="BU147" s="9"/>
       <c r="BV147" s="9"/>
       <c r="BW147" s="9" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="BX147" s="9"/>
       <c r="BY147" s="9"/>
@@ -17423,7 +17449,7 @@
       <c r="BU148" s="9"/>
       <c r="BV148" s="9"/>
       <c r="BW148" s="9" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="BX148" s="9"/>
       <c r="BY148" s="9"/>
@@ -17474,7 +17500,7 @@
       <c r="BU149" s="9"/>
       <c r="BV149" s="9"/>
       <c r="BW149" s="9" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="BX149" s="9"/>
       <c r="BY149" s="9"/>
@@ -17525,7 +17551,7 @@
       <c r="BU150" s="9"/>
       <c r="BV150" s="9"/>
       <c r="BW150" s="9" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="BX150" s="9"/>
       <c r="BY150" s="9"/>
@@ -17576,7 +17602,7 @@
       <c r="BU151" s="9"/>
       <c r="BV151" s="9"/>
       <c r="BW151" s="9" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="BX151" s="9"/>
       <c r="BY151" s="9"/>
@@ -17627,7 +17653,7 @@
       <c r="BU152" s="9"/>
       <c r="BV152" s="9"/>
       <c r="BW152" s="9" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="BX152" s="9"/>
       <c r="BY152" s="9"/>
@@ -17678,7 +17704,7 @@
       <c r="BU153" s="9"/>
       <c r="BV153" s="9"/>
       <c r="BW153" s="9" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="BX153" s="9"/>
       <c r="BY153" s="9"/>
@@ -17729,7 +17755,7 @@
       <c r="BU154" s="9"/>
       <c r="BV154" s="9"/>
       <c r="BW154" s="9" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="BX154" s="9"/>
       <c r="BY154" s="9"/>
@@ -17780,7 +17806,7 @@
       <c r="BU155" s="9"/>
       <c r="BV155" s="9"/>
       <c r="BW155" s="9" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="BX155" s="9"/>
       <c r="BY155" s="9"/>
@@ -17831,7 +17857,7 @@
       <c r="BU156" s="9"/>
       <c r="BV156" s="9"/>
       <c r="BW156" s="9" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="BX156" s="9"/>
       <c r="BY156" s="9"/>
@@ -17882,7 +17908,7 @@
       <c r="BU157" s="9"/>
       <c r="BV157" s="9"/>
       <c r="BW157" s="9" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="BX157" s="9"/>
       <c r="BY157" s="9"/>
@@ -17933,7 +17959,7 @@
       <c r="BU158" s="9"/>
       <c r="BV158" s="9"/>
       <c r="BW158" s="9" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="BX158" s="9"/>
       <c r="BY158" s="9"/>
@@ -17984,7 +18010,7 @@
       <c r="BU159" s="9"/>
       <c r="BV159" s="9"/>
       <c r="BW159" s="9" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="BX159" s="9"/>
       <c r="BY159" s="9"/>
@@ -18035,7 +18061,7 @@
       <c r="BU160" s="9"/>
       <c r="BV160" s="9"/>
       <c r="BW160" s="9" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="BX160" s="9"/>
       <c r="BY160" s="9"/>
@@ -18086,7 +18112,7 @@
       <c r="BU161" s="9"/>
       <c r="BV161" s="9"/>
       <c r="BW161" s="9" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="BX161" s="9"/>
       <c r="BY161" s="9"/>
@@ -18137,7 +18163,7 @@
       <c r="BU162" s="9"/>
       <c r="BV162" s="9"/>
       <c r="BW162" s="9" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="BX162" s="9"/>
       <c r="BY162" s="9"/>
@@ -18188,7 +18214,7 @@
       <c r="BU163" s="9"/>
       <c r="BV163" s="9"/>
       <c r="BW163" s="9" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="BX163" s="9"/>
       <c r="BY163" s="9"/>
@@ -18239,7 +18265,7 @@
       <c r="BU164" s="9"/>
       <c r="BV164" s="9"/>
       <c r="BW164" s="9" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="BX164" s="9"/>
       <c r="BY164" s="9"/>
@@ -18290,7 +18316,7 @@
       <c r="BU165" s="9"/>
       <c r="BV165" s="9"/>
       <c r="BW165" s="9" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="BX165" s="9"/>
       <c r="BY165" s="9"/>
@@ -18341,7 +18367,7 @@
       <c r="BU166" s="9"/>
       <c r="BV166" s="9"/>
       <c r="BW166" s="9" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="BX166" s="9"/>
       <c r="BY166" s="9"/>
@@ -18392,7 +18418,7 @@
       <c r="BU167" s="9"/>
       <c r="BV167" s="9"/>
       <c r="BW167" s="9" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="BX167" s="9"/>
       <c r="BY167" s="9"/>
@@ -18443,7 +18469,7 @@
       <c r="BU168" s="9"/>
       <c r="BV168" s="9"/>
       <c r="BW168" s="9" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="BX168" s="9"/>
       <c r="BY168" s="9"/>
@@ -18494,7 +18520,7 @@
       <c r="BU169" s="9"/>
       <c r="BV169" s="9"/>
       <c r="BW169" s="9" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="BX169" s="9"/>
       <c r="BY169" s="9"/>
@@ -18545,7 +18571,7 @@
       <c r="BU170" s="9"/>
       <c r="BV170" s="9"/>
       <c r="BW170" s="9" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="BX170" s="9"/>
       <c r="BY170" s="9"/>
@@ -18596,7 +18622,7 @@
       <c r="BU171" s="9"/>
       <c r="BV171" s="9"/>
       <c r="BW171" s="9" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="BX171" s="9"/>
       <c r="BY171" s="9"/>

--- a/docs/CDOP Enumerated Values Lists.xlsx
+++ b/docs/CDOP Enumerated Values Lists.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Enumerated Values Lists/9_16_26/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/sebastian_weeks_rmi_org/Documents/Documents/CDOP Resources/UseCase_Category CSVs_JSONs/Master Version/Round 2 Pods for Testing/Slow Track Pods/R2ST Enumerated Values/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{22CD7E23-D148-4265-8DDA-C8A8D8F9DF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF08119B-5833-458F-B72A-6D4CDB9F8C4B}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{22CD7E23-D148-4265-8DDA-C8A8D8F9DF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC5CECC8-6405-444E-AA52-2ADF3026144E}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="760" windowWidth="18480" windowHeight="9960" xr2:uid="{6157C829-B9E8-47C5-B94D-577BB9DC27B4}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6157C829-B9E8-47C5-B94D-577BB9DC27B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Enumerated Values Lists" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2160" uniqueCount="1851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2184" uniqueCount="1865">
   <si>
     <t>Enumerated Values List</t>
   </si>
@@ -2249,9 +2249,6 @@
     <t>ECO Natural Forest Standard</t>
   </si>
   <si>
-    <t>Verificed Carbon Standard (VCS)</t>
-  </si>
-  <si>
     <t>BCR0001_ARR Activities</t>
   </si>
   <si>
@@ -4313,9 +4310,6 @@
     <t>origin_registry &amp; current_registry &amp; current_project_issuance_registry</t>
   </si>
   <si>
-    <t>crediting_program_name &amp; previous_project_crediting_program_name</t>
-  </si>
-  <si>
     <t>financing_options</t>
   </si>
   <si>
@@ -5589,13 +5583,61 @@
   </si>
   <si>
     <t>Waste Reduction</t>
+  </si>
+  <si>
+    <t>Verified Carbon Standard (VCS)</t>
+  </si>
+  <si>
+    <t>crediting_program_name &amp; previous_project_crediting_program_name &amp; crediting_programme</t>
+  </si>
+  <si>
+    <t>methodology &amp; methodology_name</t>
+  </si>
+  <si>
+    <t>use_status</t>
+  </si>
+  <si>
+    <t>use_status_reason</t>
+  </si>
+  <si>
+    <t>Draft</t>
+  </si>
+  <si>
+    <t>In force</t>
+  </si>
+  <si>
+    <t>New version released</t>
+  </si>
+  <si>
+    <t>Methodology retired</t>
+  </si>
+  <si>
+    <t>Grace period ended</t>
+  </si>
+  <si>
+    <t>methodology_version_use_status</t>
+  </si>
+  <si>
+    <t>methodology_version_use_status_reason</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Program update</t>
+  </si>
+  <si>
+    <t>Project design change</t>
+  </si>
+  <si>
+    <t>VVB requirement</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5683,6 +5725,19 @@
       <name val="Aptos Display"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -5728,7 +5783,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -5792,6 +5847,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -6169,6 +6226,9 @@
     <col min="108" max="108" width="12.90625" customWidth="1"/>
     <col min="109" max="109" width="33.7265625" customWidth="1"/>
     <col min="110" max="110" width="24" customWidth="1"/>
+    <col min="111" max="111" width="24.453125" customWidth="1"/>
+    <col min="113" max="113" width="38" customWidth="1"/>
+    <col min="115" max="115" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:121" x14ac:dyDescent="0.35">
@@ -6217,189 +6277,201 @@
     </row>
     <row r="3" spans="1:121" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="F3" s="12"/>
       <c r="G3" s="12" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="H3" s="12"/>
       <c r="J3" s="12"/>
       <c r="L3" s="12"/>
       <c r="M3" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="P3" s="2"/>
       <c r="Q3" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="R3" s="2"/>
       <c r="S3" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="T3" s="2"/>
       <c r="U3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="W3" t="s">
         <v>1336</v>
       </c>
-      <c r="W3" t="s">
+      <c r="Y3" t="s">
         <v>1337</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="AA3" t="s">
         <v>1338</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AC3" t="s">
         <v>1339</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AE3" t="s">
         <v>1340</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AG3" t="s">
         <v>1341</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AI3" t="s">
         <v>1342</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AK3" t="s">
+        <v>1423</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>1850</v>
+      </c>
+      <c r="AO3" t="s">
         <v>1343</v>
       </c>
-      <c r="AK3" t="s">
+      <c r="AQ3" t="s">
+        <v>1851</v>
+      </c>
+      <c r="AS3" s="6" t="s">
+        <v>1314</v>
+      </c>
+      <c r="AU3" s="6" t="s">
+        <v>1344</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="AY3" s="13" t="s">
+        <v>1346</v>
+      </c>
+      <c r="BA3" s="13" t="s">
+        <v>1347</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="BE3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>1350</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>1351</v>
+      </c>
+      <c r="BK3" s="9" t="s">
         <v>1424</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>1425</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>1344</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>608</v>
-      </c>
-      <c r="AS3" s="6" t="s">
-        <v>1315</v>
-      </c>
-      <c r="AU3" s="6" t="s">
-        <v>1345</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>1346</v>
-      </c>
-      <c r="AY3" s="13" t="s">
-        <v>1347</v>
-      </c>
-      <c r="BA3" s="13" t="s">
-        <v>1348</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>1349</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>1350</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>1351</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>1352</v>
-      </c>
-      <c r="BK3" s="9" t="s">
-        <v>1426</v>
       </c>
       <c r="BL3" s="9"/>
       <c r="BM3" s="9" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="BN3" s="9"/>
       <c r="BO3" s="9" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="BP3" s="9"/>
       <c r="BQ3" s="9" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="BR3" s="9"/>
       <c r="BS3" s="9" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="BT3" s="9"/>
       <c r="BU3" s="23" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="BV3" s="23"/>
       <c r="BW3" s="9" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="BX3" s="9"/>
       <c r="BY3" s="9" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="BZ3" s="9"/>
       <c r="CA3" s="9" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="CB3" s="9"/>
       <c r="CC3" s="9" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="CD3" s="9"/>
       <c r="CE3" s="9" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="CG3" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="CI3" t="s">
+        <v>1676</v>
+      </c>
+      <c r="CK3" s="22" t="s">
+        <v>1675</v>
+      </c>
+      <c r="CM3" t="s">
+        <v>1677</v>
+      </c>
+      <c r="CO3" t="s">
         <v>1678</v>
       </c>
-      <c r="CK3" s="22" t="s">
-        <v>1677</v>
-      </c>
-      <c r="CM3" t="s">
-        <v>1679</v>
-      </c>
-      <c r="CO3" t="s">
-        <v>1680</v>
-      </c>
       <c r="CQ3" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="CS3" s="27" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="CT3" s="27"/>
       <c r="CU3" s="27" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="CV3" s="27"/>
       <c r="CW3" s="27" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="CX3" s="27"/>
       <c r="CY3" s="27" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="CZ3" s="27"/>
       <c r="DA3" s="27" t="s">
-        <v>1766</v>
+        <v>1764</v>
       </c>
       <c r="DB3" s="27"/>
       <c r="DC3" s="27" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="DD3" s="27"/>
       <c r="DE3" s="27" t="s">
-        <v>1767</v>
+        <v>1765</v>
+      </c>
+      <c r="DG3" s="31" t="s">
+        <v>1859</v>
+      </c>
+      <c r="DI3" s="31" t="s">
+        <v>1860</v>
+      </c>
+      <c r="DK3" t="s">
+        <v>1852</v>
+      </c>
+      <c r="DM3" t="s">
+        <v>1853</v>
       </c>
     </row>
     <row r="4" spans="1:121" ht="16" x14ac:dyDescent="0.4">
@@ -6486,136 +6558,144 @@
         <v>608</v>
       </c>
       <c r="AS4" s="5" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="AT4" s="5"/>
       <c r="AU4" s="5" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="AV4" s="5"/>
       <c r="AW4" s="5" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="AY4" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="BA4" s="7" t="s">
         <v>1353</v>
       </c>
-      <c r="BA4" s="7" t="s">
+      <c r="BC4" s="8" t="s">
         <v>1354</v>
       </c>
-      <c r="BC4" s="8" t="s">
+      <c r="BE4" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="BE4" s="1" t="s">
+      <c r="BG4" s="1" t="s">
         <v>1356</v>
       </c>
-      <c r="BG4" s="1" t="s">
+      <c r="BI4" s="1" t="s">
         <v>1357</v>
       </c>
-      <c r="BI4" s="1" t="s">
-        <v>1358</v>
-      </c>
       <c r="BK4" s="24" t="s">
-        <v>1426</v>
+        <v>1424</v>
       </c>
       <c r="BL4" s="9"/>
       <c r="BM4" s="24" t="s">
-        <v>1427</v>
+        <v>1425</v>
       </c>
       <c r="BN4" s="24"/>
       <c r="BO4" s="24" t="s">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="BP4" s="24"/>
       <c r="BQ4" s="24" t="s">
-        <v>1429</v>
+        <v>1427</v>
       </c>
       <c r="BR4" s="24"/>
       <c r="BS4" s="24" t="s">
-        <v>1430</v>
+        <v>1428</v>
       </c>
       <c r="BT4" s="24"/>
       <c r="BU4" s="25" t="s">
-        <v>1431</v>
+        <v>1429</v>
       </c>
       <c r="BV4" s="25"/>
       <c r="BW4" s="24" t="s">
-        <v>1432</v>
+        <v>1430</v>
       </c>
       <c r="BX4" s="24"/>
       <c r="BY4" s="24" t="s">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="BZ4" s="24"/>
       <c r="CA4" s="24" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="CB4" s="24"/>
       <c r="CC4" s="24" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="CD4" s="24"/>
       <c r="CE4" s="24" t="s">
-        <v>1436</v>
+        <v>1434</v>
       </c>
       <c r="CG4" s="1" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="CH4" s="1"/>
       <c r="CI4" s="1" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="CJ4" s="1"/>
       <c r="CK4" s="1" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="CL4" s="1"/>
       <c r="CM4" s="1" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="CN4" s="1"/>
       <c r="CO4" s="1" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="CP4" s="1"/>
       <c r="CQ4" s="1" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="CR4" s="1"/>
       <c r="CS4" s="26" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="CT4" s="26"/>
       <c r="CU4" s="26" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
       <c r="CV4" s="26"/>
       <c r="CW4" s="26" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
       <c r="CX4" s="26"/>
       <c r="CY4" s="26" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="CZ4" s="26"/>
       <c r="DA4" s="26" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="DB4" s="26"/>
       <c r="DC4" s="26" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="DD4" s="26"/>
       <c r="DE4" s="26" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="DF4" s="26"/>
-      <c r="DG4" s="1"/>
+      <c r="DG4" s="32" t="s">
+        <v>1859</v>
+      </c>
       <c r="DH4" s="1"/>
-      <c r="DI4" s="1"/>
+      <c r="DI4" s="32" t="s">
+        <v>1860</v>
+      </c>
       <c r="DJ4" s="1"/>
-      <c r="DK4" s="1"/>
+      <c r="DK4" s="1" t="s">
+        <v>1852</v>
+      </c>
       <c r="DL4" s="1"/>
-      <c r="DM4" s="1"/>
+      <c r="DM4" s="1" t="s">
+        <v>1853</v>
+      </c>
       <c r="DN4" s="1"/>
       <c r="DO4" s="1"/>
       <c r="DP4" s="1"/>
@@ -6667,7 +6747,7 @@
         <v>611</v>
       </c>
       <c r="AA5" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="AC5" s="9" t="s">
         <v>613</v>
@@ -6682,7 +6762,7 @@
       </c>
       <c r="AH5" s="9"/>
       <c r="AI5" s="10" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="AJ5" s="9"/>
       <c r="AK5" s="9" t="s">
@@ -6700,43 +6780,43 @@
         <v>618</v>
       </c>
       <c r="AS5" s="12" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="AT5" s="12"/>
       <c r="AU5" t="s">
         <v>610</v>
       </c>
       <c r="AW5" s="12" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="AY5" s="9" t="s">
+        <v>1359</v>
+      </c>
+      <c r="BA5" s="17" t="s">
         <v>1360</v>
       </c>
-      <c r="BA5" s="17" t="s">
+      <c r="BC5" s="18" t="s">
         <v>1361</v>
       </c>
-      <c r="BC5" s="18" t="s">
+      <c r="BE5" t="s">
         <v>1362</v>
       </c>
-      <c r="BE5" t="s">
+      <c r="BG5" s="9" t="s">
         <v>1363</v>
       </c>
-      <c r="BG5" s="9" t="s">
+      <c r="BI5" t="s">
         <v>1364</v>
       </c>
-      <c r="BI5" t="s">
-        <v>1365</v>
-      </c>
       <c r="BK5" s="9" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="BL5" s="9"/>
       <c r="BM5" s="9" t="s">
-        <v>1437</v>
+        <v>1435</v>
       </c>
       <c r="BN5" s="9"/>
       <c r="BO5" s="9" t="s">
-        <v>1438</v>
+        <v>1436</v>
       </c>
       <c r="BP5" s="9"/>
       <c r="BQ5" s="9" t="s">
@@ -6744,78 +6824,90 @@
       </c>
       <c r="BR5" s="9"/>
       <c r="BS5" s="9" t="s">
-        <v>1439</v>
+        <v>1437</v>
       </c>
       <c r="BT5" s="9"/>
       <c r="BU5" s="9" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="BV5" s="9"/>
       <c r="BW5" s="9" t="s">
-        <v>1441</v>
+        <v>1439</v>
       </c>
       <c r="BX5" s="9"/>
       <c r="BY5" s="9" t="s">
-        <v>1442</v>
+        <v>1440</v>
       </c>
       <c r="BZ5" s="9"/>
       <c r="CA5" s="9" t="s">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="CB5" s="9"/>
       <c r="CC5" s="9" t="s">
-        <v>1444</v>
+        <v>1442</v>
       </c>
       <c r="CD5" s="9"/>
       <c r="CE5" s="9" t="s">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="CG5" s="19" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="CI5" s="19" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="CK5" s="19" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="CM5" s="19" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="CO5" s="19" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="CQ5" s="19" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="CS5" s="27" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="CT5" s="27"/>
       <c r="CU5" s="27" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="CV5" s="27"/>
       <c r="CW5" s="27" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="CX5" s="27"/>
       <c r="CY5" s="28" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="CZ5" s="28"/>
       <c r="DA5" s="28" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="DB5" s="28"/>
       <c r="DC5" s="28" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="DD5" s="28"/>
       <c r="DE5" s="28" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="DF5" s="28"/>
+      <c r="DG5" t="s">
+        <v>1854</v>
+      </c>
+      <c r="DI5" t="s">
+        <v>1856</v>
+      </c>
+      <c r="DK5" t="s">
+        <v>1861</v>
+      </c>
+      <c r="DM5" t="s">
+        <v>1862</v>
+      </c>
     </row>
     <row r="6" spans="1:121" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="20" t="s">
@@ -6863,7 +6955,7 @@
         <v>621</v>
       </c>
       <c r="AA6" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="AC6" s="21" t="s">
         <v>623</v>
@@ -6878,7 +6970,7 @@
       </c>
       <c r="AH6" s="9"/>
       <c r="AI6" s="10" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="AJ6" s="9"/>
       <c r="AK6" t="s">
@@ -6894,43 +6986,43 @@
         <v>629</v>
       </c>
       <c r="AS6" s="12" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="AT6" s="12"/>
       <c r="AU6" t="s">
         <v>620</v>
       </c>
       <c r="AW6" s="12" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="AY6" s="9" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="BA6" s="17" t="s">
         <v>622</v>
       </c>
       <c r="BC6" s="18" t="s">
+        <v>1367</v>
+      </c>
+      <c r="BE6" t="s">
         <v>1368</v>
       </c>
-      <c r="BE6" t="s">
+      <c r="BG6" s="9" t="s">
         <v>1369</v>
       </c>
-      <c r="BG6" s="9" t="s">
+      <c r="BI6" t="s">
         <v>1370</v>
       </c>
-      <c r="BI6" t="s">
-        <v>1371</v>
-      </c>
       <c r="BK6" s="9" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="BL6" s="9"/>
       <c r="BM6" s="9" t="s">
-        <v>1446</v>
+        <v>1444</v>
       </c>
       <c r="BN6" s="9"/>
       <c r="BO6" s="9" t="s">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="BP6" s="9"/>
       <c r="BQ6" s="9" t="s">
@@ -6938,76 +7030,88 @@
       </c>
       <c r="BR6" s="9"/>
       <c r="BS6" s="9" t="s">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="BT6" s="9"/>
       <c r="BU6" s="9" t="s">
-        <v>1449</v>
+        <v>1447</v>
       </c>
       <c r="BV6" s="9"/>
       <c r="BW6" s="9" t="s">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="BX6" s="9"/>
       <c r="BY6" s="9" t="s">
-        <v>1451</v>
+        <v>1449</v>
       </c>
       <c r="BZ6" s="9"/>
       <c r="CA6" s="9" t="s">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="CB6" s="9"/>
       <c r="CC6" s="9" t="s">
-        <v>1453</v>
+        <v>1451</v>
       </c>
       <c r="CD6" s="9"/>
       <c r="CE6" s="9" t="s">
-        <v>1454</v>
+        <v>1452</v>
       </c>
       <c r="CG6" s="19" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="CI6" s="19" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="CK6" s="19" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="CM6" s="19" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="CO6" s="19" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="CQ6" s="19" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="CS6" s="28" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="CT6" s="28"/>
       <c r="CU6" s="27" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="CV6" s="27"/>
       <c r="CW6" s="27"/>
       <c r="CX6" s="27"/>
       <c r="CY6" s="28" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="CZ6" s="28"/>
       <c r="DA6" s="28" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="DB6" s="28"/>
       <c r="DC6" s="28" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="DD6" s="28"/>
       <c r="DE6" s="28" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="DF6" s="28"/>
+      <c r="DG6" t="s">
+        <v>644</v>
+      </c>
+      <c r="DI6" t="s">
+        <v>1857</v>
+      </c>
+      <c r="DK6" t="s">
+        <v>622</v>
+      </c>
+      <c r="DM6" t="s">
+        <v>1857</v>
+      </c>
     </row>
     <row r="7" spans="1:121" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
@@ -7053,7 +7157,7 @@
         <v>632</v>
       </c>
       <c r="AA7" s="22" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="AB7" s="22"/>
       <c r="AC7" s="9" t="s">
@@ -7069,7 +7173,7 @@
       </c>
       <c r="AH7" s="9"/>
       <c r="AI7" s="11" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="AJ7" s="9"/>
       <c r="AK7" s="9" t="s">
@@ -7086,37 +7190,37 @@
         <v>640</v>
       </c>
       <c r="AS7" s="12" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="AT7" s="12"/>
       <c r="AU7" t="s">
         <v>631</v>
       </c>
       <c r="AW7" s="12" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="AY7" t="s">
+        <v>1373</v>
+      </c>
+      <c r="BA7" s="17" t="s">
         <v>1374</v>
       </c>
-      <c r="BA7" s="17" t="s">
+      <c r="BE7" t="s">
         <v>1375</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BG7" s="9" t="s">
         <v>1376</v>
       </c>
-      <c r="BG7" s="9" t="s">
-        <v>1377</v>
-      </c>
       <c r="BK7" s="9" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="BL7" s="9"/>
       <c r="BM7" s="9" t="s">
-        <v>1455</v>
+        <v>1453</v>
       </c>
       <c r="BN7" s="9"/>
       <c r="BO7" s="9" t="s">
-        <v>1456</v>
+        <v>1454</v>
       </c>
       <c r="BP7" s="9"/>
       <c r="BQ7" s="9" t="s">
@@ -7124,76 +7228,88 @@
       </c>
       <c r="BR7" s="9"/>
       <c r="BS7" s="9" t="s">
-        <v>1457</v>
+        <v>1455</v>
       </c>
       <c r="BT7" s="9"/>
       <c r="BU7" s="9" t="s">
-        <v>1458</v>
+        <v>1456</v>
       </c>
       <c r="BV7" s="9"/>
       <c r="BW7" s="9" t="s">
-        <v>1459</v>
+        <v>1457</v>
       </c>
       <c r="BX7" s="9"/>
       <c r="BY7" s="9" t="s">
-        <v>1460</v>
+        <v>1458</v>
       </c>
       <c r="BZ7" s="9"/>
       <c r="CA7" s="9" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
       <c r="CB7" s="9"/>
       <c r="CC7" s="9" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
       <c r="CD7" s="9"/>
       <c r="CE7" s="9" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
       <c r="CG7" s="19" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="CI7" s="19" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="CK7" s="19" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="CM7" s="19" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="CO7" s="19" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="CQ7" s="19" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="CS7" s="28" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="CT7" s="28"/>
       <c r="CU7" s="27" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="CV7" s="27"/>
       <c r="CW7" s="27"/>
       <c r="CX7" s="27"/>
       <c r="CY7" s="28" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="CZ7" s="28"/>
       <c r="DA7" s="28" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="DB7" s="28"/>
       <c r="DC7" s="28" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="DD7" s="28"/>
       <c r="DE7" s="28" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="DF7" s="28"/>
+      <c r="DG7" t="s">
+        <v>1855</v>
+      </c>
+      <c r="DI7" t="s">
+        <v>1858</v>
+      </c>
+      <c r="DK7" t="s">
+        <v>1368</v>
+      </c>
+      <c r="DM7" t="s">
+        <v>1863</v>
+      </c>
     </row>
     <row r="8" spans="1:121" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="20" t="s">
@@ -7237,7 +7353,7 @@
         <v>643</v>
       </c>
       <c r="AA8" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="AE8" s="9" t="s">
         <v>645</v>
@@ -7248,7 +7364,7 @@
       </c>
       <c r="AH8" s="9"/>
       <c r="AI8" s="11" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="AJ8" s="9"/>
       <c r="AK8" s="9" t="s">
@@ -7265,34 +7381,34 @@
         <v>650</v>
       </c>
       <c r="AS8" s="12" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="AT8" s="12"/>
       <c r="AU8" t="s">
         <v>642</v>
       </c>
       <c r="AW8" s="12" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="AY8" t="s">
         <v>733</v>
       </c>
       <c r="BE8" t="s">
+        <v>1379</v>
+      </c>
+      <c r="BG8" s="9" t="s">
         <v>1380</v>
       </c>
-      <c r="BG8" s="9" t="s">
-        <v>1381</v>
-      </c>
       <c r="BK8" s="9" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="BL8" s="9"/>
       <c r="BM8" s="9" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
       <c r="BN8" s="9"/>
       <c r="BO8" s="9" t="s">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="BP8" s="9"/>
       <c r="BQ8" s="9" t="s">
@@ -7300,76 +7416,85 @@
       </c>
       <c r="BR8" s="9"/>
       <c r="BS8" s="9" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
       <c r="BT8" s="9"/>
       <c r="BU8" s="9" t="s">
-        <v>1467</v>
+        <v>1465</v>
       </c>
       <c r="BV8" s="9"/>
       <c r="BW8" s="9" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="BX8" s="9"/>
       <c r="BY8" s="9" t="s">
-        <v>1469</v>
+        <v>1467</v>
       </c>
       <c r="BZ8" s="9"/>
       <c r="CA8" s="9" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="CB8" s="9"/>
       <c r="CC8" s="9" t="s">
-        <v>1470</v>
+        <v>1468</v>
       </c>
       <c r="CD8" s="9"/>
       <c r="CE8" s="9" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="CG8" s="19" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="CI8" s="19" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="CK8" s="19" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="CM8" s="19" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="CO8" s="19" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="CQ8" s="19" t="s">
         <v>733</v>
       </c>
       <c r="CS8" s="28" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="CT8" s="28"/>
       <c r="CU8" s="27" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="CV8" s="27"/>
       <c r="CW8" s="27"/>
       <c r="CX8" s="27"/>
       <c r="CY8" s="28" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="CZ8" s="28"/>
       <c r="DA8" s="28" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="DB8" s="28"/>
       <c r="DC8" s="28" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="DD8" s="28"/>
       <c r="DE8" s="28" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="DF8" s="27"/>
+      <c r="DG8" t="s">
+        <v>1374</v>
+      </c>
+      <c r="DK8" t="s">
+        <v>1374</v>
+      </c>
+      <c r="DM8" t="s">
+        <v>1864</v>
+      </c>
     </row>
     <row r="9" spans="1:121" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
@@ -7410,7 +7535,7 @@
         <v>652</v>
       </c>
       <c r="AA9" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="AE9" s="9" t="s">
         <v>654</v>
@@ -7421,7 +7546,7 @@
       </c>
       <c r="AH9" s="9"/>
       <c r="AI9" s="10" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="AJ9" s="9"/>
       <c r="AK9" s="9" t="s">
@@ -7444,24 +7569,24 @@
         <v>651</v>
       </c>
       <c r="AW9" s="12" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="BE9" t="s">
+        <v>1383</v>
+      </c>
+      <c r="BG9" s="9" t="s">
         <v>1384</v>
       </c>
-      <c r="BG9" s="9" t="s">
-        <v>1385</v>
-      </c>
       <c r="BK9" s="9" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="BL9" s="9"/>
       <c r="BM9" s="9" t="s">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="BN9" s="9"/>
       <c r="BO9" s="9" t="s">
-        <v>1472</v>
+        <v>1470</v>
       </c>
       <c r="BP9" s="9"/>
       <c r="BQ9" s="9" t="s">
@@ -7469,71 +7594,74 @@
       </c>
       <c r="BR9" s="9"/>
       <c r="BS9" s="9" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
       <c r="BT9" s="9"/>
       <c r="BU9" s="9" t="s">
-        <v>1474</v>
+        <v>1472</v>
       </c>
       <c r="BV9" s="9"/>
       <c r="BW9" s="9" t="s">
-        <v>1475</v>
+        <v>1473</v>
       </c>
       <c r="BX9" s="9"/>
       <c r="BY9" s="9"/>
       <c r="BZ9" s="9"/>
       <c r="CA9" s="9" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="CB9" s="9"/>
       <c r="CC9" s="9" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="CD9" s="9"/>
       <c r="CE9" s="9" t="s">
-        <v>1477</v>
+        <v>1475</v>
       </c>
       <c r="CG9" s="19" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="CI9" s="19" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="CK9" s="19" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="CM9" s="19" t="s">
-        <v>1468</v>
+        <v>1466</v>
       </c>
       <c r="CO9" s="19" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="CS9" s="28" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="CT9" s="28"/>
       <c r="CU9" s="27" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="CV9" s="27"/>
       <c r="CW9" s="27"/>
       <c r="CX9" s="27"/>
       <c r="CY9" s="28" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="CZ9" s="28"/>
       <c r="DA9" s="28" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="DB9" s="28"/>
       <c r="DC9" s="28" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="DD9" s="28"/>
       <c r="DE9" s="28" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="DF9" s="27"/>
+      <c r="DG9" t="s">
+        <v>668</v>
+      </c>
     </row>
     <row r="10" spans="1:121" ht="16" x14ac:dyDescent="0.4">
       <c r="A10" s="20" t="s">
@@ -7588,7 +7716,7 @@
       </c>
       <c r="AH10" s="9"/>
       <c r="AI10" s="10" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="AJ10" s="9"/>
       <c r="AK10" s="9" t="s">
@@ -7611,24 +7739,24 @@
         <v>659</v>
       </c>
       <c r="AW10" s="12" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="BE10" t="s">
+        <v>1386</v>
+      </c>
+      <c r="BG10" s="9" t="s">
         <v>1387</v>
       </c>
-      <c r="BG10" s="9" t="s">
-        <v>1388</v>
-      </c>
       <c r="BK10" s="9" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="BL10" s="9"/>
       <c r="BM10" s="9" t="s">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="BN10" s="9"/>
       <c r="BO10" s="9" t="s">
-        <v>1479</v>
+        <v>1477</v>
       </c>
       <c r="BP10" s="9"/>
       <c r="BQ10" s="9" t="s">
@@ -7640,7 +7768,7 @@
       <c r="BU10" s="9"/>
       <c r="BV10" s="9"/>
       <c r="BW10" s="9" t="s">
-        <v>1480</v>
+        <v>1478</v>
       </c>
       <c r="BX10" s="9"/>
       <c r="BY10" s="9"/>
@@ -7657,19 +7785,19 @@
         <v>689</v>
       </c>
       <c r="CG10" s="19" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="CI10" s="19" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="CK10" s="19" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="CM10" s="19" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="CO10" s="19" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="CS10" s="27"/>
       <c r="CT10" s="27"/>
@@ -7678,19 +7806,19 @@
       <c r="CW10" s="27"/>
       <c r="CX10" s="27"/>
       <c r="CY10" s="28" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="CZ10" s="28"/>
       <c r="DA10" s="28" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="DB10" s="28"/>
       <c r="DC10" s="28" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="DD10" s="28"/>
       <c r="DE10" s="28" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="DF10" s="27"/>
     </row>
@@ -7730,14 +7858,14 @@
         <v>667</v>
       </c>
       <c r="AA11" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="AG11" s="9" t="s">
         <v>669</v>
       </c>
       <c r="AH11" s="9"/>
       <c r="AI11" s="10" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="AJ11" s="9"/>
       <c r="AK11" s="9" t="s">
@@ -7759,17 +7887,17 @@
         <v>667</v>
       </c>
       <c r="BE11" t="s">
+        <v>1390</v>
+      </c>
+      <c r="BG11" s="9" t="s">
         <v>1391</v>
       </c>
-      <c r="BG11" s="9" t="s">
-        <v>1392</v>
-      </c>
       <c r="BK11" s="9" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="BL11" s="9"/>
       <c r="BM11" s="9" t="s">
-        <v>1481</v>
+        <v>1479</v>
       </c>
       <c r="BN11" s="9"/>
       <c r="BO11" s="9"/>
@@ -7783,31 +7911,31 @@
       <c r="BU11" s="9"/>
       <c r="BV11" s="9"/>
       <c r="BW11" s="9" t="s">
-        <v>1482</v>
+        <v>1480</v>
       </c>
       <c r="BX11" s="9"/>
       <c r="BY11" s="9"/>
       <c r="BZ11" s="9"/>
       <c r="CA11" s="9" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="CB11" s="9"/>
       <c r="CC11" s="9"/>
       <c r="CD11" s="9"/>
       <c r="CE11" s="9" t="s">
-        <v>1483</v>
+        <v>1481</v>
       </c>
       <c r="CG11" s="19" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="CI11" s="19" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="CM11" s="19" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="CO11" s="19" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="CS11" s="27"/>
       <c r="CT11" s="27"/>
@@ -7816,19 +7944,19 @@
       <c r="CW11" s="27"/>
       <c r="CX11" s="27"/>
       <c r="CY11" s="28" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="CZ11" s="28"/>
       <c r="DA11" s="28" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="DB11" s="28"/>
       <c r="DC11" s="28" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="DD11" s="28"/>
       <c r="DE11" s="28" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="DF11" s="27"/>
     </row>
@@ -7875,7 +8003,7 @@
       </c>
       <c r="AH12" s="9"/>
       <c r="AI12" s="11" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="AJ12" s="9"/>
       <c r="AK12" s="9" t="s">
@@ -7898,7 +8026,7 @@
         <v>674</v>
       </c>
       <c r="BG12" s="9" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="BK12" s="9"/>
       <c r="BL12" s="9"/>
@@ -7915,7 +8043,7 @@
       <c r="BU12" s="9"/>
       <c r="BV12" s="9"/>
       <c r="BW12" s="9" t="s">
-        <v>1484</v>
+        <v>1482</v>
       </c>
       <c r="BX12" s="9"/>
       <c r="BY12" s="9"/>
@@ -7928,13 +8056,13 @@
       <c r="CD12" s="9"/>
       <c r="CE12" s="9"/>
       <c r="CG12" s="19" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="CI12" s="19" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="CO12" s="19" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="CS12" s="27"/>
       <c r="CT12" s="27"/>
@@ -7943,19 +8071,19 @@
       <c r="CW12" s="27"/>
       <c r="CX12" s="27"/>
       <c r="CY12" s="28" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="CZ12" s="28"/>
       <c r="DA12" s="28" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="DB12" s="28"/>
       <c r="DC12" s="28" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="DD12" s="28"/>
       <c r="DE12" s="28" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="DF12" s="27"/>
     </row>
@@ -8000,7 +8128,7 @@
       </c>
       <c r="AH13" s="9"/>
       <c r="AI13" s="10" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="AJ13" s="9"/>
       <c r="AK13" t="s">
@@ -8021,7 +8149,7 @@
         <v>681</v>
       </c>
       <c r="BG13" s="9" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="BK13" s="9"/>
       <c r="BL13" s="9"/>
@@ -8038,7 +8166,7 @@
       <c r="BU13" s="9"/>
       <c r="BV13" s="9"/>
       <c r="BW13" s="9" t="s">
-        <v>1485</v>
+        <v>1483</v>
       </c>
       <c r="BX13" s="9"/>
       <c r="BY13" s="9"/>
@@ -8051,13 +8179,13 @@
       <c r="CD13" s="9"/>
       <c r="CE13" s="9"/>
       <c r="CG13" s="19" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="CI13" s="19" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="CO13" s="19" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="CS13" s="27"/>
       <c r="CT13" s="27"/>
@@ -8066,19 +8194,19 @@
       <c r="CW13" s="27"/>
       <c r="CX13" s="27"/>
       <c r="CY13" s="28" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="CZ13" s="28"/>
       <c r="DA13" s="28" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="DB13" s="28"/>
       <c r="DC13" s="28" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="DD13" s="28"/>
       <c r="DE13" s="28" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="DF13" s="27"/>
     </row>
@@ -8123,7 +8251,7 @@
       </c>
       <c r="AH14" s="9"/>
       <c r="AI14" s="10" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="AJ14" s="9"/>
       <c r="AK14" s="9" t="s">
@@ -8146,7 +8274,7 @@
         <v>688</v>
       </c>
       <c r="BG14" s="9" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="BK14" s="9"/>
       <c r="BL14" s="9"/>
@@ -8163,7 +8291,7 @@
       <c r="BU14" s="9"/>
       <c r="BV14" s="9"/>
       <c r="BW14" s="9" t="s">
-        <v>1486</v>
+        <v>1484</v>
       </c>
       <c r="BX14" s="9"/>
       <c r="BY14" s="9"/>
@@ -8176,10 +8304,10 @@
       <c r="CD14" s="9"/>
       <c r="CE14" s="9"/>
       <c r="CG14" s="19" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="CI14" s="19" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="CO14" s="19" t="s">
         <v>733</v>
@@ -8191,19 +8319,19 @@
       <c r="CW14" s="27"/>
       <c r="CX14" s="27"/>
       <c r="CY14" s="28" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="CZ14" s="28"/>
       <c r="DA14" s="28" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="DB14" s="28"/>
       <c r="DC14" s="28" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="DD14" s="28"/>
       <c r="DE14" s="28" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="DF14" s="27"/>
     </row>
@@ -8249,7 +8377,7 @@
       </c>
       <c r="AH15" s="9"/>
       <c r="AI15" s="10" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="AJ15" s="9"/>
       <c r="AK15" s="9" t="s">
@@ -8272,7 +8400,7 @@
         <v>694</v>
       </c>
       <c r="BG15" s="9" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="BK15" s="9"/>
       <c r="BL15" s="9"/>
@@ -8289,7 +8417,7 @@
       <c r="BU15" s="9"/>
       <c r="BV15" s="9"/>
       <c r="BW15" s="9" t="s">
-        <v>1487</v>
+        <v>1485</v>
       </c>
       <c r="BX15" s="9"/>
       <c r="BY15" s="9"/>
@@ -8302,10 +8430,10 @@
       <c r="CD15" s="9"/>
       <c r="CE15" s="9"/>
       <c r="CG15" s="19" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="CI15" s="19" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="CS15" s="27"/>
       <c r="CT15" s="27"/>
@@ -8314,19 +8442,19 @@
       <c r="CW15" s="27"/>
       <c r="CX15" s="27"/>
       <c r="CY15" s="28" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="CZ15" s="28"/>
       <c r="DA15" s="28" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="DB15" s="28"/>
       <c r="DC15" s="28" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="DD15" s="28"/>
       <c r="DE15" s="28" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="DF15" s="27"/>
     </row>
@@ -8364,14 +8492,14 @@
         <v>700</v>
       </c>
       <c r="AA16" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="AG16" s="9" t="s">
         <v>701</v>
       </c>
       <c r="AH16" s="9"/>
       <c r="AI16" s="10" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="AJ16" s="9"/>
       <c r="AK16" t="s">
@@ -8392,7 +8520,7 @@
         <v>700</v>
       </c>
       <c r="BG16" s="9" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="BK16" s="9"/>
       <c r="BL16" s="9"/>
@@ -8409,20 +8537,20 @@
       <c r="BU16" s="9"/>
       <c r="BV16" s="9"/>
       <c r="BW16" s="9" t="s">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="BX16" s="9"/>
       <c r="BY16" s="9"/>
       <c r="BZ16" s="9"/>
       <c r="CA16" s="9" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="CB16" s="9"/>
       <c r="CC16" s="9"/>
       <c r="CD16" s="9"/>
       <c r="CE16" s="9"/>
       <c r="CG16" s="19" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="CS16" s="27"/>
       <c r="CT16" s="27"/>
@@ -8431,19 +8559,19 @@
       <c r="CW16" s="27"/>
       <c r="CX16" s="27"/>
       <c r="CY16" s="28" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="CZ16" s="28"/>
       <c r="DA16" s="28" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="DB16" s="28"/>
       <c r="DC16" s="28" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="DD16" s="28"/>
       <c r="DE16" s="28" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="DF16" s="27"/>
     </row>
@@ -8488,7 +8616,7 @@
       </c>
       <c r="AH17" s="9"/>
       <c r="AI17" s="10" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="AJ17" s="9"/>
       <c r="AK17" s="9" t="s">
@@ -8511,7 +8639,7 @@
         <v>706</v>
       </c>
       <c r="BG17" s="9" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="BK17" s="9"/>
       <c r="BL17" s="9"/>
@@ -8528,7 +8656,7 @@
       <c r="BU17" s="9"/>
       <c r="BV17" s="9"/>
       <c r="BW17" s="9" t="s">
-        <v>1489</v>
+        <v>1487</v>
       </c>
       <c r="BX17" s="9"/>
       <c r="BY17" s="9"/>
@@ -8539,7 +8667,7 @@
       <c r="CD17" s="9"/>
       <c r="CE17" s="9"/>
       <c r="CG17" s="19" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="CS17" s="27"/>
       <c r="CT17" s="27"/>
@@ -8548,19 +8676,19 @@
       <c r="CW17" s="27"/>
       <c r="CX17" s="27"/>
       <c r="CY17" s="28" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="CZ17" s="28"/>
       <c r="DA17" s="28" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="DB17" s="28"/>
       <c r="DC17" s="28" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="DD17" s="28"/>
       <c r="DE17" s="28" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="DF17" s="27"/>
     </row>
@@ -8605,7 +8733,7 @@
       </c>
       <c r="AH18" s="9"/>
       <c r="AI18" s="10" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="AJ18" s="9"/>
       <c r="AK18" t="s">
@@ -8627,7 +8755,7 @@
         <v>711</v>
       </c>
       <c r="BG18" s="9" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="BK18" s="9"/>
       <c r="BL18" s="9"/>
@@ -8644,7 +8772,7 @@
       <c r="BU18" s="9"/>
       <c r="BV18" s="9"/>
       <c r="BW18" s="9" t="s">
-        <v>1490</v>
+        <v>1488</v>
       </c>
       <c r="BX18" s="9"/>
       <c r="BY18" s="9"/>
@@ -8655,7 +8783,7 @@
       <c r="CD18" s="9"/>
       <c r="CE18" s="9"/>
       <c r="CG18" s="19" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="CS18" s="27"/>
       <c r="CT18" s="27"/>
@@ -8664,19 +8792,19 @@
       <c r="CW18" s="27"/>
       <c r="CX18" s="27"/>
       <c r="CY18" s="28" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="CZ18" s="28"/>
       <c r="DA18" s="28" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="DB18" s="28"/>
       <c r="DC18" s="28" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="DD18" s="28"/>
       <c r="DE18" s="28" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="DF18" s="27"/>
     </row>
@@ -8721,7 +8849,7 @@
       </c>
       <c r="AH19" s="9"/>
       <c r="AI19" s="10" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="AJ19" s="9"/>
       <c r="AK19" s="9" t="s">
@@ -8743,7 +8871,7 @@
         <v>716</v>
       </c>
       <c r="BG19" s="9" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="BK19" s="9"/>
       <c r="BL19" s="9"/>
@@ -8760,7 +8888,7 @@
       <c r="BU19" s="9"/>
       <c r="BV19" s="9"/>
       <c r="BW19" s="9" t="s">
-        <v>1491</v>
+        <v>1489</v>
       </c>
       <c r="BX19" s="9"/>
       <c r="BY19" s="9"/>
@@ -8771,7 +8899,7 @@
       <c r="CD19" s="9"/>
       <c r="CE19" s="9"/>
       <c r="CG19" s="19" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="CS19" s="27"/>
       <c r="CT19" s="27"/>
@@ -8780,19 +8908,19 @@
       <c r="CW19" s="27"/>
       <c r="CX19" s="27"/>
       <c r="CY19" s="28" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="CZ19" s="28"/>
       <c r="DA19" s="28" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="DB19" s="28"/>
       <c r="DC19" s="28" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="DD19" s="28"/>
       <c r="DE19" s="28" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="DF19" s="27"/>
     </row>
@@ -8837,7 +8965,7 @@
       </c>
       <c r="AH20" s="9"/>
       <c r="AI20" s="10" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="AJ20" s="9"/>
       <c r="AK20" t="s">
@@ -8872,7 +9000,7 @@
       <c r="BU20" s="9"/>
       <c r="BV20" s="9"/>
       <c r="BW20" s="9" t="s">
-        <v>1492</v>
+        <v>1490</v>
       </c>
       <c r="BX20" s="9"/>
       <c r="BY20" s="9"/>
@@ -8883,7 +9011,7 @@
       <c r="CD20" s="9"/>
       <c r="CE20" s="9"/>
       <c r="CG20" s="19" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="CS20" s="27"/>
       <c r="CT20" s="27"/>
@@ -8892,19 +9020,19 @@
       <c r="CW20" s="27"/>
       <c r="CX20" s="27"/>
       <c r="CY20" s="28" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="CZ20" s="28"/>
       <c r="DA20" s="28" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="DB20" s="28"/>
       <c r="DC20" s="28" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="DD20" s="28"/>
       <c r="DE20" s="28" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="DF20" s="27"/>
     </row>
@@ -8947,7 +9075,7 @@
       </c>
       <c r="AH21" s="9"/>
       <c r="AI21" s="10" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="AJ21" s="9"/>
       <c r="AK21" s="9" t="s">
@@ -8984,7 +9112,7 @@
       <c r="BU21" s="9"/>
       <c r="BV21" s="9"/>
       <c r="BW21" s="9" t="s">
-        <v>1493</v>
+        <v>1491</v>
       </c>
       <c r="BX21" s="9"/>
       <c r="BY21" s="9"/>
@@ -8995,7 +9123,7 @@
       <c r="CD21" s="9"/>
       <c r="CE21" s="9"/>
       <c r="CG21" s="19" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="CS21" s="27"/>
       <c r="CT21" s="27"/>
@@ -9004,19 +9132,19 @@
       <c r="CW21" s="27"/>
       <c r="CX21" s="27"/>
       <c r="CY21" s="28" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="CZ21" s="28"/>
       <c r="DA21" s="28" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="DB21" s="28"/>
       <c r="DC21" s="28" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="DD21" s="28"/>
       <c r="DE21" s="28" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="DF21" s="27"/>
     </row>
@@ -9056,7 +9184,7 @@
       </c>
       <c r="AH22" s="9"/>
       <c r="AI22" s="10" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="AJ22" s="9"/>
       <c r="AK22" s="9" t="s">
@@ -9067,10 +9195,10 @@
         <v>736</v>
       </c>
       <c r="AO22" t="s">
+        <v>1849</v>
+      </c>
+      <c r="AQ22" s="9" t="s">
         <v>737</v>
-      </c>
-      <c r="AQ22" s="9" t="s">
-        <v>738</v>
       </c>
       <c r="AS22" s="12"/>
       <c r="AT22" s="12"/>
@@ -9092,7 +9220,7 @@
       <c r="BU22" s="9"/>
       <c r="BV22" s="9"/>
       <c r="BW22" s="9" t="s">
-        <v>1494</v>
+        <v>1492</v>
       </c>
       <c r="BX22" s="9"/>
       <c r="BY22" s="9"/>
@@ -9109,19 +9237,19 @@
       <c r="CW22" s="27"/>
       <c r="CX22" s="27"/>
       <c r="CY22" s="28" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="CZ22" s="28"/>
       <c r="DA22" s="28" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="DB22" s="28"/>
       <c r="DC22" s="28" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="DD22" s="28"/>
       <c r="DE22" s="28" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="DF22" s="27"/>
     </row>
@@ -9154,25 +9282,25 @@
       <c r="R23" s="12"/>
       <c r="S23" s="12"/>
       <c r="AG23" s="9" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AH23" s="9"/>
       <c r="AI23" s="10" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="AJ23" s="9"/>
       <c r="AK23" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AM23" s="9" t="s">
         <v>696</v>
       </c>
       <c r="AN23" s="9"/>
       <c r="AO23" t="s">
+        <v>740</v>
+      </c>
+      <c r="AQ23" s="9" t="s">
         <v>741</v>
-      </c>
-      <c r="AQ23" s="9" t="s">
-        <v>742</v>
       </c>
       <c r="BK23" s="9"/>
       <c r="BL23" s="9"/>
@@ -9181,7 +9309,7 @@
       <c r="BO23" s="9"/>
       <c r="BP23" s="9"/>
       <c r="BQ23" s="9" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="BR23" s="9"/>
       <c r="BS23" s="9"/>
@@ -9189,7 +9317,7 @@
       <c r="BU23" s="9"/>
       <c r="BV23" s="9"/>
       <c r="BW23" s="9" t="s">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="BX23" s="9"/>
       <c r="BY23" s="9"/>
@@ -9206,19 +9334,19 @@
       <c r="CW23" s="27"/>
       <c r="CX23" s="27"/>
       <c r="CY23" s="28" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="CZ23" s="28"/>
       <c r="DA23" s="28" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="DB23" s="28"/>
       <c r="DC23" s="28" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="DD23" s="28"/>
       <c r="DE23" s="28" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="DF23" s="27"/>
     </row>
@@ -9251,21 +9379,21 @@
       <c r="R24" s="12"/>
       <c r="S24" s="12"/>
       <c r="AG24" s="9" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AH24" s="9"/>
       <c r="AI24" s="10" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="AJ24" s="9"/>
       <c r="AK24" t="s">
+        <v>744</v>
+      </c>
+      <c r="AM24" t="s">
         <v>745</v>
       </c>
-      <c r="AM24" t="s">
+      <c r="AQ24" s="9" t="s">
         <v>746</v>
-      </c>
-      <c r="AQ24" s="9" t="s">
-        <v>747</v>
       </c>
       <c r="BK24" s="9"/>
       <c r="BL24" s="9"/>
@@ -9274,7 +9402,7 @@
       <c r="BO24" s="9"/>
       <c r="BP24" s="9"/>
       <c r="BQ24" s="9" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="BR24" s="9"/>
       <c r="BS24" s="9"/>
@@ -9282,7 +9410,7 @@
       <c r="BU24" s="9"/>
       <c r="BV24" s="9"/>
       <c r="BW24" s="9" t="s">
-        <v>1496</v>
+        <v>1494</v>
       </c>
       <c r="BX24" s="9"/>
       <c r="BY24" s="9"/>
@@ -9299,19 +9427,19 @@
       <c r="CW24" s="27"/>
       <c r="CX24" s="27"/>
       <c r="CY24" s="28" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="CZ24" s="28"/>
       <c r="DA24" s="28" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="DB24" s="28"/>
       <c r="DC24" s="28" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="DD24" s="28"/>
       <c r="DE24" s="28" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="DF24" s="27"/>
     </row>
@@ -9344,22 +9472,22 @@
       <c r="R25" s="12"/>
       <c r="S25" s="12"/>
       <c r="AG25" s="9" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AH25" s="9"/>
       <c r="AI25" s="10" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="AJ25" s="9"/>
       <c r="AK25" t="s">
+        <v>748</v>
+      </c>
+      <c r="AM25" s="9" t="s">
         <v>749</v>
-      </c>
-      <c r="AM25" s="9" t="s">
-        <v>750</v>
       </c>
       <c r="AN25" s="9"/>
       <c r="AQ25" s="9" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="BK25" s="9"/>
       <c r="BL25" s="9"/>
@@ -9368,7 +9496,7 @@
       <c r="BO25" s="9"/>
       <c r="BP25" s="9"/>
       <c r="BQ25" s="9" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="BR25" s="9"/>
       <c r="BS25" s="9"/>
@@ -9393,19 +9521,19 @@
       <c r="CW25" s="27"/>
       <c r="CX25" s="27"/>
       <c r="CY25" s="28" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="CZ25" s="28"/>
       <c r="DA25" s="28" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="DB25" s="28"/>
       <c r="DC25" s="28" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="DD25" s="28"/>
       <c r="DE25" s="28" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="DF25" s="27"/>
     </row>
@@ -9438,15 +9566,15 @@
       <c r="R26" s="12"/>
       <c r="S26" s="12"/>
       <c r="AG26" s="9" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AH26" s="9"/>
       <c r="AI26" s="10" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AJ26" s="9"/>
       <c r="AK26" s="9" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AL26" s="9"/>
       <c r="AM26" s="9" t="s">
@@ -9454,7 +9582,7 @@
       </c>
       <c r="AN26" s="9"/>
       <c r="AQ26" s="9" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="BK26" s="9"/>
       <c r="BL26" s="9"/>
@@ -9463,7 +9591,7 @@
       <c r="BO26" s="9"/>
       <c r="BP26" s="9"/>
       <c r="BQ26" s="9" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="BR26" s="9"/>
       <c r="BS26" s="9"/>
@@ -9471,7 +9599,7 @@
       <c r="BU26" s="9"/>
       <c r="BV26" s="9"/>
       <c r="BW26" s="9" t="s">
-        <v>1497</v>
+        <v>1495</v>
       </c>
       <c r="BX26" s="9"/>
       <c r="BY26" s="9"/>
@@ -9488,19 +9616,19 @@
       <c r="CW26" s="27"/>
       <c r="CX26" s="27"/>
       <c r="CY26" s="28" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="CZ26" s="28"/>
       <c r="DA26" s="28" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="DB26" s="28"/>
       <c r="DC26" s="28" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="DD26" s="28"/>
       <c r="DE26" s="28" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="DF26" s="27"/>
     </row>
@@ -9533,21 +9661,21 @@
       <c r="R27" s="12"/>
       <c r="S27" s="12"/>
       <c r="AG27" s="9" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="AH27" s="9"/>
       <c r="AI27" s="10" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="AK27" s="9" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AL27" s="9"/>
       <c r="AM27" t="s">
+        <v>756</v>
+      </c>
+      <c r="AQ27" s="9" t="s">
         <v>757</v>
-      </c>
-      <c r="AQ27" s="9" t="s">
-        <v>758</v>
       </c>
       <c r="BK27" s="9"/>
       <c r="BL27" s="9"/>
@@ -9556,7 +9684,7 @@
       <c r="BO27" s="9"/>
       <c r="BP27" s="9"/>
       <c r="BQ27" s="9" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="BR27" s="9"/>
       <c r="BS27" s="9"/>
@@ -9564,7 +9692,7 @@
       <c r="BU27" s="9"/>
       <c r="BV27" s="9"/>
       <c r="BW27" s="9" t="s">
-        <v>1498</v>
+        <v>1496</v>
       </c>
       <c r="BX27" s="9"/>
       <c r="BY27" s="9"/>
@@ -9581,19 +9709,19 @@
       <c r="CW27" s="27"/>
       <c r="CX27" s="27"/>
       <c r="CY27" s="28" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="CZ27" s="28"/>
       <c r="DA27" s="28" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="DB27" s="28"/>
       <c r="DC27" s="28" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="DD27" s="28"/>
       <c r="DE27" s="28" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="DF27" s="27"/>
     </row>
@@ -9626,21 +9754,21 @@
       <c r="R28" s="12"/>
       <c r="S28" s="12"/>
       <c r="AG28" s="9" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="AH28" s="9"/>
       <c r="AI28" s="10" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="AK28" s="9" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AL28" s="9"/>
       <c r="AM28" t="s">
+        <v>760</v>
+      </c>
+      <c r="AQ28" s="9" t="s">
         <v>761</v>
-      </c>
-      <c r="AQ28" s="9" t="s">
-        <v>762</v>
       </c>
       <c r="BK28" s="9"/>
       <c r="BL28" s="9"/>
@@ -9649,7 +9777,7 @@
       <c r="BO28" s="9"/>
       <c r="BP28" s="9"/>
       <c r="BQ28" s="9" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="BR28" s="9"/>
       <c r="BS28" s="9"/>
@@ -9657,7 +9785,7 @@
       <c r="BU28" s="9"/>
       <c r="BV28" s="9"/>
       <c r="BW28" s="9" t="s">
-        <v>1499</v>
+        <v>1497</v>
       </c>
       <c r="BX28" s="9"/>
       <c r="BY28" s="9"/>
@@ -9674,19 +9802,19 @@
       <c r="CW28" s="27"/>
       <c r="CX28" s="27"/>
       <c r="CY28" s="28" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="CZ28" s="28"/>
       <c r="DA28" s="28" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="DB28" s="28"/>
       <c r="DC28" s="28" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="DD28" s="28"/>
       <c r="DE28" s="28" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="DF28" s="27"/>
     </row>
@@ -9719,20 +9847,20 @@
       <c r="R29" s="12"/>
       <c r="S29" s="12"/>
       <c r="AG29" s="9" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AH29" s="9"/>
       <c r="AI29" s="10" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="AK29" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AM29" t="s">
         <v>724</v>
       </c>
       <c r="AQ29" s="9" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="BK29" s="9"/>
       <c r="BL29" s="9"/>
@@ -9741,7 +9869,7 @@
       <c r="BO29" s="9"/>
       <c r="BP29" s="9"/>
       <c r="BQ29" s="9" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="BR29" s="9"/>
       <c r="BS29" s="9"/>
@@ -9749,7 +9877,7 @@
       <c r="BU29" s="9"/>
       <c r="BV29" s="9"/>
       <c r="BW29" s="9" t="s">
-        <v>1500</v>
+        <v>1498</v>
       </c>
       <c r="BX29" s="9"/>
       <c r="BY29" s="9"/>
@@ -9766,19 +9894,19 @@
       <c r="CW29" s="27"/>
       <c r="CX29" s="27"/>
       <c r="CY29" s="28" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="CZ29" s="28"/>
       <c r="DA29" s="28" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="DB29" s="28"/>
       <c r="DC29" s="28" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="DD29" s="28"/>
       <c r="DE29" s="28" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="DF29" s="27"/>
     </row>
@@ -9811,21 +9939,21 @@
       <c r="R30" s="12"/>
       <c r="S30" s="12"/>
       <c r="AG30" s="9" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AH30" s="9"/>
       <c r="AI30" s="11" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="AK30" s="9" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AL30" s="9"/>
       <c r="AM30" t="s">
+        <v>767</v>
+      </c>
+      <c r="AQ30" s="9" t="s">
         <v>768</v>
-      </c>
-      <c r="AQ30" s="9" t="s">
-        <v>769</v>
       </c>
       <c r="BK30" s="9"/>
       <c r="BL30" s="9"/>
@@ -9834,7 +9962,7 @@
       <c r="BO30" s="9"/>
       <c r="BP30" s="9"/>
       <c r="BQ30" s="9" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="BR30" s="9"/>
       <c r="BS30" s="9"/>
@@ -9842,7 +9970,7 @@
       <c r="BU30" s="9"/>
       <c r="BV30" s="9"/>
       <c r="BW30" s="9" t="s">
-        <v>1501</v>
+        <v>1499</v>
       </c>
       <c r="BX30" s="9"/>
       <c r="BY30" s="9"/>
@@ -9859,19 +9987,19 @@
       <c r="CW30" s="27"/>
       <c r="CX30" s="27"/>
       <c r="CY30" s="28" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="CZ30" s="28"/>
       <c r="DA30" s="28" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="DB30" s="28"/>
       <c r="DC30" s="28" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="DD30" s="28"/>
       <c r="DE30" s="28" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="DF30" s="27"/>
     </row>
@@ -9904,14 +10032,14 @@
       <c r="R31" s="12"/>
       <c r="S31" s="12"/>
       <c r="AG31" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AH31" s="9"/>
       <c r="AI31" s="10" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="AK31" s="9" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="AL31" s="9"/>
       <c r="AM31" s="9" t="s">
@@ -9919,7 +10047,7 @@
       </c>
       <c r="AN31" s="9"/>
       <c r="AQ31" s="9" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="BK31" s="9"/>
       <c r="BL31" s="9"/>
@@ -9928,7 +10056,7 @@
       <c r="BO31" s="9"/>
       <c r="BP31" s="9"/>
       <c r="BQ31" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="BR31" s="9"/>
       <c r="BS31" s="9"/>
@@ -9936,7 +10064,7 @@
       <c r="BU31" s="9"/>
       <c r="BV31" s="9"/>
       <c r="BW31" s="9" t="s">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="BX31" s="9"/>
       <c r="BY31" s="9"/>
@@ -9953,19 +10081,19 @@
       <c r="CW31" s="27"/>
       <c r="CX31" s="27"/>
       <c r="CY31" s="28" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="CZ31" s="28"/>
       <c r="DA31" s="28" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="DB31" s="28"/>
       <c r="DC31" s="28" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="DD31" s="28"/>
       <c r="DE31" s="28" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="DF31" s="27"/>
     </row>
@@ -9998,21 +10126,21 @@
       <c r="R32" s="12"/>
       <c r="S32" s="12"/>
       <c r="AG32" s="9" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="AH32" s="9"/>
       <c r="AI32" s="9" t="s">
-        <v>1768</v>
+        <v>1766</v>
       </c>
       <c r="AK32" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AM32" s="9" t="s">
         <v>735</v>
       </c>
       <c r="AN32" s="9"/>
       <c r="AQ32" s="9" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="BK32" s="9"/>
       <c r="BL32" s="9"/>
@@ -10021,7 +10149,7 @@
       <c r="BO32" s="9"/>
       <c r="BP32" s="9"/>
       <c r="BQ32" s="9" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="BR32" s="9"/>
       <c r="BS32" s="9"/>
@@ -10029,7 +10157,7 @@
       <c r="BU32" s="9"/>
       <c r="BV32" s="9"/>
       <c r="BW32" s="9" t="s">
-        <v>1503</v>
+        <v>1501</v>
       </c>
       <c r="BX32" s="9"/>
       <c r="BY32" s="9"/>
@@ -10046,19 +10174,19 @@
       <c r="CW32" s="27"/>
       <c r="CX32" s="27"/>
       <c r="CY32" s="28" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="CZ32" s="28"/>
       <c r="DA32" s="28" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="DB32" s="28"/>
       <c r="DC32" s="28" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="DD32" s="28"/>
       <c r="DE32" s="28" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="DF32" s="27"/>
     </row>
@@ -10091,21 +10219,21 @@
       <c r="R33" s="12"/>
       <c r="S33" s="12"/>
       <c r="AG33" s="9" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="AH33" s="9"/>
       <c r="AI33" s="9" t="s">
-        <v>1769</v>
+        <v>1767</v>
       </c>
       <c r="AK33" s="9" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AL33" s="9"/>
       <c r="AM33" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AQ33" s="9" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="BK33" s="9"/>
       <c r="BL33" s="9"/>
@@ -10114,7 +10242,7 @@
       <c r="BO33" s="9"/>
       <c r="BP33" s="9"/>
       <c r="BQ33" s="9" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="BR33" s="9"/>
       <c r="BS33" s="9"/>
@@ -10122,7 +10250,7 @@
       <c r="BU33" s="9"/>
       <c r="BV33" s="9"/>
       <c r="BW33" s="9" t="s">
-        <v>1504</v>
+        <v>1502</v>
       </c>
       <c r="BX33" s="9"/>
       <c r="BY33" s="9"/>
@@ -10139,19 +10267,19 @@
       <c r="CW33" s="27"/>
       <c r="CX33" s="27"/>
       <c r="CY33" s="28" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="CZ33" s="28"/>
       <c r="DA33" s="28" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="DB33" s="28"/>
       <c r="DC33" s="28" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="DD33" s="28"/>
       <c r="DE33" s="28" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="DF33" s="27"/>
     </row>
@@ -10184,22 +10312,22 @@
       <c r="R34" s="12"/>
       <c r="S34" s="12"/>
       <c r="AG34" s="9" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="AH34" s="9"/>
       <c r="AI34" s="9" t="s">
-        <v>1770</v>
+        <v>1768</v>
       </c>
       <c r="AK34" s="9" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AL34" s="9"/>
       <c r="AM34" s="9" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AN34" s="9"/>
       <c r="AQ34" s="9" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="BK34" s="9"/>
       <c r="BL34" s="9"/>
@@ -10208,7 +10336,7 @@
       <c r="BO34" s="9"/>
       <c r="BP34" s="9"/>
       <c r="BQ34" s="9" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="BR34" s="9"/>
       <c r="BS34" s="9"/>
@@ -10216,7 +10344,7 @@
       <c r="BU34" s="9"/>
       <c r="BV34" s="9"/>
       <c r="BW34" s="9" t="s">
-        <v>1505</v>
+        <v>1503</v>
       </c>
       <c r="BX34" s="9"/>
       <c r="BY34" s="9"/>
@@ -10233,19 +10361,19 @@
       <c r="CW34" s="27"/>
       <c r="CX34" s="27"/>
       <c r="CY34" s="28" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="CZ34" s="28"/>
       <c r="DA34" s="28" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="DB34" s="28"/>
       <c r="DC34" s="28" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="DD34" s="28"/>
       <c r="DE34" s="28" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="DF34" s="27"/>
     </row>
@@ -10278,22 +10406,22 @@
       <c r="R35" s="12"/>
       <c r="S35" s="12"/>
       <c r="AG35" s="9" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AH35" s="9"/>
       <c r="AI35" s="30" t="s">
-        <v>1771</v>
+        <v>1769</v>
       </c>
       <c r="AK35" s="9" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AL35" s="9"/>
       <c r="AM35" s="9" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="AN35" s="9"/>
       <c r="AQ35" s="9" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="BK35" s="9"/>
       <c r="BL35" s="9"/>
@@ -10302,7 +10430,7 @@
       <c r="BO35" s="9"/>
       <c r="BP35" s="9"/>
       <c r="BQ35" s="9" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="BR35" s="9"/>
       <c r="BS35" s="9"/>
@@ -10310,7 +10438,7 @@
       <c r="BU35" s="9"/>
       <c r="BV35" s="9"/>
       <c r="BW35" s="9" t="s">
-        <v>1506</v>
+        <v>1504</v>
       </c>
       <c r="BX35" s="9"/>
       <c r="BY35" s="9"/>
@@ -10327,19 +10455,19 @@
       <c r="CW35" s="27"/>
       <c r="CX35" s="27"/>
       <c r="CY35" s="28" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="CZ35" s="28"/>
       <c r="DA35" s="28" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="DB35" s="28"/>
       <c r="DC35" s="28" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="DD35" s="28"/>
       <c r="DE35" s="28" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="DF35" s="27"/>
     </row>
@@ -10368,22 +10496,22 @@
       <c r="R36" s="12"/>
       <c r="S36" s="12"/>
       <c r="AG36" s="9" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AH36" s="9"/>
       <c r="AI36" s="9" t="s">
-        <v>1772</v>
+        <v>1770</v>
       </c>
       <c r="AK36" s="9" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AL36" s="9"/>
       <c r="AM36" s="9" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="AN36" s="9"/>
       <c r="AQ36" s="9" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="BK36" s="9"/>
       <c r="BL36" s="9"/>
@@ -10392,7 +10520,7 @@
       <c r="BO36" s="9"/>
       <c r="BP36" s="9"/>
       <c r="BQ36" s="9" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="BR36" s="9"/>
       <c r="BS36" s="9"/>
@@ -10400,7 +10528,7 @@
       <c r="BU36" s="9"/>
       <c r="BV36" s="9"/>
       <c r="BW36" s="9" t="s">
-        <v>1507</v>
+        <v>1505</v>
       </c>
       <c r="BX36" s="9"/>
       <c r="BY36" s="9"/>
@@ -10417,19 +10545,19 @@
       <c r="CW36" s="27"/>
       <c r="CX36" s="27"/>
       <c r="CY36" s="28" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="CZ36" s="28"/>
       <c r="DA36" s="28" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="DB36" s="28"/>
       <c r="DC36" s="28" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="DD36" s="28"/>
       <c r="DE36" s="28" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="DF36" s="27"/>
     </row>
@@ -10458,20 +10586,20 @@
       <c r="R37" s="12"/>
       <c r="S37" s="12"/>
       <c r="AG37" s="9" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AH37" s="9"/>
       <c r="AI37" s="9" t="s">
-        <v>1773</v>
+        <v>1771</v>
       </c>
       <c r="AK37" t="s">
+        <v>789</v>
+      </c>
+      <c r="AM37" t="s">
+        <v>763</v>
+      </c>
+      <c r="AQ37" s="9" t="s">
         <v>790</v>
-      </c>
-      <c r="AM37" t="s">
-        <v>764</v>
-      </c>
-      <c r="AQ37" s="9" t="s">
-        <v>791</v>
       </c>
       <c r="BK37" s="9"/>
       <c r="BL37" s="9"/>
@@ -10480,7 +10608,7 @@
       <c r="BO37" s="9"/>
       <c r="BP37" s="9"/>
       <c r="BQ37" s="9" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="BR37" s="9"/>
       <c r="BS37" s="9"/>
@@ -10488,7 +10616,7 @@
       <c r="BU37" s="9"/>
       <c r="BV37" s="9"/>
       <c r="BW37" s="9" t="s">
-        <v>1508</v>
+        <v>1506</v>
       </c>
       <c r="BX37" s="9"/>
       <c r="BY37" s="9"/>
@@ -10505,19 +10633,19 @@
       <c r="CW37" s="27"/>
       <c r="CX37" s="27"/>
       <c r="CY37" s="28" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="CZ37" s="28"/>
       <c r="DA37" s="28" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="DB37" s="28"/>
       <c r="DC37" s="28" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="DD37" s="28"/>
       <c r="DE37" s="28" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="DF37" s="27"/>
     </row>
@@ -10546,22 +10674,22 @@
       <c r="R38" s="12"/>
       <c r="S38" s="12"/>
       <c r="AG38" s="9" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="AH38" s="9"/>
       <c r="AI38" s="9" t="s">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="AK38" s="9" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AL38" s="9"/>
       <c r="AM38" s="9" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="AN38" s="9"/>
       <c r="AQ38" s="9" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="BK38" s="9"/>
       <c r="BL38" s="9"/>
@@ -10570,7 +10698,7 @@
       <c r="BO38" s="9"/>
       <c r="BP38" s="9"/>
       <c r="BQ38" s="9" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="BR38" s="9"/>
       <c r="BS38" s="9"/>
@@ -10578,7 +10706,7 @@
       <c r="BU38" s="9"/>
       <c r="BV38" s="9"/>
       <c r="BW38" s="9" t="s">
-        <v>1509</v>
+        <v>1507</v>
       </c>
       <c r="BX38" s="9"/>
       <c r="BY38" s="9"/>
@@ -10595,19 +10723,19 @@
       <c r="CW38" s="27"/>
       <c r="CX38" s="27"/>
       <c r="CY38" s="28" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="CZ38" s="28"/>
       <c r="DA38" s="28" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="DB38" s="28"/>
       <c r="DC38" s="28" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="DD38" s="28"/>
       <c r="DE38" s="28" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="DF38" s="27"/>
     </row>
@@ -10636,21 +10764,21 @@
       <c r="R39" s="12"/>
       <c r="S39" s="12"/>
       <c r="AG39" s="9" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="AH39" s="9"/>
       <c r="AI39" s="9" t="s">
-        <v>1775</v>
+        <v>1773</v>
       </c>
       <c r="AK39" s="9" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AL39" s="9"/>
       <c r="AM39" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AQ39" s="9" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="BK39" s="9"/>
       <c r="BL39" s="9"/>
@@ -10659,7 +10787,7 @@
       <c r="BO39" s="9"/>
       <c r="BP39" s="9"/>
       <c r="BQ39" s="9" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="BR39" s="9"/>
       <c r="BS39" s="9"/>
@@ -10667,7 +10795,7 @@
       <c r="BU39" s="9"/>
       <c r="BV39" s="9"/>
       <c r="BW39" s="9" t="s">
-        <v>1510</v>
+        <v>1508</v>
       </c>
       <c r="BX39" s="9"/>
       <c r="BY39" s="9"/>
@@ -10684,19 +10812,19 @@
       <c r="CW39" s="27"/>
       <c r="CX39" s="27"/>
       <c r="CY39" s="28" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="CZ39" s="28"/>
       <c r="DA39" s="28" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="DB39" s="28"/>
       <c r="DC39" s="28" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="DD39" s="28"/>
       <c r="DE39" s="28" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="DF39" s="27"/>
     </row>
@@ -10725,18 +10853,18 @@
       <c r="R40" s="12"/>
       <c r="S40" s="12"/>
       <c r="AG40" s="9" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AH40" s="9"/>
       <c r="AI40" s="9" t="s">
-        <v>1776</v>
+        <v>1774</v>
       </c>
       <c r="AM40" s="9" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="AN40" s="9"/>
       <c r="AQ40" s="9" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="BK40" s="9"/>
       <c r="BL40" s="9"/>
@@ -10745,7 +10873,7 @@
       <c r="BO40" s="9"/>
       <c r="BP40" s="9"/>
       <c r="BQ40" s="9" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="BR40" s="9"/>
       <c r="BS40" s="9"/>
@@ -10753,7 +10881,7 @@
       <c r="BU40" s="9"/>
       <c r="BV40" s="9"/>
       <c r="BW40" s="9" t="s">
-        <v>1511</v>
+        <v>1509</v>
       </c>
       <c r="BX40" s="9"/>
       <c r="BY40" s="9"/>
@@ -10770,19 +10898,19 @@
       <c r="CW40" s="27"/>
       <c r="CX40" s="27"/>
       <c r="CY40" s="28" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="CZ40" s="28"/>
       <c r="DA40" s="28" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="DB40" s="28"/>
       <c r="DC40" s="28" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="DD40" s="28"/>
       <c r="DE40" s="28" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="DF40" s="27"/>
     </row>
@@ -10811,18 +10939,18 @@
       <c r="R41" s="12"/>
       <c r="S41" s="12"/>
       <c r="AG41" s="9" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="AH41" s="9"/>
       <c r="AI41" s="9" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="AM41" s="9" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AN41" s="9"/>
       <c r="AQ41" s="9" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="BK41" s="9"/>
       <c r="BL41" s="9"/>
@@ -10831,7 +10959,7 @@
       <c r="BO41" s="9"/>
       <c r="BP41" s="9"/>
       <c r="BQ41" s="9" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="BR41" s="9"/>
       <c r="BS41" s="9"/>
@@ -10839,7 +10967,7 @@
       <c r="BU41" s="9"/>
       <c r="BV41" s="9"/>
       <c r="BW41" s="9" t="s">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="BX41" s="9"/>
       <c r="BY41" s="9"/>
@@ -10856,19 +10984,19 @@
       <c r="CW41" s="27"/>
       <c r="CX41" s="27"/>
       <c r="CY41" s="28" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="CZ41" s="28"/>
       <c r="DA41" s="28" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="DB41" s="28"/>
       <c r="DC41" s="28" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="DD41" s="28"/>
       <c r="DE41" s="28" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="DF41" s="27"/>
     </row>
@@ -10897,18 +11025,18 @@
       <c r="R42" s="12"/>
       <c r="S42" s="12"/>
       <c r="AG42" s="9" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="AH42" s="9"/>
       <c r="AI42" s="9" t="s">
-        <v>1778</v>
+        <v>1776</v>
       </c>
       <c r="AM42" s="9" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AN42" s="9"/>
       <c r="AQ42" s="9" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="BK42" s="9"/>
       <c r="BL42" s="9"/>
@@ -10917,7 +11045,7 @@
       <c r="BO42" s="9"/>
       <c r="BP42" s="9"/>
       <c r="BQ42" s="9" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="BR42" s="9"/>
       <c r="BS42" s="9"/>
@@ -10925,7 +11053,7 @@
       <c r="BU42" s="9"/>
       <c r="BV42" s="9"/>
       <c r="BW42" s="9" t="s">
-        <v>1513</v>
+        <v>1511</v>
       </c>
       <c r="BX42" s="9"/>
       <c r="BY42" s="9"/>
@@ -10942,19 +11070,19 @@
       <c r="CW42" s="27"/>
       <c r="CX42" s="27"/>
       <c r="CY42" s="28" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="CZ42" s="28"/>
       <c r="DA42" s="28" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="DB42" s="28"/>
       <c r="DC42" s="28" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="DD42" s="28"/>
       <c r="DE42" s="28" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="DF42" s="27"/>
     </row>
@@ -10983,17 +11111,17 @@
       <c r="R43" s="12"/>
       <c r="S43" s="12"/>
       <c r="AG43" s="9" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="AH43" s="9"/>
       <c r="AI43" s="9" t="s">
-        <v>1779</v>
+        <v>1777</v>
       </c>
       <c r="AM43" t="s">
+        <v>806</v>
+      </c>
+      <c r="AQ43" s="9" t="s">
         <v>807</v>
-      </c>
-      <c r="AQ43" s="9" t="s">
-        <v>808</v>
       </c>
       <c r="BK43" s="9"/>
       <c r="BL43" s="9"/>
@@ -11002,7 +11130,7 @@
       <c r="BO43" s="9"/>
       <c r="BP43" s="9"/>
       <c r="BQ43" s="9" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="BR43" s="9"/>
       <c r="BS43" s="9"/>
@@ -11010,7 +11138,7 @@
       <c r="BU43" s="9"/>
       <c r="BV43" s="9"/>
       <c r="BW43" s="9" t="s">
-        <v>1514</v>
+        <v>1512</v>
       </c>
       <c r="BX43" s="9"/>
       <c r="BY43" s="9"/>
@@ -11027,19 +11155,19 @@
       <c r="CW43" s="27"/>
       <c r="CX43" s="27"/>
       <c r="CY43" s="28" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="CZ43" s="28"/>
       <c r="DA43" s="28" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="DB43" s="28"/>
       <c r="DC43" s="28" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="DD43" s="28"/>
       <c r="DE43" s="28" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="DF43" s="27"/>
     </row>
@@ -11068,18 +11196,18 @@
       <c r="R44" s="12"/>
       <c r="S44" s="12"/>
       <c r="AG44" s="9" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AH44" s="9"/>
       <c r="AI44" s="9" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="AM44" s="9" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AN44" s="9"/>
       <c r="AQ44" s="9" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="BK44" s="9"/>
       <c r="BL44" s="9"/>
@@ -11088,7 +11216,7 @@
       <c r="BO44" s="9"/>
       <c r="BP44" s="9"/>
       <c r="BQ44" s="9" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="BR44" s="9"/>
       <c r="BS44" s="9"/>
@@ -11096,7 +11224,7 @@
       <c r="BU44" s="9"/>
       <c r="BV44" s="9"/>
       <c r="BW44" s="9" t="s">
-        <v>1515</v>
+        <v>1513</v>
       </c>
       <c r="BX44" s="9"/>
       <c r="BY44" s="9"/>
@@ -11113,19 +11241,19 @@
       <c r="CW44" s="27"/>
       <c r="CX44" s="27"/>
       <c r="CY44" s="28" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="CZ44" s="28"/>
       <c r="DA44" s="28" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="DB44" s="28"/>
       <c r="DC44" s="28" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="DD44" s="28"/>
       <c r="DE44" s="28" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="DF44" s="27"/>
     </row>
@@ -11154,18 +11282,18 @@
       <c r="R45" s="12"/>
       <c r="S45" s="12"/>
       <c r="AG45" s="9" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="AH45" s="9"/>
       <c r="AI45" s="9" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="AM45" s="9" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AN45" s="9"/>
       <c r="AQ45" s="9" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="BK45" s="9"/>
       <c r="BL45" s="9"/>
@@ -11174,7 +11302,7 @@
       <c r="BO45" s="9"/>
       <c r="BP45" s="9"/>
       <c r="BQ45" s="9" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="BR45" s="9"/>
       <c r="BS45" s="9"/>
@@ -11182,7 +11310,7 @@
       <c r="BU45" s="9"/>
       <c r="BV45" s="9"/>
       <c r="BW45" s="9" t="s">
-        <v>1516</v>
+        <v>1514</v>
       </c>
       <c r="BX45" s="9"/>
       <c r="BY45" s="9"/>
@@ -11199,19 +11327,19 @@
       <c r="CW45" s="27"/>
       <c r="CX45" s="27"/>
       <c r="CY45" s="28" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="CZ45" s="28"/>
       <c r="DA45" s="28" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="DB45" s="28"/>
       <c r="DC45" s="28" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="DD45" s="28"/>
       <c r="DE45" s="28" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="DF45" s="27"/>
     </row>
@@ -11240,17 +11368,17 @@
       <c r="R46" s="12"/>
       <c r="S46" s="12"/>
       <c r="AG46" s="9" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="AH46" s="9"/>
       <c r="AI46" s="9" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
       <c r="AM46" t="s">
+        <v>813</v>
+      </c>
+      <c r="AQ46" s="9" t="s">
         <v>814</v>
-      </c>
-      <c r="AQ46" s="9" t="s">
-        <v>815</v>
       </c>
       <c r="BK46" s="9"/>
       <c r="BL46" s="9"/>
@@ -11259,7 +11387,7 @@
       <c r="BO46" s="9"/>
       <c r="BP46" s="9"/>
       <c r="BQ46" s="9" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="BR46" s="9"/>
       <c r="BS46" s="9"/>
@@ -11267,7 +11395,7 @@
       <c r="BU46" s="9"/>
       <c r="BV46" s="9"/>
       <c r="BW46" s="9" t="s">
-        <v>1517</v>
+        <v>1515</v>
       </c>
       <c r="BX46" s="9"/>
       <c r="BY46" s="9"/>
@@ -11284,19 +11412,19 @@
       <c r="CW46" s="27"/>
       <c r="CX46" s="27"/>
       <c r="CY46" s="28" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="CZ46" s="28"/>
       <c r="DA46" s="28" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="DB46" s="28"/>
       <c r="DC46" s="28" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="DD46" s="28"/>
       <c r="DE46" s="28" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="DF46" s="27"/>
     </row>
@@ -11325,18 +11453,18 @@
       <c r="R47" s="12"/>
       <c r="S47" s="12"/>
       <c r="AG47" s="9" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AH47" s="9"/>
       <c r="AI47" s="9" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="AM47" s="9" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="AN47" s="9"/>
       <c r="AQ47" s="9" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="BK47" s="9"/>
       <c r="BL47" s="9"/>
@@ -11345,7 +11473,7 @@
       <c r="BO47" s="9"/>
       <c r="BP47" s="9"/>
       <c r="BQ47" s="9" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="BR47" s="9"/>
       <c r="BS47" s="9"/>
@@ -11353,7 +11481,7 @@
       <c r="BU47" s="9"/>
       <c r="BV47" s="9"/>
       <c r="BW47" s="9" t="s">
-        <v>1518</v>
+        <v>1516</v>
       </c>
       <c r="BX47" s="9"/>
       <c r="BY47" s="9"/>
@@ -11370,19 +11498,19 @@
       <c r="CW47" s="27"/>
       <c r="CX47" s="27"/>
       <c r="CY47" s="28" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="CZ47" s="28"/>
       <c r="DA47" s="28" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="DB47" s="28"/>
       <c r="DC47" s="28" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="DD47" s="28"/>
       <c r="DE47" s="28" t="s">
-        <v>1764</v>
+        <v>1762</v>
       </c>
       <c r="DF47" s="27"/>
     </row>
@@ -11411,14 +11539,14 @@
       <c r="R48" s="12"/>
       <c r="S48" s="12"/>
       <c r="AG48" s="9" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="AH48" s="9"/>
       <c r="AI48" s="9" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="AQ48" s="9" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="BK48" s="9"/>
       <c r="BL48" s="9"/>
@@ -11427,7 +11555,7 @@
       <c r="BO48" s="9"/>
       <c r="BP48" s="9"/>
       <c r="BQ48" s="9" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="BR48" s="9"/>
       <c r="BS48" s="9"/>
@@ -11435,7 +11563,7 @@
       <c r="BU48" s="9"/>
       <c r="BV48" s="9"/>
       <c r="BW48" s="9" t="s">
-        <v>1519</v>
+        <v>1517</v>
       </c>
       <c r="BX48" s="9"/>
       <c r="BY48" s="9"/>
@@ -11452,19 +11580,19 @@
       <c r="CW48" s="27"/>
       <c r="CX48" s="27"/>
       <c r="CY48" s="28" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="CZ48" s="28"/>
       <c r="DA48" s="28" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="DB48" s="28"/>
       <c r="DC48" s="28" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="DD48" s="28"/>
       <c r="DE48" s="28" t="s">
-        <v>1765</v>
+        <v>1763</v>
       </c>
       <c r="DF48" s="27"/>
     </row>
@@ -11493,14 +11621,14 @@
       <c r="R49" s="12"/>
       <c r="S49" s="12"/>
       <c r="AG49" s="9" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AH49" s="9"/>
       <c r="AI49" s="9" t="s">
-        <v>1785</v>
+        <v>1783</v>
       </c>
       <c r="AQ49" s="9" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="BK49" s="9"/>
       <c r="BL49" s="9"/>
@@ -11509,7 +11637,7 @@
       <c r="BO49" s="9"/>
       <c r="BP49" s="9"/>
       <c r="BQ49" s="9" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="BR49" s="9"/>
       <c r="BS49" s="9"/>
@@ -11517,7 +11645,7 @@
       <c r="BU49" s="9"/>
       <c r="BV49" s="9"/>
       <c r="BW49" s="9" t="s">
-        <v>1520</v>
+        <v>1518</v>
       </c>
       <c r="BX49" s="9"/>
       <c r="BY49" s="9"/>
@@ -11553,14 +11681,14 @@
       <c r="R50" s="12"/>
       <c r="S50" s="12"/>
       <c r="AG50" s="9" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="AH50" s="9"/>
       <c r="AI50" s="9" t="s">
-        <v>1786</v>
+        <v>1784</v>
       </c>
       <c r="AQ50" s="9" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="BK50" s="9"/>
       <c r="BL50" s="9"/>
@@ -11569,7 +11697,7 @@
       <c r="BO50" s="9"/>
       <c r="BP50" s="9"/>
       <c r="BQ50" s="9" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="BR50" s="9"/>
       <c r="BS50" s="9"/>
@@ -11577,7 +11705,7 @@
       <c r="BU50" s="9"/>
       <c r="BV50" s="9"/>
       <c r="BW50" s="9" t="s">
-        <v>1521</v>
+        <v>1519</v>
       </c>
       <c r="BX50" s="9"/>
       <c r="BY50" s="9"/>
@@ -11613,14 +11741,14 @@
       <c r="R51" s="12"/>
       <c r="S51" s="12"/>
       <c r="AG51" s="9" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AH51" s="9"/>
       <c r="AI51" s="9" t="s">
-        <v>1787</v>
+        <v>1785</v>
       </c>
       <c r="AQ51" s="9" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="BK51" s="9"/>
       <c r="BL51" s="9"/>
@@ -11629,7 +11757,7 @@
       <c r="BO51" s="9"/>
       <c r="BP51" s="9"/>
       <c r="BQ51" s="9" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="BR51" s="9"/>
       <c r="BS51" s="9"/>
@@ -11637,7 +11765,7 @@
       <c r="BU51" s="9"/>
       <c r="BV51" s="9"/>
       <c r="BW51" s="9" t="s">
-        <v>1522</v>
+        <v>1520</v>
       </c>
       <c r="BX51" s="9"/>
       <c r="BY51" s="9"/>
@@ -11673,14 +11801,14 @@
       <c r="R52" s="12"/>
       <c r="S52" s="12"/>
       <c r="AG52" s="9" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AH52" s="9"/>
       <c r="AI52" s="9" t="s">
-        <v>1788</v>
+        <v>1786</v>
       </c>
       <c r="AQ52" s="9" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="BK52" s="9"/>
       <c r="BL52" s="9"/>
@@ -11689,7 +11817,7 @@
       <c r="BO52" s="9"/>
       <c r="BP52" s="9"/>
       <c r="BQ52" s="9" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="BR52" s="9"/>
       <c r="BS52" s="9"/>
@@ -11697,7 +11825,7 @@
       <c r="BU52" s="9"/>
       <c r="BV52" s="9"/>
       <c r="BW52" s="9" t="s">
-        <v>1523</v>
+        <v>1521</v>
       </c>
       <c r="BX52" s="9"/>
       <c r="BY52" s="9"/>
@@ -11733,14 +11861,14 @@
       <c r="R53" s="12"/>
       <c r="S53" s="12"/>
       <c r="AG53" s="9" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AH53" s="9"/>
       <c r="AI53" s="9" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="AQ53" s="9" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="BK53" s="9"/>
       <c r="BL53" s="9"/>
@@ -11749,7 +11877,7 @@
       <c r="BO53" s="9"/>
       <c r="BP53" s="9"/>
       <c r="BQ53" s="9" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="BR53" s="9"/>
       <c r="BS53" s="9"/>
@@ -11757,7 +11885,7 @@
       <c r="BU53" s="9"/>
       <c r="BV53" s="9"/>
       <c r="BW53" s="9" t="s">
-        <v>1524</v>
+        <v>1522</v>
       </c>
       <c r="BX53" s="9"/>
       <c r="BY53" s="9"/>
@@ -11793,14 +11921,14 @@
       <c r="R54" s="12"/>
       <c r="S54" s="12"/>
       <c r="AG54" s="9" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AH54" s="9"/>
       <c r="AI54" s="9" t="s">
-        <v>1790</v>
+        <v>1788</v>
       </c>
       <c r="AQ54" s="9" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="BK54" s="9"/>
       <c r="BL54" s="9"/>
@@ -11809,7 +11937,7 @@
       <c r="BO54" s="9"/>
       <c r="BP54" s="9"/>
       <c r="BQ54" s="9" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="BR54" s="9"/>
       <c r="BS54" s="9"/>
@@ -11817,7 +11945,7 @@
       <c r="BU54" s="9"/>
       <c r="BV54" s="9"/>
       <c r="BW54" s="9" t="s">
-        <v>1525</v>
+        <v>1523</v>
       </c>
       <c r="BX54" s="9"/>
       <c r="BY54" s="9"/>
@@ -11853,14 +11981,14 @@
       <c r="R55" s="12"/>
       <c r="S55" s="12"/>
       <c r="AG55" s="9" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AH55" s="9"/>
       <c r="AI55" s="9" t="s">
-        <v>1791</v>
+        <v>1789</v>
       </c>
       <c r="AQ55" s="9" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="BK55" s="9"/>
       <c r="BL55" s="9"/>
@@ -11869,7 +11997,7 @@
       <c r="BO55" s="9"/>
       <c r="BP55" s="9"/>
       <c r="BQ55" s="9" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="BR55" s="9"/>
       <c r="BS55" s="9"/>
@@ -11877,7 +12005,7 @@
       <c r="BU55" s="9"/>
       <c r="BV55" s="9"/>
       <c r="BW55" s="9" t="s">
-        <v>1526</v>
+        <v>1524</v>
       </c>
       <c r="BX55" s="9"/>
       <c r="BY55" s="9"/>
@@ -11913,14 +12041,14 @@
       <c r="R56" s="12"/>
       <c r="S56" s="12"/>
       <c r="AG56" s="9" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="AH56" s="9"/>
       <c r="AI56" s="9" t="s">
-        <v>1792</v>
+        <v>1790</v>
       </c>
       <c r="AQ56" s="9" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="BK56" s="9"/>
       <c r="BL56" s="9"/>
@@ -11929,7 +12057,7 @@
       <c r="BO56" s="9"/>
       <c r="BP56" s="9"/>
       <c r="BQ56" s="9" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="BR56" s="9"/>
       <c r="BS56" s="9"/>
@@ -11937,7 +12065,7 @@
       <c r="BU56" s="9"/>
       <c r="BV56" s="9"/>
       <c r="BW56" s="9" t="s">
-        <v>1527</v>
+        <v>1525</v>
       </c>
       <c r="BX56" s="9"/>
       <c r="BY56" s="9"/>
@@ -11973,14 +12101,14 @@
       <c r="R57" s="12"/>
       <c r="S57" s="12"/>
       <c r="AG57" s="9" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AH57" s="9"/>
       <c r="AI57" s="9" t="s">
-        <v>1793</v>
+        <v>1791</v>
       </c>
       <c r="AQ57" s="9" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="BK57" s="9"/>
       <c r="BL57" s="9"/>
@@ -11989,7 +12117,7 @@
       <c r="BO57" s="9"/>
       <c r="BP57" s="9"/>
       <c r="BQ57" s="9" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="BR57" s="9"/>
       <c r="BS57" s="9"/>
@@ -11997,7 +12125,7 @@
       <c r="BU57" s="9"/>
       <c r="BV57" s="9"/>
       <c r="BW57" s="9" t="s">
-        <v>1528</v>
+        <v>1526</v>
       </c>
       <c r="BX57" s="9"/>
       <c r="BY57" s="9"/>
@@ -12033,14 +12161,14 @@
       <c r="R58" s="12"/>
       <c r="S58" s="12"/>
       <c r="AG58" s="9" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="AH58" s="9"/>
       <c r="AI58" s="9" t="s">
-        <v>1794</v>
+        <v>1792</v>
       </c>
       <c r="AQ58" s="9" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="BK58" s="9"/>
       <c r="BL58" s="9"/>
@@ -12049,7 +12177,7 @@
       <c r="BO58" s="9"/>
       <c r="BP58" s="9"/>
       <c r="BQ58" s="9" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="BR58" s="9"/>
       <c r="BS58" s="9"/>
@@ -12057,7 +12185,7 @@
       <c r="BU58" s="9"/>
       <c r="BV58" s="9"/>
       <c r="BW58" s="9" t="s">
-        <v>1529</v>
+        <v>1527</v>
       </c>
       <c r="BX58" s="9"/>
       <c r="BY58" s="9"/>
@@ -12093,14 +12221,14 @@
       <c r="R59" s="12"/>
       <c r="S59" s="12"/>
       <c r="AG59" s="9" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AH59" s="9"/>
       <c r="AI59" s="9" t="s">
-        <v>1795</v>
+        <v>1793</v>
       </c>
       <c r="AQ59" s="9" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="BK59" s="9"/>
       <c r="BL59" s="9"/>
@@ -12109,7 +12237,7 @@
       <c r="BO59" s="9"/>
       <c r="BP59" s="9"/>
       <c r="BQ59" s="9" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="BR59" s="9"/>
       <c r="BS59" s="9"/>
@@ -12117,7 +12245,7 @@
       <c r="BU59" s="9"/>
       <c r="BV59" s="9"/>
       <c r="BW59" s="9" t="s">
-        <v>1530</v>
+        <v>1528</v>
       </c>
       <c r="BX59" s="9"/>
       <c r="BY59" s="9"/>
@@ -12153,14 +12281,14 @@
       <c r="R60" s="12"/>
       <c r="S60" s="12"/>
       <c r="AG60" s="9" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AH60" s="9"/>
       <c r="AI60" s="9" t="s">
-        <v>1796</v>
+        <v>1794</v>
       </c>
       <c r="AQ60" s="9" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="BK60" s="9"/>
       <c r="BL60" s="9"/>
@@ -12169,7 +12297,7 @@
       <c r="BO60" s="9"/>
       <c r="BP60" s="9"/>
       <c r="BQ60" s="9" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="BR60" s="9"/>
       <c r="BS60" s="9"/>
@@ -12177,7 +12305,7 @@
       <c r="BU60" s="9"/>
       <c r="BV60" s="9"/>
       <c r="BW60" s="9" t="s">
-        <v>1531</v>
+        <v>1529</v>
       </c>
       <c r="BX60" s="9"/>
       <c r="BY60" s="9"/>
@@ -12213,14 +12341,14 @@
       <c r="R61" s="12"/>
       <c r="S61" s="12"/>
       <c r="AG61" s="9" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="AH61" s="9"/>
       <c r="AI61" s="9" t="s">
-        <v>1797</v>
+        <v>1795</v>
       </c>
       <c r="AQ61" s="9" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="BK61" s="9"/>
       <c r="BL61" s="9"/>
@@ -12229,7 +12357,7 @@
       <c r="BO61" s="9"/>
       <c r="BP61" s="9"/>
       <c r="BQ61" s="9" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="BR61" s="9"/>
       <c r="BS61" s="9"/>
@@ -12237,7 +12365,7 @@
       <c r="BU61" s="9"/>
       <c r="BV61" s="9"/>
       <c r="BW61" s="9" t="s">
-        <v>1532</v>
+        <v>1530</v>
       </c>
       <c r="BX61" s="9"/>
       <c r="BY61" s="9"/>
@@ -12273,14 +12401,14 @@
       <c r="R62" s="12"/>
       <c r="S62" s="12"/>
       <c r="AG62" s="9" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="AH62" s="9"/>
       <c r="AI62" s="9" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="AQ62" s="9" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="BK62" s="9"/>
       <c r="BL62" s="9"/>
@@ -12289,7 +12417,7 @@
       <c r="BO62" s="9"/>
       <c r="BP62" s="9"/>
       <c r="BQ62" s="9" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="BR62" s="9"/>
       <c r="BS62" s="9"/>
@@ -12297,7 +12425,7 @@
       <c r="BU62" s="9"/>
       <c r="BV62" s="9"/>
       <c r="BW62" s="9" t="s">
-        <v>1533</v>
+        <v>1531</v>
       </c>
       <c r="BX62" s="9"/>
       <c r="BY62" s="9"/>
@@ -12333,14 +12461,14 @@
       <c r="R63" s="12"/>
       <c r="S63" s="12"/>
       <c r="AG63" s="9" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="AH63" s="9"/>
       <c r="AI63" s="9" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="AQ63" s="9" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="BK63" s="9"/>
       <c r="BL63" s="9"/>
@@ -12349,7 +12477,7 @@
       <c r="BO63" s="9"/>
       <c r="BP63" s="9"/>
       <c r="BQ63" s="9" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="BR63" s="9"/>
       <c r="BS63" s="9"/>
@@ -12357,7 +12485,7 @@
       <c r="BU63" s="9"/>
       <c r="BV63" s="9"/>
       <c r="BW63" s="9" t="s">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="BX63" s="9"/>
       <c r="BY63" s="9"/>
@@ -12393,14 +12521,14 @@
       <c r="R64" s="12"/>
       <c r="S64" s="12"/>
       <c r="AG64" s="9" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="AH64" s="9"/>
       <c r="AI64" s="9" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="AQ64" s="9" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="BK64" s="9"/>
       <c r="BL64" s="9"/>
@@ -12409,7 +12537,7 @@
       <c r="BO64" s="9"/>
       <c r="BP64" s="9"/>
       <c r="BQ64" s="9" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="BR64" s="9"/>
       <c r="BS64" s="9"/>
@@ -12417,7 +12545,7 @@
       <c r="BU64" s="9"/>
       <c r="BV64" s="9"/>
       <c r="BW64" s="9" t="s">
-        <v>1535</v>
+        <v>1533</v>
       </c>
       <c r="BX64" s="9"/>
       <c r="BY64" s="9"/>
@@ -12453,14 +12581,14 @@
       <c r="R65" s="12"/>
       <c r="S65" s="12"/>
       <c r="AG65" s="9" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AH65" s="9"/>
       <c r="AI65" s="9" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="AQ65" s="9" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="BK65" s="9"/>
       <c r="BL65" s="9"/>
@@ -12469,7 +12597,7 @@
       <c r="BO65" s="9"/>
       <c r="BP65" s="9"/>
       <c r="BQ65" s="9" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="BR65" s="9"/>
       <c r="BS65" s="9"/>
@@ -12477,7 +12605,7 @@
       <c r="BU65" s="9"/>
       <c r="BV65" s="9"/>
       <c r="BW65" s="9" t="s">
-        <v>1536</v>
+        <v>1534</v>
       </c>
       <c r="BX65" s="9"/>
       <c r="BY65" s="9"/>
@@ -12513,14 +12641,14 @@
       <c r="R66" s="12"/>
       <c r="S66" s="12"/>
       <c r="AG66" s="9" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AH66" s="9"/>
       <c r="AI66" s="9" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="AQ66" s="9" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="BK66" s="9"/>
       <c r="BL66" s="9"/>
@@ -12529,7 +12657,7 @@
       <c r="BO66" s="9"/>
       <c r="BP66" s="9"/>
       <c r="BQ66" s="9" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="BR66" s="9"/>
       <c r="BS66" s="9"/>
@@ -12537,7 +12665,7 @@
       <c r="BU66" s="9"/>
       <c r="BV66" s="9"/>
       <c r="BW66" s="9" t="s">
-        <v>1537</v>
+        <v>1535</v>
       </c>
       <c r="BX66" s="9"/>
       <c r="BY66" s="9"/>
@@ -12573,14 +12701,14 @@
       <c r="R67" s="12"/>
       <c r="S67" s="12"/>
       <c r="AG67" s="9" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AH67" s="9"/>
       <c r="AI67" s="9" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="AQ67" s="9" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="BK67" s="9"/>
       <c r="BL67" s="9"/>
@@ -12589,7 +12717,7 @@
       <c r="BO67" s="9"/>
       <c r="BP67" s="9"/>
       <c r="BQ67" s="9" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="BR67" s="9"/>
       <c r="BS67" s="9"/>
@@ -12597,7 +12725,7 @@
       <c r="BU67" s="9"/>
       <c r="BV67" s="9"/>
       <c r="BW67" s="9" t="s">
-        <v>1538</v>
+        <v>1536</v>
       </c>
       <c r="BX67" s="9"/>
       <c r="BY67" s="9"/>
@@ -12633,14 +12761,14 @@
       <c r="R68" s="12"/>
       <c r="S68" s="12"/>
       <c r="AG68" s="9" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AH68" s="9"/>
       <c r="AI68" s="9" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="AQ68" s="9" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="BK68" s="9"/>
       <c r="BL68" s="9"/>
@@ -12649,7 +12777,7 @@
       <c r="BO68" s="9"/>
       <c r="BP68" s="9"/>
       <c r="BQ68" s="9" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="BR68" s="9"/>
       <c r="BS68" s="9"/>
@@ -12657,7 +12785,7 @@
       <c r="BU68" s="9"/>
       <c r="BV68" s="9"/>
       <c r="BW68" s="9" t="s">
-        <v>1539</v>
+        <v>1537</v>
       </c>
       <c r="BX68" s="9"/>
       <c r="BY68" s="9"/>
@@ -12693,14 +12821,14 @@
       <c r="R69" s="12"/>
       <c r="S69" s="12"/>
       <c r="AG69" s="9" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="AH69" s="9"/>
       <c r="AI69" s="9" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="AQ69" s="9" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="BK69" s="9"/>
       <c r="BL69" s="9"/>
@@ -12709,7 +12837,7 @@
       <c r="BO69" s="9"/>
       <c r="BP69" s="9"/>
       <c r="BQ69" s="9" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="BR69" s="9"/>
       <c r="BS69" s="9"/>
@@ -12717,7 +12845,7 @@
       <c r="BU69" s="9"/>
       <c r="BV69" s="9"/>
       <c r="BW69" s="9" t="s">
-        <v>1540</v>
+        <v>1538</v>
       </c>
       <c r="BX69" s="9"/>
       <c r="BY69" s="9"/>
@@ -12753,14 +12881,14 @@
       <c r="R70" s="12"/>
       <c r="S70" s="12"/>
       <c r="AG70" s="9" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AH70" s="9"/>
       <c r="AI70" s="9" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="AQ70" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="BK70" s="9"/>
       <c r="BL70" s="9"/>
@@ -12769,7 +12897,7 @@
       <c r="BO70" s="9"/>
       <c r="BP70" s="9"/>
       <c r="BQ70" s="9" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="BR70" s="9"/>
       <c r="BS70" s="9"/>
@@ -12777,7 +12905,7 @@
       <c r="BU70" s="9"/>
       <c r="BV70" s="9"/>
       <c r="BW70" s="9" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="BX70" s="9"/>
       <c r="BY70" s="9"/>
@@ -12813,14 +12941,14 @@
       <c r="R71" s="12"/>
       <c r="S71" s="12"/>
       <c r="AG71" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="AH71" s="9"/>
       <c r="AI71" s="9" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="AQ71" s="9" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="BK71" s="9"/>
       <c r="BL71" s="9"/>
@@ -12829,7 +12957,7 @@
       <c r="BO71" s="9"/>
       <c r="BP71" s="9"/>
       <c r="BQ71" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="BR71" s="9"/>
       <c r="BS71" s="9"/>
@@ -12837,7 +12965,7 @@
       <c r="BU71" s="9"/>
       <c r="BV71" s="9"/>
       <c r="BW71" s="9" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="BX71" s="9"/>
       <c r="BY71" s="9"/>
@@ -12873,14 +13001,14 @@
       <c r="R72" s="12"/>
       <c r="S72" s="12"/>
       <c r="AG72" s="9" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="AH72" s="9"/>
       <c r="AI72" s="9" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="AQ72" s="9" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="BK72" s="9"/>
       <c r="BL72" s="9"/>
@@ -12889,7 +13017,7 @@
       <c r="BO72" s="9"/>
       <c r="BP72" s="9"/>
       <c r="BQ72" s="9" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="BR72" s="9"/>
       <c r="BS72" s="9"/>
@@ -12897,7 +13025,7 @@
       <c r="BU72" s="9"/>
       <c r="BV72" s="9"/>
       <c r="BW72" s="9" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="BX72" s="9"/>
       <c r="BY72" s="9"/>
@@ -12933,14 +13061,14 @@
       <c r="R73" s="12"/>
       <c r="S73" s="12"/>
       <c r="AG73" s="9" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="AH73" s="9"/>
       <c r="AI73" s="9" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="AQ73" s="9" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="BK73" s="9"/>
       <c r="BL73" s="9"/>
@@ -12949,7 +13077,7 @@
       <c r="BO73" s="9"/>
       <c r="BP73" s="9"/>
       <c r="BQ73" s="9" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="BR73" s="9"/>
       <c r="BS73" s="9"/>
@@ -12957,7 +13085,7 @@
       <c r="BU73" s="9"/>
       <c r="BV73" s="9"/>
       <c r="BW73" s="9" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="BX73" s="9"/>
       <c r="BY73" s="9"/>
@@ -12993,14 +13121,14 @@
       <c r="R74" s="12"/>
       <c r="S74" s="12"/>
       <c r="AG74" s="9" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="AH74" s="9"/>
       <c r="AI74" s="9" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="AQ74" s="9" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="BK74" s="9"/>
       <c r="BL74" s="9"/>
@@ -13009,7 +13137,7 @@
       <c r="BO74" s="9"/>
       <c r="BP74" s="9"/>
       <c r="BQ74" s="9" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="BR74" s="9"/>
       <c r="BS74" s="9"/>
@@ -13017,7 +13145,7 @@
       <c r="BU74" s="9"/>
       <c r="BV74" s="9"/>
       <c r="BW74" s="9" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="BX74" s="9"/>
       <c r="BY74" s="9"/>
@@ -13053,14 +13181,14 @@
       <c r="R75" s="12"/>
       <c r="S75" s="12"/>
       <c r="AG75" s="9" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="AH75" s="9"/>
       <c r="AI75" s="9" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="AQ75" s="9" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="BK75" s="9"/>
       <c r="BL75" s="9"/>
@@ -13069,7 +13197,7 @@
       <c r="BO75" s="9"/>
       <c r="BP75" s="9"/>
       <c r="BQ75" s="9" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="BR75" s="9"/>
       <c r="BS75" s="9"/>
@@ -13077,7 +13205,7 @@
       <c r="BU75" s="9"/>
       <c r="BV75" s="9"/>
       <c r="BW75" s="9" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="BX75" s="9"/>
       <c r="BY75" s="9"/>
@@ -13113,14 +13241,14 @@
       <c r="R76" s="12"/>
       <c r="S76" s="12"/>
       <c r="AG76" s="9" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AH76" s="9"/>
       <c r="AI76" s="9" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="AQ76" s="9" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="BK76" s="9"/>
       <c r="BL76" s="9"/>
@@ -13129,7 +13257,7 @@
       <c r="BO76" s="9"/>
       <c r="BP76" s="9"/>
       <c r="BQ76" s="9" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="BR76" s="9"/>
       <c r="BS76" s="9"/>
@@ -13137,7 +13265,7 @@
       <c r="BU76" s="9"/>
       <c r="BV76" s="9"/>
       <c r="BW76" s="9" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="BX76" s="9"/>
       <c r="BY76" s="9"/>
@@ -13173,14 +13301,14 @@
       <c r="R77" s="12"/>
       <c r="S77" s="12"/>
       <c r="AG77" s="9" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="AH77" s="9"/>
       <c r="AI77" s="9" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="AQ77" s="9" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="BK77" s="9"/>
       <c r="BL77" s="9"/>
@@ -13189,7 +13317,7 @@
       <c r="BO77" s="9"/>
       <c r="BP77" s="9"/>
       <c r="BQ77" s="9" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="BR77" s="9"/>
       <c r="BS77" s="9"/>
@@ -13197,7 +13325,7 @@
       <c r="BU77" s="9"/>
       <c r="BV77" s="9"/>
       <c r="BW77" s="9" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="BX77" s="9"/>
       <c r="BY77" s="9"/>
@@ -13233,14 +13361,14 @@
       <c r="R78" s="12"/>
       <c r="S78" s="12"/>
       <c r="AG78" s="9" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="AH78" s="9"/>
       <c r="AI78" s="9" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="AQ78" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="BK78" s="9"/>
       <c r="BL78" s="9"/>
@@ -13249,7 +13377,7 @@
       <c r="BO78" s="9"/>
       <c r="BP78" s="9"/>
       <c r="BQ78" s="9" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="BR78" s="9"/>
       <c r="BS78" s="9"/>
@@ -13257,7 +13385,7 @@
       <c r="BU78" s="9"/>
       <c r="BV78" s="9"/>
       <c r="BW78" s="9" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="BX78" s="9"/>
       <c r="BY78" s="9"/>
@@ -13293,14 +13421,14 @@
       <c r="R79" s="12"/>
       <c r="S79" s="12"/>
       <c r="AG79" s="9" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="AH79" s="9"/>
       <c r="AI79" s="9" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="AQ79" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="BK79" s="9"/>
       <c r="BL79" s="9"/>
@@ -13309,7 +13437,7 @@
       <c r="BO79" s="9"/>
       <c r="BP79" s="9"/>
       <c r="BQ79" s="9" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="BR79" s="9"/>
       <c r="BS79" s="9"/>
@@ -13317,7 +13445,7 @@
       <c r="BU79" s="9"/>
       <c r="BV79" s="9"/>
       <c r="BW79" s="9" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="BX79" s="9"/>
       <c r="BY79" s="9"/>
@@ -13353,14 +13481,14 @@
       <c r="R80" s="12"/>
       <c r="S80" s="12"/>
       <c r="AG80" s="9" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="AH80" s="9"/>
       <c r="AI80" s="9" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="AQ80" s="9" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="BK80" s="9"/>
       <c r="BL80" s="9"/>
@@ -13369,7 +13497,7 @@
       <c r="BO80" s="9"/>
       <c r="BP80" s="9"/>
       <c r="BQ80" s="9" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="BR80" s="9"/>
       <c r="BS80" s="9"/>
@@ -13377,7 +13505,7 @@
       <c r="BU80" s="9"/>
       <c r="BV80" s="9"/>
       <c r="BW80" s="9" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="BX80" s="9"/>
       <c r="BY80" s="9"/>
@@ -13413,14 +13541,14 @@
       <c r="R81" s="12"/>
       <c r="S81" s="12"/>
       <c r="AG81" s="9" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="AH81" s="9"/>
       <c r="AI81" s="9" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="AQ81" s="9" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="BK81" s="9"/>
       <c r="BL81" s="9"/>
@@ -13429,7 +13557,7 @@
       <c r="BO81" s="9"/>
       <c r="BP81" s="9"/>
       <c r="BQ81" s="9" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="BR81" s="9"/>
       <c r="BS81" s="9"/>
@@ -13437,7 +13565,7 @@
       <c r="BU81" s="9"/>
       <c r="BV81" s="9"/>
       <c r="BW81" s="9" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="BX81" s="9"/>
       <c r="BY81" s="9"/>
@@ -13473,14 +13601,14 @@
       <c r="R82" s="12"/>
       <c r="S82" s="12"/>
       <c r="AG82" s="9" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="AH82" s="9"/>
       <c r="AI82" s="9" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="AQ82" s="9" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="BK82" s="9"/>
       <c r="BL82" s="9"/>
@@ -13489,7 +13617,7 @@
       <c r="BO82" s="9"/>
       <c r="BP82" s="9"/>
       <c r="BQ82" s="9" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="BR82" s="9"/>
       <c r="BS82" s="9"/>
@@ -13497,7 +13625,7 @@
       <c r="BU82" s="9"/>
       <c r="BV82" s="9"/>
       <c r="BW82" s="9" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
       <c r="BX82" s="9"/>
       <c r="BY82" s="9"/>
@@ -13533,14 +13661,14 @@
       <c r="R83" s="12"/>
       <c r="S83" s="12"/>
       <c r="AG83" s="9" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="AH83" s="9"/>
       <c r="AI83" s="9" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="AQ83" s="9" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="BK83" s="9"/>
       <c r="BL83" s="9"/>
@@ -13549,7 +13677,7 @@
       <c r="BO83" s="9"/>
       <c r="BP83" s="9"/>
       <c r="BQ83" s="9" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="BR83" s="9"/>
       <c r="BS83" s="9"/>
@@ -13557,7 +13685,7 @@
       <c r="BU83" s="9"/>
       <c r="BV83" s="9"/>
       <c r="BW83" s="9" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="BX83" s="9"/>
       <c r="BY83" s="9"/>
@@ -13593,14 +13721,14 @@
       <c r="R84" s="12"/>
       <c r="S84" s="12"/>
       <c r="AG84" s="9" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="AH84" s="9"/>
       <c r="AI84" s="9" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="AQ84" s="9" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="BK84" s="9"/>
       <c r="BL84" s="9"/>
@@ -13609,7 +13737,7 @@
       <c r="BO84" s="9"/>
       <c r="BP84" s="9"/>
       <c r="BQ84" s="9" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="BR84" s="9"/>
       <c r="BS84" s="9"/>
@@ -13617,7 +13745,7 @@
       <c r="BU84" s="9"/>
       <c r="BV84" s="9"/>
       <c r="BW84" s="9" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="BX84" s="9"/>
       <c r="BY84" s="9"/>
@@ -13653,14 +13781,14 @@
       <c r="R85" s="12"/>
       <c r="S85" s="12"/>
       <c r="AG85" s="9" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="AH85" s="9"/>
       <c r="AI85" s="9" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="AQ85" s="9" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="BK85" s="9"/>
       <c r="BL85" s="9"/>
@@ -13669,7 +13797,7 @@
       <c r="BO85" s="9"/>
       <c r="BP85" s="9"/>
       <c r="BQ85" s="9" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="BR85" s="9"/>
       <c r="BS85" s="9"/>
@@ -13677,7 +13805,7 @@
       <c r="BU85" s="9"/>
       <c r="BV85" s="9"/>
       <c r="BW85" s="9" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="BX85" s="9"/>
       <c r="BY85" s="9"/>
@@ -13713,14 +13841,14 @@
       <c r="R86" s="12"/>
       <c r="S86" s="12"/>
       <c r="AG86" s="9" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="AH86" s="9"/>
       <c r="AI86" s="9" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="AQ86" s="9" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="BK86" s="9"/>
       <c r="BL86" s="9"/>
@@ -13729,7 +13857,7 @@
       <c r="BO86" s="9"/>
       <c r="BP86" s="9"/>
       <c r="BQ86" s="9" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="BR86" s="9"/>
       <c r="BS86" s="9"/>
@@ -13737,7 +13865,7 @@
       <c r="BU86" s="9"/>
       <c r="BV86" s="9"/>
       <c r="BW86" s="9" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="BX86" s="9"/>
       <c r="BY86" s="9"/>
@@ -13773,14 +13901,14 @@
       <c r="R87" s="12"/>
       <c r="S87" s="12"/>
       <c r="AG87" s="9" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="AH87" s="9"/>
       <c r="AI87" s="9" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="AQ87" s="9" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="BK87" s="9"/>
       <c r="BL87" s="9"/>
@@ -13789,7 +13917,7 @@
       <c r="BO87" s="9"/>
       <c r="BP87" s="9"/>
       <c r="BQ87" s="9" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="BR87" s="9"/>
       <c r="BS87" s="9"/>
@@ -13797,7 +13925,7 @@
       <c r="BU87" s="9"/>
       <c r="BV87" s="9"/>
       <c r="BW87" s="9" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="BX87" s="9"/>
       <c r="BY87" s="9"/>
@@ -13833,14 +13961,14 @@
       <c r="R88" s="12"/>
       <c r="S88" s="12"/>
       <c r="AG88" s="9" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="AH88" s="9"/>
       <c r="AI88" s="9" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="AQ88" s="9" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="BK88" s="9"/>
       <c r="BL88" s="9"/>
@@ -13849,7 +13977,7 @@
       <c r="BO88" s="9"/>
       <c r="BP88" s="9"/>
       <c r="BQ88" s="9" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="BR88" s="9"/>
       <c r="BS88" s="9"/>
@@ -13857,7 +13985,7 @@
       <c r="BU88" s="9"/>
       <c r="BV88" s="9"/>
       <c r="BW88" s="9" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="BX88" s="9"/>
       <c r="BY88" s="9"/>
@@ -13893,14 +14021,14 @@
       <c r="R89" s="12"/>
       <c r="S89" s="12"/>
       <c r="AG89" s="9" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="AH89" s="9"/>
       <c r="AI89" s="9" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="AQ89" s="9" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="BK89" s="9"/>
       <c r="BL89" s="9"/>
@@ -13909,7 +14037,7 @@
       <c r="BO89" s="9"/>
       <c r="BP89" s="9"/>
       <c r="BQ89" s="9" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="BR89" s="9"/>
       <c r="BS89" s="9"/>
@@ -13917,7 +14045,7 @@
       <c r="BU89" s="9"/>
       <c r="BV89" s="9"/>
       <c r="BW89" s="9" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="BX89" s="9"/>
       <c r="BY89" s="9"/>
@@ -13953,14 +14081,14 @@
       <c r="R90" s="12"/>
       <c r="S90" s="12"/>
       <c r="AG90" s="9" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="AH90" s="9"/>
       <c r="AI90" s="9" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="AQ90" s="9" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="BK90" s="9"/>
       <c r="BL90" s="9"/>
@@ -13969,7 +14097,7 @@
       <c r="BO90" s="9"/>
       <c r="BP90" s="9"/>
       <c r="BQ90" s="9" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="BR90" s="9"/>
       <c r="BS90" s="9"/>
@@ -13977,7 +14105,7 @@
       <c r="BU90" s="9"/>
       <c r="BV90" s="9"/>
       <c r="BW90" s="9" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
       <c r="BX90" s="9"/>
       <c r="BY90" s="9"/>
@@ -14013,14 +14141,14 @@
       <c r="R91" s="12"/>
       <c r="S91" s="12"/>
       <c r="AG91" s="9" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="AH91" s="9"/>
       <c r="AI91" s="9" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="AQ91" s="9" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="BK91" s="9"/>
       <c r="BL91" s="9"/>
@@ -14029,7 +14157,7 @@
       <c r="BO91" s="9"/>
       <c r="BP91" s="9"/>
       <c r="BQ91" s="9" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="BR91" s="9"/>
       <c r="BS91" s="9"/>
@@ -14037,7 +14165,7 @@
       <c r="BU91" s="9"/>
       <c r="BV91" s="9"/>
       <c r="BW91" s="9" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="BX91" s="9"/>
       <c r="BY91" s="9"/>
@@ -14073,10 +14201,10 @@
       <c r="R92" s="12"/>
       <c r="S92" s="12"/>
       <c r="AI92" s="9" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="AQ92" s="9" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="BK92" s="9"/>
       <c r="BL92" s="9"/>
@@ -14091,7 +14219,7 @@
       <c r="BU92" s="9"/>
       <c r="BV92" s="9"/>
       <c r="BW92" s="9" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="BX92" s="9"/>
       <c r="BY92" s="9"/>
@@ -14130,7 +14258,7 @@
         <v>100</v>
       </c>
       <c r="AQ93" s="9" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="BK93" s="9"/>
       <c r="BL93" s="9"/>
@@ -14145,7 +14273,7 @@
       <c r="BU93" s="9"/>
       <c r="BV93" s="9"/>
       <c r="BW93" s="9" t="s">
-        <v>1564</v>
+        <v>1562</v>
       </c>
       <c r="BX93" s="9"/>
       <c r="BY93" s="9"/>
@@ -14181,10 +14309,10 @@
       <c r="R94" s="12"/>
       <c r="S94" s="12"/>
       <c r="AI94" s="9" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="AQ94" s="9" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="BK94" s="9"/>
       <c r="BL94" s="9"/>
@@ -14199,7 +14327,7 @@
       <c r="BU94" s="9"/>
       <c r="BV94" s="9"/>
       <c r="BW94" s="9" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="BX94" s="9"/>
       <c r="BY94" s="9"/>
@@ -14235,10 +14363,10 @@
       <c r="R95" s="12"/>
       <c r="S95" s="12"/>
       <c r="AI95" s="9" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="AQ95" s="9" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="BK95" s="9"/>
       <c r="BL95" s="9"/>
@@ -14253,7 +14381,7 @@
       <c r="BU95" s="9"/>
       <c r="BV95" s="9"/>
       <c r="BW95" s="9" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="BX95" s="9"/>
       <c r="BY95" s="9"/>
@@ -14289,10 +14417,10 @@
       <c r="R96" s="12"/>
       <c r="S96" s="12"/>
       <c r="AI96" s="9" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="AQ96" s="9" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="BK96" s="9"/>
       <c r="BL96" s="9"/>
@@ -14307,7 +14435,7 @@
       <c r="BU96" s="9"/>
       <c r="BV96" s="9"/>
       <c r="BW96" s="9" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="BX96" s="9"/>
       <c r="BY96" s="9"/>
@@ -14343,10 +14471,10 @@
       <c r="R97" s="12"/>
       <c r="S97" s="12"/>
       <c r="AI97" s="9" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="AQ97" s="9" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="BK97" s="9"/>
       <c r="BL97" s="9"/>
@@ -14361,7 +14489,7 @@
       <c r="BU97" s="9"/>
       <c r="BV97" s="9"/>
       <c r="BW97" s="9" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="BX97" s="9"/>
       <c r="BY97" s="9"/>
@@ -14397,10 +14525,10 @@
       <c r="R98" s="12"/>
       <c r="S98" s="12"/>
       <c r="AI98" s="9" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="AQ98" s="9" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="BK98" s="9"/>
       <c r="BL98" s="9"/>
@@ -14415,7 +14543,7 @@
       <c r="BU98" s="9"/>
       <c r="BV98" s="9"/>
       <c r="BW98" s="9" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="BX98" s="9"/>
       <c r="BY98" s="9"/>
@@ -14451,10 +14579,10 @@
       <c r="R99" s="12"/>
       <c r="S99" s="12"/>
       <c r="AI99" s="9" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="AQ99" s="9" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="BK99" s="9"/>
       <c r="BL99" s="9"/>
@@ -14469,7 +14597,7 @@
       <c r="BU99" s="9"/>
       <c r="BV99" s="9"/>
       <c r="BW99" s="9" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="BX99" s="9"/>
       <c r="BY99" s="9"/>
@@ -14505,10 +14633,10 @@
       <c r="R100" s="12"/>
       <c r="S100" s="12"/>
       <c r="AI100" s="9" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="AQ100" s="9" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="BK100" s="9"/>
       <c r="BL100" s="9"/>
@@ -14523,7 +14651,7 @@
       <c r="BU100" s="9"/>
       <c r="BV100" s="9"/>
       <c r="BW100" s="9" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="BX100" s="9"/>
       <c r="BY100" s="9"/>
@@ -14559,10 +14687,10 @@
       <c r="R101" s="12"/>
       <c r="S101" s="12"/>
       <c r="AI101" s="9" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="AQ101" s="9" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="BK101" s="9"/>
       <c r="BL101" s="9"/>
@@ -14577,7 +14705,7 @@
       <c r="BU101" s="9"/>
       <c r="BV101" s="9"/>
       <c r="BW101" s="9" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="BX101" s="9"/>
       <c r="BY101" s="9"/>
@@ -14613,10 +14741,10 @@
       <c r="R102" s="12"/>
       <c r="S102" s="12"/>
       <c r="AI102" s="9" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="AQ102" s="9" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="BK102" s="9"/>
       <c r="BL102" s="9"/>
@@ -14631,7 +14759,7 @@
       <c r="BU102" s="9"/>
       <c r="BV102" s="9"/>
       <c r="BW102" s="9" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="BX102" s="9"/>
       <c r="BY102" s="9"/>
@@ -14667,10 +14795,10 @@
       <c r="R103" s="12"/>
       <c r="S103" s="12"/>
       <c r="AI103" s="9" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="AQ103" s="9" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="BK103" s="9"/>
       <c r="BL103" s="9"/>
@@ -14685,7 +14813,7 @@
       <c r="BU103" s="9"/>
       <c r="BV103" s="9"/>
       <c r="BW103" s="9" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="BX103" s="9"/>
       <c r="BY103" s="9"/>
@@ -14721,10 +14849,10 @@
       <c r="R104" s="12"/>
       <c r="S104" s="12"/>
       <c r="AI104" s="9" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="AQ104" s="9" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="BK104" s="9"/>
       <c r="BL104" s="9"/>
@@ -14739,7 +14867,7 @@
       <c r="BU104" s="9"/>
       <c r="BV104" s="9"/>
       <c r="BW104" s="9" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="BX104" s="9"/>
       <c r="BY104" s="9"/>
@@ -14775,10 +14903,10 @@
       <c r="R105" s="12"/>
       <c r="S105" s="12"/>
       <c r="AI105" s="9" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="AQ105" s="9" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="BK105" s="9"/>
       <c r="BL105" s="9"/>
@@ -14793,7 +14921,7 @@
       <c r="BU105" s="9"/>
       <c r="BV105" s="9"/>
       <c r="BW105" s="9" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="BX105" s="9"/>
       <c r="BY105" s="9"/>
@@ -14829,10 +14957,10 @@
       <c r="R106" s="12"/>
       <c r="S106" s="12"/>
       <c r="AI106" s="9" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="AQ106" s="9" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="BK106" s="9"/>
       <c r="BL106" s="9"/>
@@ -14847,7 +14975,7 @@
       <c r="BU106" s="9"/>
       <c r="BV106" s="9"/>
       <c r="BW106" s="9" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="BX106" s="9"/>
       <c r="BY106" s="9"/>
@@ -14883,10 +15011,10 @@
       <c r="R107" s="12"/>
       <c r="S107" s="12"/>
       <c r="AI107" s="9" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="AQ107" s="9" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="BK107" s="9"/>
       <c r="BL107" s="9"/>
@@ -14901,7 +15029,7 @@
       <c r="BU107" s="9"/>
       <c r="BV107" s="9"/>
       <c r="BW107" s="9" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="BX107" s="9"/>
       <c r="BY107" s="9"/>
@@ -14937,10 +15065,10 @@
       <c r="R108" s="12"/>
       <c r="S108" s="12"/>
       <c r="AI108" s="9" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="AQ108" s="9" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="BK108" s="9"/>
       <c r="BL108" s="9"/>
@@ -14955,7 +15083,7 @@
       <c r="BU108" s="9"/>
       <c r="BV108" s="9"/>
       <c r="BW108" s="9" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="BX108" s="9"/>
       <c r="BY108" s="9"/>
@@ -14991,10 +15119,10 @@
       <c r="R109" s="12"/>
       <c r="S109" s="12"/>
       <c r="AI109" s="9" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="AQ109" s="9" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="BK109" s="9"/>
       <c r="BL109" s="9"/>
@@ -15009,7 +15137,7 @@
       <c r="BU109" s="9"/>
       <c r="BV109" s="9"/>
       <c r="BW109" s="9" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="BX109" s="9"/>
       <c r="BY109" s="9"/>
@@ -15045,10 +15173,10 @@
       <c r="R110" s="12"/>
       <c r="S110" s="12"/>
       <c r="AI110" s="9" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="AQ110" s="9" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="BK110" s="9"/>
       <c r="BL110" s="9"/>
@@ -15063,7 +15191,7 @@
       <c r="BU110" s="9"/>
       <c r="BV110" s="9"/>
       <c r="BW110" s="9" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="BX110" s="9"/>
       <c r="BY110" s="9"/>
@@ -15099,10 +15227,10 @@
       <c r="R111" s="12"/>
       <c r="S111" s="12"/>
       <c r="AI111" s="9" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="AQ111" s="9" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="BK111" s="9"/>
       <c r="BL111" s="9"/>
@@ -15117,7 +15245,7 @@
       <c r="BU111" s="9"/>
       <c r="BV111" s="9"/>
       <c r="BW111" s="9" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="BX111" s="9"/>
       <c r="BY111" s="9"/>
@@ -15153,10 +15281,10 @@
       <c r="R112" s="12"/>
       <c r="S112" s="12"/>
       <c r="AI112" s="9" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="AQ112" s="9" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="BK112" s="9"/>
       <c r="BL112" s="9"/>
@@ -15171,7 +15299,7 @@
       <c r="BU112" s="9"/>
       <c r="BV112" s="9"/>
       <c r="BW112" s="9" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="BX112" s="9"/>
       <c r="BY112" s="9"/>
@@ -15207,10 +15335,10 @@
       <c r="R113" s="12"/>
       <c r="S113" s="12"/>
       <c r="AI113" s="9" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="AQ113" s="9" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="BK113" s="9"/>
       <c r="BL113" s="9"/>
@@ -15225,7 +15353,7 @@
       <c r="BU113" s="9"/>
       <c r="BV113" s="9"/>
       <c r="BW113" s="9" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="BX113" s="9"/>
       <c r="BY113" s="9"/>
@@ -15261,10 +15389,10 @@
       <c r="R114" s="12"/>
       <c r="S114" s="12"/>
       <c r="AI114" s="9" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="AQ114" s="9" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="BK114" s="9"/>
       <c r="BL114" s="9"/>
@@ -15279,7 +15407,7 @@
       <c r="BU114" s="9"/>
       <c r="BV114" s="9"/>
       <c r="BW114" s="9" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="BX114" s="9"/>
       <c r="BY114" s="9"/>
@@ -15315,10 +15443,10 @@
       <c r="R115" s="12"/>
       <c r="S115" s="12"/>
       <c r="AI115" s="9" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="AQ115" s="9" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="BK115" s="9"/>
       <c r="BL115" s="9"/>
@@ -15333,7 +15461,7 @@
       <c r="BU115" s="9"/>
       <c r="BV115" s="9"/>
       <c r="BW115" s="9" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="BX115" s="9"/>
       <c r="BY115" s="9"/>
@@ -15369,10 +15497,10 @@
       <c r="R116" s="12"/>
       <c r="S116" s="12"/>
       <c r="AI116" s="9" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="AQ116" s="9" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="BK116" s="9"/>
       <c r="BL116" s="9"/>
@@ -15387,7 +15515,7 @@
       <c r="BU116" s="9"/>
       <c r="BV116" s="9"/>
       <c r="BW116" s="9" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="BX116" s="9"/>
       <c r="BY116" s="9"/>
@@ -15423,10 +15551,10 @@
       <c r="R117" s="12"/>
       <c r="S117" s="12"/>
       <c r="AI117" s="9" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="AQ117" s="9" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="BK117" s="9"/>
       <c r="BL117" s="9"/>
@@ -15441,7 +15569,7 @@
       <c r="BU117" s="9"/>
       <c r="BV117" s="9"/>
       <c r="BW117" s="9" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="BX117" s="9"/>
       <c r="BY117" s="9"/>
@@ -15477,10 +15605,10 @@
       <c r="R118" s="12"/>
       <c r="S118" s="12"/>
       <c r="AI118" s="29" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="AQ118" s="9" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="BK118" s="9"/>
       <c r="BL118" s="9"/>
@@ -15495,7 +15623,7 @@
       <c r="BU118" s="9"/>
       <c r="BV118" s="9"/>
       <c r="BW118" s="9" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="BX118" s="9"/>
       <c r="BY118" s="9"/>
@@ -15531,7 +15659,7 @@
       <c r="R119" s="12"/>
       <c r="S119" s="12"/>
       <c r="AQ119" s="9" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="BK119" s="9"/>
       <c r="BL119" s="9"/>
@@ -15546,7 +15674,7 @@
       <c r="BU119" s="9"/>
       <c r="BV119" s="9"/>
       <c r="BW119" s="9" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="BX119" s="9"/>
       <c r="BY119" s="9"/>
@@ -15582,7 +15710,7 @@
       <c r="R120" s="12"/>
       <c r="S120" s="12"/>
       <c r="AQ120" s="9" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="BK120" s="9"/>
       <c r="BL120" s="9"/>
@@ -15597,7 +15725,7 @@
       <c r="BU120" s="9"/>
       <c r="BV120" s="9"/>
       <c r="BW120" s="9" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="BX120" s="9"/>
       <c r="BY120" s="9"/>
@@ -15633,7 +15761,7 @@
       <c r="R121" s="12"/>
       <c r="S121" s="12"/>
       <c r="AQ121" s="9" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="BK121" s="9"/>
       <c r="BL121" s="9"/>
@@ -15648,7 +15776,7 @@
       <c r="BU121" s="9"/>
       <c r="BV121" s="9"/>
       <c r="BW121" s="9" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="BX121" s="9"/>
       <c r="BY121" s="9"/>
@@ -15684,7 +15812,7 @@
       <c r="R122" s="12"/>
       <c r="S122" s="12"/>
       <c r="AQ122" s="9" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="BK122" s="9"/>
       <c r="BL122" s="9"/>
@@ -15699,7 +15827,7 @@
       <c r="BU122" s="9"/>
       <c r="BV122" s="9"/>
       <c r="BW122" s="9" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="BX122" s="9"/>
       <c r="BY122" s="9"/>
@@ -15735,7 +15863,7 @@
       <c r="R123" s="12"/>
       <c r="S123" s="12"/>
       <c r="AQ123" s="9" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="BK123" s="9"/>
       <c r="BL123" s="9"/>
@@ -15750,7 +15878,7 @@
       <c r="BU123" s="9"/>
       <c r="BV123" s="9"/>
       <c r="BW123" s="9" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="BX123" s="9"/>
       <c r="BY123" s="9"/>
@@ -15786,7 +15914,7 @@
       <c r="R124" s="12"/>
       <c r="S124" s="12"/>
       <c r="AQ124" s="9" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="BK124" s="9"/>
       <c r="BL124" s="9"/>
@@ -15801,7 +15929,7 @@
       <c r="BU124" s="9"/>
       <c r="BV124" s="9"/>
       <c r="BW124" s="9" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="BX124" s="9"/>
       <c r="BY124" s="9"/>
@@ -15837,7 +15965,7 @@
       <c r="R125" s="12"/>
       <c r="S125" s="12"/>
       <c r="AQ125" s="9" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="BK125" s="9"/>
       <c r="BL125" s="9"/>
@@ -15888,7 +16016,7 @@
       <c r="R126" s="12"/>
       <c r="S126" s="12"/>
       <c r="AQ126" s="9" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="BK126" s="9"/>
       <c r="BL126" s="9"/>
@@ -15903,7 +16031,7 @@
       <c r="BU126" s="9"/>
       <c r="BV126" s="9"/>
       <c r="BW126" s="9" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="BX126" s="9"/>
       <c r="BY126" s="9"/>
@@ -15939,7 +16067,7 @@
       <c r="R127" s="12"/>
       <c r="S127" s="12"/>
       <c r="AQ127" s="9" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="BK127" s="9"/>
       <c r="BL127" s="9"/>
@@ -15954,7 +16082,7 @@
       <c r="BU127" s="9"/>
       <c r="BV127" s="9"/>
       <c r="BW127" s="9" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="BX127" s="9"/>
       <c r="BY127" s="9"/>
@@ -15990,7 +16118,7 @@
       <c r="R128" s="12"/>
       <c r="S128" s="12"/>
       <c r="AQ128" s="9" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="BK128" s="9"/>
       <c r="BL128" s="9"/>
@@ -16005,7 +16133,7 @@
       <c r="BU128" s="9"/>
       <c r="BV128" s="9"/>
       <c r="BW128" s="9" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="BX128" s="9"/>
       <c r="BY128" s="9"/>
@@ -16041,7 +16169,7 @@
       <c r="R129" s="12"/>
       <c r="S129" s="12"/>
       <c r="AQ129" s="9" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="BK129" s="9"/>
       <c r="BL129" s="9"/>
@@ -16056,7 +16184,7 @@
       <c r="BU129" s="9"/>
       <c r="BV129" s="9"/>
       <c r="BW129" s="9" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="BX129" s="9"/>
       <c r="BY129" s="9"/>
@@ -16092,7 +16220,7 @@
       <c r="R130" s="12"/>
       <c r="S130" s="12"/>
       <c r="AQ130" s="9" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="BK130" s="9"/>
       <c r="BL130" s="9"/>
@@ -16107,7 +16235,7 @@
       <c r="BU130" s="9"/>
       <c r="BV130" s="9"/>
       <c r="BW130" s="9" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="BX130" s="9"/>
       <c r="BY130" s="9"/>
@@ -16143,7 +16271,7 @@
       <c r="R131" s="12"/>
       <c r="S131" s="12"/>
       <c r="AQ131" s="9" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="BK131" s="9"/>
       <c r="BL131" s="9"/>
@@ -16158,7 +16286,7 @@
       <c r="BU131" s="9"/>
       <c r="BV131" s="9"/>
       <c r="BW131" s="9" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="BX131" s="9"/>
       <c r="BY131" s="9"/>
@@ -16194,7 +16322,7 @@
       <c r="R132" s="12"/>
       <c r="S132" s="12"/>
       <c r="AQ132" s="9" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="BK132" s="9"/>
       <c r="BL132" s="9"/>
@@ -16209,7 +16337,7 @@
       <c r="BU132" s="9"/>
       <c r="BV132" s="9"/>
       <c r="BW132" s="9" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="BX132" s="9"/>
       <c r="BY132" s="9"/>
@@ -16245,7 +16373,7 @@
       <c r="R133" s="12"/>
       <c r="S133" s="12"/>
       <c r="AQ133" s="9" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="BK133" s="9"/>
       <c r="BL133" s="9"/>
@@ -16260,7 +16388,7 @@
       <c r="BU133" s="9"/>
       <c r="BV133" s="9"/>
       <c r="BW133" s="9" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="BX133" s="9"/>
       <c r="BY133" s="9"/>
@@ -16296,7 +16424,7 @@
       <c r="R134" s="12"/>
       <c r="S134" s="12"/>
       <c r="AQ134" s="9" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="BK134" s="9"/>
       <c r="BL134" s="9"/>
@@ -16311,7 +16439,7 @@
       <c r="BU134" s="9"/>
       <c r="BV134" s="9"/>
       <c r="BW134" s="9" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="BX134" s="9"/>
       <c r="BY134" s="9"/>
@@ -16347,7 +16475,7 @@
       <c r="R135" s="12"/>
       <c r="S135" s="12"/>
       <c r="AQ135" s="9" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="BK135" s="9"/>
       <c r="BL135" s="9"/>
@@ -16398,7 +16526,7 @@
       <c r="R136" s="12"/>
       <c r="S136" s="12"/>
       <c r="AQ136" s="9" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="BK136" s="9"/>
       <c r="BL136" s="9"/>
@@ -16413,7 +16541,7 @@
       <c r="BU136" s="9"/>
       <c r="BV136" s="9"/>
       <c r="BW136" s="9" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="BX136" s="9"/>
       <c r="BY136" s="9"/>
@@ -16449,7 +16577,7 @@
       <c r="R137" s="12"/>
       <c r="S137" s="12"/>
       <c r="AQ137" s="9" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="BK137" s="9"/>
       <c r="BL137" s="9"/>
@@ -16464,7 +16592,7 @@
       <c r="BU137" s="9"/>
       <c r="BV137" s="9"/>
       <c r="BW137" s="9" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="BX137" s="9"/>
       <c r="BY137" s="9"/>
@@ -16500,7 +16628,7 @@
       <c r="R138" s="12"/>
       <c r="S138" s="12"/>
       <c r="AQ138" s="9" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="BK138" s="9"/>
       <c r="BL138" s="9"/>
@@ -16515,7 +16643,7 @@
       <c r="BU138" s="9"/>
       <c r="BV138" s="9"/>
       <c r="BW138" s="9" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="BX138" s="9"/>
       <c r="BY138" s="9"/>
@@ -16551,7 +16679,7 @@
       <c r="R139" s="12"/>
       <c r="S139" s="12"/>
       <c r="AQ139" s="9" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="BK139" s="9"/>
       <c r="BL139" s="9"/>
@@ -16566,7 +16694,7 @@
       <c r="BU139" s="9"/>
       <c r="BV139" s="9"/>
       <c r="BW139" s="9" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="BX139" s="9"/>
       <c r="BY139" s="9"/>
@@ -16602,7 +16730,7 @@
       <c r="R140" s="12"/>
       <c r="S140" s="12"/>
       <c r="AQ140" s="9" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="BK140" s="9"/>
       <c r="BL140" s="9"/>
@@ -16617,7 +16745,7 @@
       <c r="BU140" s="9"/>
       <c r="BV140" s="9"/>
       <c r="BW140" s="9" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="BX140" s="9"/>
       <c r="BY140" s="9"/>
@@ -16653,7 +16781,7 @@
       <c r="R141" s="12"/>
       <c r="S141" s="12"/>
       <c r="AQ141" s="9" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="BK141" s="9"/>
       <c r="BL141" s="9"/>
@@ -16668,7 +16796,7 @@
       <c r="BU141" s="9"/>
       <c r="BV141" s="9"/>
       <c r="BW141" s="9" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="BX141" s="9"/>
       <c r="BY141" s="9"/>
@@ -16704,7 +16832,7 @@
       <c r="R142" s="12"/>
       <c r="S142" s="12"/>
       <c r="AQ142" s="9" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="BK142" s="9"/>
       <c r="BL142" s="9"/>
@@ -16719,7 +16847,7 @@
       <c r="BU142" s="9"/>
       <c r="BV142" s="9"/>
       <c r="BW142" s="9" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="BX142" s="9"/>
       <c r="BY142" s="9"/>
@@ -16755,7 +16883,7 @@
       <c r="R143" s="12"/>
       <c r="S143" s="12"/>
       <c r="AQ143" s="9" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="BK143" s="9"/>
       <c r="BL143" s="9"/>
@@ -16770,7 +16898,7 @@
       <c r="BU143" s="9"/>
       <c r="BV143" s="9"/>
       <c r="BW143" s="9" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="BX143" s="9"/>
       <c r="BY143" s="9"/>
@@ -16806,7 +16934,7 @@
       <c r="R144" s="12"/>
       <c r="S144" s="12"/>
       <c r="AQ144" s="9" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="BK144" s="9"/>
       <c r="BL144" s="9"/>
@@ -16821,7 +16949,7 @@
       <c r="BU144" s="9"/>
       <c r="BV144" s="9"/>
       <c r="BW144" s="9" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="BX144" s="9"/>
       <c r="BY144" s="9"/>
@@ -16857,7 +16985,7 @@
       <c r="R145" s="12"/>
       <c r="S145" s="12"/>
       <c r="AQ145" s="9" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="BK145" s="9"/>
       <c r="BL145" s="9"/>
@@ -16872,7 +17000,7 @@
       <c r="BU145" s="9"/>
       <c r="BV145" s="9"/>
       <c r="BW145" s="9" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="BX145" s="9"/>
       <c r="BY145" s="9"/>
@@ -16908,7 +17036,7 @@
       <c r="R146" s="12"/>
       <c r="S146" s="12"/>
       <c r="AQ146" s="9" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="BK146" s="9"/>
       <c r="BL146" s="9"/>
@@ -16959,7 +17087,7 @@
       <c r="R147" s="12"/>
       <c r="S147" s="12"/>
       <c r="AQ147" s="9" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="BK147" s="9"/>
       <c r="BL147" s="9"/>
@@ -16974,7 +17102,7 @@
       <c r="BU147" s="9"/>
       <c r="BV147" s="9"/>
       <c r="BW147" s="9" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="BX147" s="9"/>
       <c r="BY147" s="9"/>
@@ -17010,7 +17138,7 @@
       <c r="R148" s="12"/>
       <c r="S148" s="12"/>
       <c r="AQ148" s="9" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="BK148" s="9"/>
       <c r="BL148" s="9"/>
@@ -17025,7 +17153,7 @@
       <c r="BU148" s="9"/>
       <c r="BV148" s="9"/>
       <c r="BW148" s="9" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="BX148" s="9"/>
       <c r="BY148" s="9"/>
@@ -17061,7 +17189,7 @@
       <c r="R149" s="12"/>
       <c r="S149" s="12"/>
       <c r="AQ149" s="9" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="BK149" s="9"/>
       <c r="BL149" s="9"/>
@@ -17076,7 +17204,7 @@
       <c r="BU149" s="9"/>
       <c r="BV149" s="9"/>
       <c r="BW149" s="9" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="BX149" s="9"/>
       <c r="BY149" s="9"/>
@@ -17112,7 +17240,7 @@
       <c r="R150" s="12"/>
       <c r="S150" s="12"/>
       <c r="AQ150" s="9" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="BK150" s="9"/>
       <c r="BL150" s="9"/>
@@ -17127,7 +17255,7 @@
       <c r="BU150" s="9"/>
       <c r="BV150" s="9"/>
       <c r="BW150" s="9" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="BX150" s="9"/>
       <c r="BY150" s="9"/>
@@ -17163,7 +17291,7 @@
       <c r="R151" s="12"/>
       <c r="S151" s="12"/>
       <c r="AQ151" s="9" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="BK151" s="9"/>
       <c r="BL151" s="9"/>
@@ -17178,7 +17306,7 @@
       <c r="BU151" s="9"/>
       <c r="BV151" s="9"/>
       <c r="BW151" s="9" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="BX151" s="9"/>
       <c r="BY151" s="9"/>
@@ -17214,7 +17342,7 @@
       <c r="R152" s="12"/>
       <c r="S152" s="12"/>
       <c r="AQ152" s="9" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="BK152" s="9"/>
       <c r="BL152" s="9"/>
@@ -17229,7 +17357,7 @@
       <c r="BU152" s="9"/>
       <c r="BV152" s="9"/>
       <c r="BW152" s="9" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="BX152" s="9"/>
       <c r="BY152" s="9"/>
@@ -17265,7 +17393,7 @@
       <c r="R153" s="12"/>
       <c r="S153" s="12"/>
       <c r="AQ153" s="9" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="BK153" s="9"/>
       <c r="BL153" s="9"/>
@@ -17280,7 +17408,7 @@
       <c r="BU153" s="9"/>
       <c r="BV153" s="9"/>
       <c r="BW153" s="9" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
       <c r="BX153" s="9"/>
       <c r="BY153" s="9"/>
@@ -17316,7 +17444,7 @@
       <c r="R154" s="12"/>
       <c r="S154" s="12"/>
       <c r="AQ154" s="9" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="BK154" s="9"/>
       <c r="BL154" s="9"/>
@@ -17331,7 +17459,7 @@
       <c r="BU154" s="9"/>
       <c r="BV154" s="9"/>
       <c r="BW154" s="9" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="BX154" s="9"/>
       <c r="BY154" s="9"/>
@@ -17367,7 +17495,7 @@
       <c r="R155" s="12"/>
       <c r="S155" s="12"/>
       <c r="AQ155" s="9" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="BK155" s="9"/>
       <c r="BL155" s="9"/>
@@ -17382,7 +17510,7 @@
       <c r="BU155" s="9"/>
       <c r="BV155" s="9"/>
       <c r="BW155" s="9" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
       <c r="BX155" s="9"/>
       <c r="BY155" s="9"/>
@@ -17418,7 +17546,7 @@
       <c r="R156" s="12"/>
       <c r="S156" s="12"/>
       <c r="AQ156" s="9" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="BK156" s="9"/>
       <c r="BL156" s="9"/>
@@ -17433,7 +17561,7 @@
       <c r="BU156" s="9"/>
       <c r="BV156" s="9"/>
       <c r="BW156" s="9" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="BX156" s="9"/>
       <c r="BY156" s="9"/>
@@ -17469,7 +17597,7 @@
       <c r="R157" s="12"/>
       <c r="S157" s="12"/>
       <c r="AQ157" s="9" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="BK157" s="9"/>
       <c r="BL157" s="9"/>
@@ -17484,7 +17612,7 @@
       <c r="BU157" s="9"/>
       <c r="BV157" s="9"/>
       <c r="BW157" s="9" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="BX157" s="9"/>
       <c r="BY157" s="9"/>
@@ -17520,7 +17648,7 @@
       <c r="R158" s="12"/>
       <c r="S158" s="12"/>
       <c r="AQ158" s="9" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="BK158" s="9"/>
       <c r="BL158" s="9"/>
@@ -17535,7 +17663,7 @@
       <c r="BU158" s="9"/>
       <c r="BV158" s="9"/>
       <c r="BW158" s="9" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="BX158" s="9"/>
       <c r="BY158" s="9"/>
@@ -17571,7 +17699,7 @@
       <c r="R159" s="12"/>
       <c r="S159" s="12"/>
       <c r="AQ159" s="9" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="BK159" s="9"/>
       <c r="BL159" s="9"/>
@@ -17586,7 +17714,7 @@
       <c r="BU159" s="9"/>
       <c r="BV159" s="9"/>
       <c r="BW159" s="9" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="BX159" s="9"/>
       <c r="BY159" s="9"/>
@@ -17622,7 +17750,7 @@
       <c r="R160" s="12"/>
       <c r="S160" s="12"/>
       <c r="AQ160" s="9" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="BK160" s="9"/>
       <c r="BL160" s="9"/>
@@ -17637,7 +17765,7 @@
       <c r="BU160" s="9"/>
       <c r="BV160" s="9"/>
       <c r="BW160" s="9" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="BX160" s="9"/>
       <c r="BY160" s="9"/>
@@ -17673,7 +17801,7 @@
       <c r="R161" s="12"/>
       <c r="S161" s="12"/>
       <c r="AQ161" s="9" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="BK161" s="9"/>
       <c r="BL161" s="9"/>
@@ -17688,7 +17816,7 @@
       <c r="BU161" s="9"/>
       <c r="BV161" s="9"/>
       <c r="BW161" s="9" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="BX161" s="9"/>
       <c r="BY161" s="9"/>
@@ -17724,7 +17852,7 @@
       <c r="R162" s="12"/>
       <c r="S162" s="12"/>
       <c r="AQ162" s="9" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="BK162" s="9"/>
       <c r="BL162" s="9"/>
@@ -17739,7 +17867,7 @@
       <c r="BU162" s="9"/>
       <c r="BV162" s="9"/>
       <c r="BW162" s="9" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="BX162" s="9"/>
       <c r="BY162" s="9"/>
@@ -17775,7 +17903,7 @@
       <c r="R163" s="12"/>
       <c r="S163" s="12"/>
       <c r="AQ163" s="9" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="BK163" s="9"/>
       <c r="BL163" s="9"/>
@@ -17790,7 +17918,7 @@
       <c r="BU163" s="9"/>
       <c r="BV163" s="9"/>
       <c r="BW163" s="9" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="BX163" s="9"/>
       <c r="BY163" s="9"/>
@@ -17826,7 +17954,7 @@
       <c r="R164" s="12"/>
       <c r="S164" s="12"/>
       <c r="AQ164" s="9" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="BK164" s="9"/>
       <c r="BL164" s="9"/>
@@ -17841,7 +17969,7 @@
       <c r="BU164" s="9"/>
       <c r="BV164" s="9"/>
       <c r="BW164" s="9" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="BX164" s="9"/>
       <c r="BY164" s="9"/>
@@ -17877,7 +18005,7 @@
       <c r="R165" s="12"/>
       <c r="S165" s="12"/>
       <c r="AQ165" s="9" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="BK165" s="9"/>
       <c r="BL165" s="9"/>
@@ -17892,7 +18020,7 @@
       <c r="BU165" s="9"/>
       <c r="BV165" s="9"/>
       <c r="BW165" s="9" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="BX165" s="9"/>
       <c r="BY165" s="9"/>
@@ -17928,7 +18056,7 @@
       <c r="R166" s="12"/>
       <c r="S166" s="12"/>
       <c r="AQ166" s="9" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="BK166" s="9"/>
       <c r="BL166" s="9"/>
@@ -17943,7 +18071,7 @@
       <c r="BU166" s="9"/>
       <c r="BV166" s="9"/>
       <c r="BW166" s="9" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="BX166" s="9"/>
       <c r="BY166" s="9"/>
@@ -17979,7 +18107,7 @@
       <c r="R167" s="12"/>
       <c r="S167" s="12"/>
       <c r="AQ167" s="9" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="BK167" s="9"/>
       <c r="BL167" s="9"/>
@@ -17994,7 +18122,7 @@
       <c r="BU167" s="9"/>
       <c r="BV167" s="9"/>
       <c r="BW167" s="9" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="BX167" s="9"/>
       <c r="BY167" s="9"/>
@@ -18030,7 +18158,7 @@
       <c r="R168" s="12"/>
       <c r="S168" s="12"/>
       <c r="AQ168" s="9" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="BK168" s="9"/>
       <c r="BL168" s="9"/>
@@ -18045,7 +18173,7 @@
       <c r="BU168" s="9"/>
       <c r="BV168" s="9"/>
       <c r="BW168" s="9" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="BX168" s="9"/>
       <c r="BY168" s="9"/>
@@ -18081,7 +18209,7 @@
       <c r="R169" s="12"/>
       <c r="S169" s="12"/>
       <c r="AQ169" s="9" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="BK169" s="9"/>
       <c r="BL169" s="9"/>
@@ -18096,7 +18224,7 @@
       <c r="BU169" s="9"/>
       <c r="BV169" s="9"/>
       <c r="BW169" s="9" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="BX169" s="9"/>
       <c r="BY169" s="9"/>
@@ -18132,7 +18260,7 @@
       <c r="R170" s="12"/>
       <c r="S170" s="12"/>
       <c r="AQ170" s="9" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="BK170" s="9"/>
       <c r="BL170" s="9"/>
@@ -18147,7 +18275,7 @@
       <c r="BU170" s="9"/>
       <c r="BV170" s="9"/>
       <c r="BW170" s="9" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="BX170" s="9"/>
       <c r="BY170" s="9"/>
@@ -18183,7 +18311,7 @@
       <c r="R171" s="12"/>
       <c r="S171" s="12"/>
       <c r="AQ171" s="9" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="BK171" s="9"/>
       <c r="BL171" s="9"/>
@@ -18198,7 +18326,7 @@
       <c r="BU171" s="9"/>
       <c r="BV171" s="9"/>
       <c r="BW171" s="9" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="BX171" s="9"/>
       <c r="BY171" s="9"/>
@@ -18234,7 +18362,7 @@
       <c r="R172" s="12"/>
       <c r="S172" s="12"/>
       <c r="AQ172" s="9" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="173" spans="1:83" x14ac:dyDescent="0.35">
@@ -18262,7 +18390,7 @@
       <c r="R173" s="12"/>
       <c r="S173" s="12"/>
       <c r="AQ173" s="9" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="174" spans="1:83" x14ac:dyDescent="0.35">
@@ -18290,7 +18418,7 @@
       <c r="R174" s="12"/>
       <c r="S174" s="12"/>
       <c r="AQ174" s="9" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="175" spans="1:83" x14ac:dyDescent="0.35">
@@ -18318,7 +18446,7 @@
       <c r="R175" s="12"/>
       <c r="S175" s="12"/>
       <c r="AQ175" s="9" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="176" spans="1:83" x14ac:dyDescent="0.35">
@@ -18346,7 +18474,7 @@
       <c r="R176" s="12"/>
       <c r="S176" s="12"/>
       <c r="AQ176" s="9" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="177" spans="1:43" x14ac:dyDescent="0.35">
@@ -18374,7 +18502,7 @@
       <c r="R177" s="12"/>
       <c r="S177" s="12"/>
       <c r="AQ177" s="9" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="178" spans="1:43" x14ac:dyDescent="0.35">
@@ -18402,7 +18530,7 @@
       <c r="R178" s="12"/>
       <c r="S178" s="12"/>
       <c r="AQ178" s="9" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="179" spans="1:43" x14ac:dyDescent="0.35">
@@ -18430,7 +18558,7 @@
       <c r="R179" s="12"/>
       <c r="S179" s="12"/>
       <c r="AQ179" s="9" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="180" spans="1:43" x14ac:dyDescent="0.35">
@@ -18458,7 +18586,7 @@
       <c r="R180" s="12"/>
       <c r="S180" s="12"/>
       <c r="AQ180" s="9" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="181" spans="1:43" x14ac:dyDescent="0.35">
@@ -18486,7 +18614,7 @@
       <c r="R181" s="12"/>
       <c r="S181" s="12"/>
       <c r="AQ181" s="9" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="182" spans="1:43" x14ac:dyDescent="0.35">
@@ -18514,7 +18642,7 @@
       <c r="R182" s="12"/>
       <c r="S182" s="12"/>
       <c r="AQ182" s="9" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="183" spans="1:43" x14ac:dyDescent="0.35">
@@ -18542,7 +18670,7 @@
       <c r="R183" s="12"/>
       <c r="S183" s="12"/>
       <c r="AQ183" s="9" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="184" spans="1:43" x14ac:dyDescent="0.35">
@@ -18570,7 +18698,7 @@
       <c r="R184" s="12"/>
       <c r="S184" s="12"/>
       <c r="AQ184" s="9" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="185" spans="1:43" x14ac:dyDescent="0.35">
@@ -18598,7 +18726,7 @@
       <c r="R185" s="12"/>
       <c r="S185" s="12"/>
       <c r="AQ185" s="9" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="186" spans="1:43" x14ac:dyDescent="0.35">
@@ -18626,7 +18754,7 @@
       <c r="R186" s="12"/>
       <c r="S186" s="12"/>
       <c r="AQ186" s="9" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="187" spans="1:43" x14ac:dyDescent="0.35">
@@ -18654,7 +18782,7 @@
       <c r="R187" s="12"/>
       <c r="S187" s="12"/>
       <c r="AQ187" s="9" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="188" spans="1:43" x14ac:dyDescent="0.35">
@@ -18682,7 +18810,7 @@
       <c r="R188" s="12"/>
       <c r="S188" s="12"/>
       <c r="AQ188" s="9" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="189" spans="1:43" x14ac:dyDescent="0.35">
@@ -18710,7 +18838,7 @@
       <c r="R189" s="12"/>
       <c r="S189" s="12"/>
       <c r="AQ189" s="9" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="190" spans="1:43" x14ac:dyDescent="0.35">
@@ -18738,7 +18866,7 @@
       <c r="R190" s="12"/>
       <c r="S190" s="12"/>
       <c r="AQ190" s="9" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="191" spans="1:43" x14ac:dyDescent="0.35">
@@ -18766,7 +18894,7 @@
       <c r="R191" s="12"/>
       <c r="S191" s="12"/>
       <c r="AQ191" s="9" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="192" spans="1:43" x14ac:dyDescent="0.35">
@@ -18794,7 +18922,7 @@
       <c r="R192" s="12"/>
       <c r="S192" s="12"/>
       <c r="AQ192" s="9" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="193" spans="1:43" x14ac:dyDescent="0.35">
@@ -18822,7 +18950,7 @@
       <c r="R193" s="12"/>
       <c r="S193" s="12"/>
       <c r="AQ193" s="9" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="194" spans="1:43" x14ac:dyDescent="0.35">
@@ -18850,7 +18978,7 @@
       <c r="R194" s="12"/>
       <c r="S194" s="12"/>
       <c r="AQ194" s="9" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="195" spans="1:43" x14ac:dyDescent="0.35">
@@ -18878,7 +19006,7 @@
       <c r="R195" s="12"/>
       <c r="S195" s="12"/>
       <c r="AQ195" s="9" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="196" spans="1:43" x14ac:dyDescent="0.35">
@@ -18906,7 +19034,7 @@
       <c r="R196" s="12"/>
       <c r="S196" s="12"/>
       <c r="AQ196" s="9" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="197" spans="1:43" x14ac:dyDescent="0.35">
@@ -18934,7 +19062,7 @@
       <c r="R197" s="12"/>
       <c r="S197" s="12"/>
       <c r="AQ197" s="9" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="198" spans="1:43" x14ac:dyDescent="0.35">
@@ -18962,7 +19090,7 @@
       <c r="R198" s="12"/>
       <c r="S198" s="12"/>
       <c r="AQ198" s="9" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="199" spans="1:43" x14ac:dyDescent="0.35">
@@ -18990,7 +19118,7 @@
       <c r="R199" s="12"/>
       <c r="S199" s="12"/>
       <c r="AQ199" s="9" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="200" spans="1:43" x14ac:dyDescent="0.35">
@@ -19018,7 +19146,7 @@
       <c r="R200" s="12"/>
       <c r="S200" s="12"/>
       <c r="AQ200" s="9" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="201" spans="1:43" x14ac:dyDescent="0.35">
@@ -19046,7 +19174,7 @@
       <c r="R201" s="12"/>
       <c r="S201" s="12"/>
       <c r="AQ201" s="9" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="202" spans="1:43" x14ac:dyDescent="0.35">
@@ -19074,7 +19202,7 @@
       <c r="R202" s="12"/>
       <c r="S202" s="12"/>
       <c r="AQ202" s="9" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="203" spans="1:43" x14ac:dyDescent="0.35">
@@ -19102,7 +19230,7 @@
       <c r="R203" s="12"/>
       <c r="S203" s="12"/>
       <c r="AQ203" s="9" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="204" spans="1:43" x14ac:dyDescent="0.35">
@@ -19130,7 +19258,7 @@
       <c r="R204" s="12"/>
       <c r="S204" s="12"/>
       <c r="AQ204" s="9" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="205" spans="1:43" x14ac:dyDescent="0.35">
@@ -19158,7 +19286,7 @@
       <c r="R205" s="12"/>
       <c r="S205" s="12"/>
       <c r="AQ205" s="9" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="206" spans="1:43" x14ac:dyDescent="0.35">
@@ -19186,7 +19314,7 @@
       <c r="R206" s="12"/>
       <c r="S206" s="12"/>
       <c r="AQ206" s="9" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="207" spans="1:43" x14ac:dyDescent="0.35">
@@ -19214,7 +19342,7 @@
       <c r="R207" s="12"/>
       <c r="S207" s="12"/>
       <c r="AQ207" s="9" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="208" spans="1:43" x14ac:dyDescent="0.35">
@@ -19242,7 +19370,7 @@
       <c r="R208" s="12"/>
       <c r="S208" s="12"/>
       <c r="AQ208" s="9" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="209" spans="1:43" x14ac:dyDescent="0.35">
@@ -19270,7 +19398,7 @@
       <c r="R209" s="12"/>
       <c r="S209" s="12"/>
       <c r="AQ209" s="9" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="210" spans="1:43" x14ac:dyDescent="0.35">
@@ -19298,7 +19426,7 @@
       <c r="R210" s="12"/>
       <c r="S210" s="12"/>
       <c r="AQ210" s="9" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="211" spans="1:43" x14ac:dyDescent="0.35">
@@ -19326,7 +19454,7 @@
       <c r="R211" s="12"/>
       <c r="S211" s="12"/>
       <c r="AQ211" s="9" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="212" spans="1:43" x14ac:dyDescent="0.35">
@@ -19354,7 +19482,7 @@
       <c r="R212" s="12"/>
       <c r="S212" s="12"/>
       <c r="AQ212" s="9" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="213" spans="1:43" x14ac:dyDescent="0.35">
@@ -19382,7 +19510,7 @@
       <c r="R213" s="12"/>
       <c r="S213" s="12"/>
       <c r="AQ213" s="9" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="214" spans="1:43" x14ac:dyDescent="0.35">
@@ -19410,7 +19538,7 @@
       <c r="R214" s="12"/>
       <c r="S214" s="12"/>
       <c r="AQ214" s="9" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="215" spans="1:43" x14ac:dyDescent="0.35">
@@ -19438,7 +19566,7 @@
       <c r="R215" s="12"/>
       <c r="S215" s="12"/>
       <c r="AQ215" s="9" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="216" spans="1:43" x14ac:dyDescent="0.35">
@@ -19466,7 +19594,7 @@
       <c r="R216" s="12"/>
       <c r="S216" s="12"/>
       <c r="AQ216" s="9" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="217" spans="1:43" x14ac:dyDescent="0.35">
@@ -19494,7 +19622,7 @@
       <c r="R217" s="12"/>
       <c r="S217" s="12"/>
       <c r="AQ217" s="9" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="218" spans="1:43" x14ac:dyDescent="0.35">
@@ -19522,7 +19650,7 @@
       <c r="R218" s="12"/>
       <c r="S218" s="12"/>
       <c r="AQ218" s="9" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="219" spans="1:43" x14ac:dyDescent="0.35">
@@ -19550,7 +19678,7 @@
       <c r="R219" s="12"/>
       <c r="S219" s="12"/>
       <c r="AQ219" s="9" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="220" spans="1:43" x14ac:dyDescent="0.35">
@@ -19578,7 +19706,7 @@
       <c r="R220" s="12"/>
       <c r="S220" s="12"/>
       <c r="AQ220" s="9" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="221" spans="1:43" x14ac:dyDescent="0.35">
@@ -19606,7 +19734,7 @@
       <c r="R221" s="12"/>
       <c r="S221" s="12"/>
       <c r="AQ221" s="9" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="222" spans="1:43" x14ac:dyDescent="0.35">
@@ -19634,7 +19762,7 @@
       <c r="R222" s="12"/>
       <c r="S222" s="12"/>
       <c r="AQ222" s="9" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="223" spans="1:43" x14ac:dyDescent="0.35">
@@ -19662,7 +19790,7 @@
       <c r="R223" s="12"/>
       <c r="S223" s="12"/>
       <c r="AQ223" s="9" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="224" spans="1:43" x14ac:dyDescent="0.35">
@@ -19690,7 +19818,7 @@
       <c r="R224" s="12"/>
       <c r="S224" s="12"/>
       <c r="AQ224" s="9" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="225" spans="1:43" x14ac:dyDescent="0.35">
@@ -19718,7 +19846,7 @@
       <c r="R225" s="12"/>
       <c r="S225" s="12"/>
       <c r="AQ225" s="9" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="226" spans="1:43" x14ac:dyDescent="0.35">
@@ -19746,7 +19874,7 @@
       <c r="R226" s="12"/>
       <c r="S226" s="12"/>
       <c r="AQ226" s="9" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="227" spans="1:43" x14ac:dyDescent="0.35">
@@ -19774,7 +19902,7 @@
       <c r="R227" s="12"/>
       <c r="S227" s="12"/>
       <c r="AQ227" s="9" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="228" spans="1:43" x14ac:dyDescent="0.35">
@@ -19802,7 +19930,7 @@
       <c r="R228" s="12"/>
       <c r="S228" s="12"/>
       <c r="AQ228" s="9" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="229" spans="1:43" x14ac:dyDescent="0.35">
@@ -19830,7 +19958,7 @@
       <c r="R229" s="12"/>
       <c r="S229" s="12"/>
       <c r="AQ229" s="9" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="230" spans="1:43" x14ac:dyDescent="0.35">
@@ -19858,7 +19986,7 @@
       <c r="R230" s="12"/>
       <c r="S230" s="12"/>
       <c r="AQ230" s="9" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="231" spans="1:43" x14ac:dyDescent="0.35">
@@ -19886,7 +20014,7 @@
       <c r="R231" s="12"/>
       <c r="S231" s="12"/>
       <c r="AQ231" s="9" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="232" spans="1:43" x14ac:dyDescent="0.35">
@@ -19914,7 +20042,7 @@
       <c r="R232" s="12"/>
       <c r="S232" s="12"/>
       <c r="AQ232" s="9" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="233" spans="1:43" x14ac:dyDescent="0.35">
@@ -19942,7 +20070,7 @@
       <c r="R233" s="12"/>
       <c r="S233" s="12"/>
       <c r="AQ233" s="9" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="234" spans="1:43" x14ac:dyDescent="0.35">
@@ -19970,7 +20098,7 @@
       <c r="R234" s="12"/>
       <c r="S234" s="12"/>
       <c r="AQ234" s="9" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="235" spans="1:43" x14ac:dyDescent="0.35">
@@ -19998,7 +20126,7 @@
       <c r="R235" s="12"/>
       <c r="S235" s="12"/>
       <c r="AQ235" s="9" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="236" spans="1:43" x14ac:dyDescent="0.35">
@@ -20026,7 +20154,7 @@
       <c r="R236" s="12"/>
       <c r="S236" s="12"/>
       <c r="AQ236" s="9" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="237" spans="1:43" x14ac:dyDescent="0.35">
@@ -20054,7 +20182,7 @@
       <c r="R237" s="12"/>
       <c r="S237" s="12"/>
       <c r="AQ237" s="9" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="238" spans="1:43" x14ac:dyDescent="0.35">
@@ -20082,7 +20210,7 @@
       <c r="R238" s="12"/>
       <c r="S238" s="12"/>
       <c r="AQ238" s="9" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="239" spans="1:43" x14ac:dyDescent="0.35">
@@ -20110,7 +20238,7 @@
       <c r="R239" s="12"/>
       <c r="S239" s="12"/>
       <c r="AQ239" s="9" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="240" spans="1:43" x14ac:dyDescent="0.35">
@@ -20138,7 +20266,7 @@
       <c r="R240" s="12"/>
       <c r="S240" s="12"/>
       <c r="AQ240" s="9" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="241" spans="1:43" x14ac:dyDescent="0.35">
@@ -20166,7 +20294,7 @@
       <c r="R241" s="12"/>
       <c r="S241" s="12"/>
       <c r="AQ241" s="9" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="242" spans="1:43" x14ac:dyDescent="0.35">
@@ -20194,7 +20322,7 @@
       <c r="R242" s="12"/>
       <c r="S242" s="12"/>
       <c r="AQ242" s="9" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="243" spans="1:43" x14ac:dyDescent="0.35">
@@ -20222,7 +20350,7 @@
       <c r="R243" s="12"/>
       <c r="S243" s="12"/>
       <c r="AQ243" s="9" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="244" spans="1:43" x14ac:dyDescent="0.35">
@@ -20250,7 +20378,7 @@
       <c r="R244" s="12"/>
       <c r="S244" s="12"/>
       <c r="AQ244" s="9" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="245" spans="1:43" x14ac:dyDescent="0.35">
@@ -20278,7 +20406,7 @@
       <c r="R245" s="12"/>
       <c r="S245" s="12"/>
       <c r="AQ245" s="9" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="246" spans="1:43" x14ac:dyDescent="0.35">
@@ -20306,7 +20434,7 @@
       <c r="R246" s="12"/>
       <c r="S246" s="12"/>
       <c r="AQ246" s="9" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="247" spans="1:43" x14ac:dyDescent="0.35">
@@ -20334,7 +20462,7 @@
       <c r="R247" s="12"/>
       <c r="S247" s="12"/>
       <c r="AQ247" s="9" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="248" spans="1:43" x14ac:dyDescent="0.35">
@@ -20362,7 +20490,7 @@
       <c r="R248" s="12"/>
       <c r="S248" s="12"/>
       <c r="AQ248" s="9" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="249" spans="1:43" x14ac:dyDescent="0.35">
@@ -20390,7 +20518,7 @@
       <c r="R249" s="12"/>
       <c r="S249" s="12"/>
       <c r="AQ249" s="9" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="250" spans="1:43" x14ac:dyDescent="0.35">
@@ -20418,7 +20546,7 @@
       <c r="R250" s="12"/>
       <c r="S250" s="12"/>
       <c r="AQ250" s="9" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="251" spans="1:43" x14ac:dyDescent="0.35">
@@ -20446,7 +20574,7 @@
       <c r="R251" s="12"/>
       <c r="S251" s="12"/>
       <c r="AQ251" s="9" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="252" spans="1:43" x14ac:dyDescent="0.35">
@@ -20474,7 +20602,7 @@
       <c r="R252" s="12"/>
       <c r="S252" s="12"/>
       <c r="AQ252" s="9" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="253" spans="1:43" x14ac:dyDescent="0.35">
@@ -20502,1242 +20630,1242 @@
       <c r="R253" s="12"/>
       <c r="S253" s="12"/>
       <c r="AQ253" s="9" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="254" spans="1:43" x14ac:dyDescent="0.35">
       <c r="AQ254" s="9" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="255" spans="1:43" x14ac:dyDescent="0.35">
       <c r="AQ255" s="9" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="256" spans="1:43" x14ac:dyDescent="0.35">
       <c r="AQ256" s="9" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="257" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ257" s="9" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="258" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ258" s="9" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="259" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ259" s="9" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="260" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ260" s="9" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="261" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ261" s="9" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="262" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ262" s="9" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="263" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ263" s="9" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="264" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ264" s="9" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="265" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ265" s="9" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="266" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ266" s="9" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="267" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ267" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="268" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ268" s="9" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="269" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ269" s="9" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="270" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ270" s="9" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="271" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ271" s="9" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="272" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ272" s="9" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="273" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ273" s="9" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="274" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ274" s="9" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="275" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ275" s="9" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="276" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ276" s="9" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="277" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ277" s="9" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="278" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ278" s="9" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="279" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ279" s="9" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="280" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ280" s="9" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="281" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ281" s="9" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="282" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ282" s="9" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="283" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ283" s="9" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="284" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ284" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="285" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ285" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="286" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ286" s="9" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="287" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ287" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="288" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ288" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="289" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ289" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="290" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ290" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="291" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ291" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="292" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ292" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="293" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ293" s="9" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="294" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ294" s="9" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="295" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ295" s="9" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="296" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ296" s="9" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="297" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ297" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="298" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ298" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="299" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ299" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="300" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ300" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="301" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ301" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="302" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ302" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="303" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ303" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="304" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ304" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="305" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ305" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="306" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ306" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="307" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ307" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="308" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ308" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="309" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ309" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="310" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ310" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="311" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ311" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="312" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ312" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="313" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ313" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="314" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ314" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="315" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ315" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="316" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ316" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="317" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ317" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="318" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ318" s="9" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="319" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ319" s="9" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="320" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ320" s="9" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="321" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ321" s="9" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="322" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ322" s="9" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="323" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ323" s="9" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="324" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ324" s="9" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="325" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ325" s="9" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="326" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ326" s="9" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="327" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ327" s="9" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="328" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ328" s="9" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="329" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ329" s="9" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="330" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ330" s="9" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="331" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ331" s="9" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="332" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ332" s="9" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="333" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ333" s="9" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="334" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ334" s="9" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="335" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ335" s="9" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="336" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ336" s="9" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="337" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ337" s="9" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="338" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ338" s="9" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="339" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ339" s="9" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="340" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ340" s="9" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="341" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ341" s="9" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="342" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ342" s="9" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="343" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ343" s="9" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="344" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ344" s="9" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="345" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ345" s="9" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="346" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ346" s="9" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="347" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ347" s="9" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="348" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ348" s="9" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="349" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ349" s="9" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="350" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ350" s="9" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="351" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ351" s="9" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="352" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ352" s="9" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="353" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ353" s="9" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="354" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ354" s="9" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="355" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ355" s="9" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="356" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ356" s="9" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="357" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ357" s="9" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="358" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ358" s="9" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="359" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ359" s="9" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="360" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ360" s="9" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="361" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ361" s="9" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="362" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ362" s="9" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="363" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ363" s="9" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="364" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ364" s="9" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="365" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ365" s="9" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="366" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ366" s="9" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="367" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ367" s="9" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="368" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ368" s="9" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="369" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ369" s="9" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="370" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ370" s="9" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="371" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ371" s="9" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="372" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ372" s="9" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="373" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ373" s="9" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="374" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ374" s="9" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="375" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ375" s="9" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="376" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ376" s="9" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="377" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ377" s="9" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="378" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ378" s="9" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="379" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ379" s="9" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="380" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ380" s="9" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="381" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ381" s="9" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="382" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ382" s="9" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="383" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ383" s="9" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="384" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ384" s="9" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="385" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ385" s="9" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="386" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ386" s="9" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="387" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ387" s="9" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="388" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ388" s="9" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="389" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ389" s="9" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="390" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ390" s="9" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="391" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ391" s="9" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="392" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ392" s="9" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="393" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ393" s="9" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="394" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ394" s="9" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="395" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ395" s="9" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="396" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ396" s="9" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="397" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ397" s="9" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="398" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ398" s="9" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="399" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ399" s="9" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="400" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ400" s="9" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="401" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ401" s="9" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="402" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ402" s="9" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="403" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ403" s="9" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="404" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ404" s="9" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="405" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ405" s="9" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="406" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ406" s="9" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="407" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ407" s="9" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="408" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ408" s="9" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="409" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ409" s="9" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="410" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ410" s="9" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="411" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ411" s="9" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="412" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ412" s="9" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="413" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ413" s="9" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="414" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ414" s="9" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="415" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ415" s="9" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="416" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ416" s="9" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="417" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ417" s="9" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="418" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ418" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="419" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ419" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="420" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ420" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="421" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ421" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="422" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ422" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="423" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ423" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="424" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ424" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="425" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ425" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="426" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ426" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="427" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ427" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="428" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ428" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="429" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ429" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="430" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ430" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="431" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ431" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="432" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ432" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="433" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ433" s="9" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="434" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ434" s="9" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="435" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ435" s="9" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="436" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ436" s="9" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="437" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ437" s="9" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="438" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ438" s="9" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="439" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ439" s="9" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="440" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ440" s="9" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="441" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ441" s="9" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="442" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ442" s="9" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="443" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ443" s="9" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="444" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ444" s="9" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="445" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ445" s="9" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="446" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ446" s="9" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="447" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ447" s="9" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="448" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ448" s="9" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="449" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ449" s="9" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="450" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ450" s="9" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="451" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ451" s="9" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="452" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ452" s="9" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="453" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ453" s="9" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="454" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ454" s="9" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="455" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ455" s="9" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="456" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ456" s="9" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="457" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ457" s="9" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="458" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ458" s="9" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="459" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ459" s="9" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="460" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ460" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="461" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ461" s="9" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="462" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ462" s="9" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="463" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ463" s="9" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="464" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ464" s="9" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="465" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ465" s="9" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="466" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ466" s="9" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="467" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ467" s="9" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="468" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ468" s="9" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="469" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ469" s="9" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="470" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ470" s="9" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="471" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ471" s="9" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="472" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ472" s="9" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="473" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ473" s="9" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="474" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ474" s="9" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="475" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ475" s="9" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="476" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ476" s="9" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="477" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ477" s="9" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="478" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ478" s="9" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="479" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ479" s="9" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="480" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ480" s="9" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="481" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ481" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="482" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ482" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="483" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ483" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="484" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ484" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="485" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ485" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="486" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ486" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="487" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ487" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="488" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ488" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="489" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ489" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="490" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ490" s="9" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="491" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ491" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="492" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ492" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="493" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ493" s="9" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="494" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ494" s="9" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="495" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ495" s="9" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="496" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ496" s="9" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="497" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ497" s="9" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="498" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ498" s="9" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="499" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ499" s="9" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="500" spans="43:43" x14ac:dyDescent="0.35">
       <c r="AQ500" s="9" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
   </sheetData>
